--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
         <v>1.68</v>
@@ -1120,7 +1120,7 @@
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>3.7</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
         <v>2.42</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>2.66</v>
       </c>
       <c r="G7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
         <v>2.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G9" t="n">
         <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I12" t="n">
         <v>2.64</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
         <v>3.85</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
         <v>1.86</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -3654,10 +3654,10 @@
         <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="I13" t="n">
         <v>2.7</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
         <v>1.74</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -4416,22 +4416,22 @@
         <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H16" t="n">
         <v>2.3</v>
       </c>
       <c r="I16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J16" t="n">
         <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -4446,13 +4446,13 @@
         <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
         <v>1.81</v>
@@ -4464,7 +4464,7 @@
         <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
@@ -4527,7 +4527,7 @@
         <v>3.85</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS16" t="n">
         <v>3.1</v>
@@ -4575,68 +4575,68 @@
         <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
         <v>2.94</v>
@@ -4930,7 +4930,7 @@
         <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
         <v>2.02</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>
@@ -5435,16 +5435,16 @@
         <v>2.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 01:50:01</t>
+          <t>2026-05-23 04:24:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -863,10 +863,10 @@
         <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -875,16 +875,16 @@
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P2" t="n">
         <v>1.58</v>
@@ -893,194 +893,194 @@
         <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -1114,227 +1114,227 @@
         <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.35</v>
+        <v>1.94</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
         <v>440</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>3.45</v>
@@ -1628,7 +1628,7 @@
         <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
         <v>1.59</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I7" t="n">
         <v>2.66</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.6</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
         <v>2.94</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="H11" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
         <v>1.86</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -4168,7 +4168,7 @@
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H16" t="n">
         <v>2.3</v>
@@ -4584,13 +4584,13 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 04:24:16</t>
+          <t>2026-05-23 06:58:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -866,7 +866,7 @@
         <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>8.6</v>
@@ -1162,7 +1162,7 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -1383,16 +1383,16 @@
         <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -1401,194 +1401,194 @@
         <v>1.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
         <v>3.45</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H11" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="I11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H12" t="n">
         <v>2.46</v>
@@ -3430,7 +3430,7 @@
         <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
         <v>2.56</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
         <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
         <v>2.66</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.39</v>
@@ -4449,7 +4449,7 @@
         <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
         <v>3.75</v>
@@ -4464,7 +4464,7 @@
         <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
         <v>3.5</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
         <v>2.02</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 06:58:38</t>
+          <t>2026-05-23 09:32:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,10 +863,10 @@
         <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I2" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -893,16 +893,16 @@
         <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V2" t="n">
         <v>1.83</v>
@@ -914,34 +914,34 @@
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -968,34 +968,34 @@
         <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
         <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
         <v>8.6</v>
@@ -1135,16 +1135,16 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.36</v>
@@ -1162,7 +1162,7 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1258,7 +1258,7 @@
         <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.94</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="I4" t="n">
         <v>2.1</v>
@@ -1380,133 +1380,133 @@
         <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
         <v>1.01</v>
@@ -1524,71 +1524,71 @@
         <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
         <v>2.24</v>
@@ -1634,19 +1634,19 @@
         <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
         <v>2.44</v>
@@ -1655,184 +1655,184 @@
         <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -1876,227 +1876,227 @@
         <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH6" t="n">
         <v>3.8</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
         <v>1.71</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -2898,13 +2898,13 @@
         <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I12" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
         <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L16" t="n">
         <v>1.39</v>
@@ -4440,10 +4440,10 @@
         <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>2.08</v>
@@ -4461,7 +4461,7 @@
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
         <v>1.41</v>
@@ -4476,7 +4476,7 @@
         <v>970</v>
       </c>
       <c r="AA16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB16" t="n">
         <v>970</v>
@@ -4521,7 +4521,7 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ16" t="n">
         <v>3.85</v>
@@ -4530,19 +4530,19 @@
         <v>4.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AT16" t="n">
         <v>4.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AX16" t="n">
         <v>3</v>
@@ -4551,28 +4551,28 @@
         <v>4.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BB16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.25</v>
       </c>
-      <c r="BC16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BE16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BF16" t="n">
         <v>3.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH16" t="n">
         <v>3.25</v>
@@ -4584,66 +4584,66 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Comerciantes Unidos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.01</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,36 +4907,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,261 +5398,769 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 09:32:54</t>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-23 12:04:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-23 12:04:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Floresta EC</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F22" t="n">
         <v>1.86</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G22" t="n">
         <v>2.1</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H22" t="n">
         <v>1.94</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I22" t="n">
         <v>7.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J22" t="n">
         <v>3.05</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K22" t="n">
         <v>650</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.48</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q22" t="n">
         <v>2.44</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-05-23 09:32:54</t>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-23 12:04:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>1.98</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -875,34 +875,34 @@
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.42</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.46</v>
       </c>
       <c r="P2" t="n">
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
         <v>1.83</v>
@@ -911,176 +911,176 @@
         <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AU2" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
         <v>1.03</v>
       </c>
       <c r="AY2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>12</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>8.6</v>
@@ -1126,7 +1126,7 @@
         <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -1162,7 +1162,7 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
@@ -1404,13 +1404,13 @@
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.92</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
@@ -1619,166 +1619,166 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>5.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.59</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.58</v>
-      </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="V5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="n">
         <v>4.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1915,16 +1915,16 @@
         <v>2.98</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
         <v>19.5</v>
@@ -1990,7 +1990,7 @@
         <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -2014,7 +2014,7 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
         <v>1.03</v>
@@ -2026,19 +2026,19 @@
         <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sarpsborg</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
         <v>2.5</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kfum Oslo</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I8" t="n">
         <v>2.32</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH8" t="n">
         <v>3.35</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
@@ -2626,229 +2626,229 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ham-Kam</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.94</v>
+        <v>1.47</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>1.52</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
@@ -2880,229 +2880,229 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Ham-Kam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.47</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,234 +3129,234 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Kfum Oslo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="G11" t="n">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="I11" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="H12" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odds BK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>Ranheim IL</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.84</v>
+        <v>1.94</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G14" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
@@ -4145,234 +4145,234 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sarpsborg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.88</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I16" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>2.26</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AA16" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP16" t="n">
         <v>20</v>
       </c>
-      <c r="AI16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>3.85</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.1</v>
+        <v>19</v>
       </c>
       <c r="AX16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.94</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.2</v>
+        <v>18</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.25</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.18</v>
+        <v>9.4</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.31</v>
+        <v>6.6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.27</v>
+        <v>7.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.26</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
         <v>1.04</v>
       </c>
-      <c r="G18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
         <v>1.04</v>
       </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0</v>
-      </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X20" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI20" t="n">
         <v>2.72</v>
       </c>
-      <c r="I20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,498 +5669,3800 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>990</v>
       </c>
       <c r="J21" t="n">
-        <v>2.92</v>
+        <v>1.72</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-23 12:04:47</t>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lyngby</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AC Horsens</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X22" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Hacken</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IFK Goteborg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>44</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Norrkoping</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Osters</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X25" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CSKA 1948 Sofia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PFC Levski Sofia</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rapid Bucharest</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Peruvian Primera Division</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Deportivo Garcilaso</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Centro Atletico Fenix</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G31" t="n">
+        <v>600</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I31" t="n">
+        <v>870</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K31" t="n">
+        <v>500</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Floresta EC</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K22" t="n">
-        <v>650</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-05-23 12:04:47</t>
+      <c r="F35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:35:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB35"/>
+  <dimension ref="A1:CB38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,10 +863,10 @@
         <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -890,7 +890,7 @@
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
@@ -899,13 +899,13 @@
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
         <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W2" t="n">
         <v>1.24</v>
@@ -935,7 +935,7 @@
         <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG2" t="n">
         <v>23</v>
@@ -956,7 +956,7 @@
         <v>110</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN2" t="n">
         <v>140</v>
@@ -971,13 +971,13 @@
         <v>5.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
         <v>5.9</v>
@@ -989,7 +989,7 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
         <v>14.5</v>
@@ -998,37 +998,37 @@
         <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
         <v>18</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>48</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>4.7</v>
@@ -1064,23 +1064,23 @@
         <v>17</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>42</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
         <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>4.9</v>
@@ -1135,13 +1135,13 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
         <v>1.8</v>
@@ -1168,7 +1168,7 @@
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
         <v>70</v>
@@ -1183,7 +1183,7 @@
         <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>130</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>120</v>
@@ -1222,13 +1222,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
@@ -1237,10 +1237,10 @@
         <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
@@ -1249,40 +1249,40 @@
         <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
         <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,29 +1312,29 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
@@ -1506,22 +1506,22 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
         <v>9.800000000000001</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
         <v>5.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
@@ -1691,7 +1691,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>25</v>
@@ -1736,7 +1736,7 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
         <v>14.5</v>
@@ -1763,13 +1763,13 @@
         <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
         <v>6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1942,7 +1942,7 @@
         <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>16</v>
@@ -1990,7 +1990,7 @@
         <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -2014,31 +2014,31 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
         <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
         <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
         <v>2.58</v>
@@ -2148,10 +2148,10 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
@@ -2163,16 +2163,16 @@
         <v>2.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
         <v>1.54</v>
@@ -2181,112 +2181,112 @@
         <v>1.47</v>
       </c>
       <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG7" t="n">
         <v>16</v>
       </c>
-      <c r="Y7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>19</v>
-      </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>11</v>
       </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -2522,22 +2522,22 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
         <v>13.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.25</v>
@@ -2671,19 +2671,19 @@
         <v>1.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
         <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
         <v>2.92</v>
@@ -2701,7 +2701,7 @@
         <v>240</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
         <v>12.5</v>
@@ -2749,10 +2749,10 @@
         <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>9.4</v>
@@ -2764,7 +2764,7 @@
         <v>19.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2776,7 +2776,7 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
@@ -2785,16 +2785,16 @@
         <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
         <v>5.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="n">
         <v>4.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -2880,28 +2880,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ham-Kam</t>
+          <t>Kfum Oslo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.94</v>
       </c>
-      <c r="G10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.36</v>
-      </c>
       <c r="I10" t="n">
-        <v>2.48</v>
+        <v>3.35</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -2913,142 +2913,142 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="n">
         <v>24</v>
       </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
       <c r="AA10" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR10" t="n">
         <v>19</v>
       </c>
-      <c r="AI10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AS10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW10" t="n">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -3134,175 +3134,175 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kfum Oslo</t>
+          <t>Sarpsborg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF11" t="n">
         <v>12</v>
       </c>
-      <c r="AR11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG11" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>2.46</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -3433,7 +3433,7 @@
         <v>1.39</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S12" t="n">
         <v>1.98</v>
@@ -3445,16 +3445,16 @@
         <v>2.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
         <v>1.57</v>
       </c>
       <c r="X12" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
@@ -3463,13 +3463,13 @@
         <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC12" t="n">
         <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>29</v>
@@ -3478,10 +3478,10 @@
         <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
         <v>32</v>
@@ -3505,19 +3505,19 @@
         <v>13.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU12" t="n">
         <v>8.6</v>
@@ -3526,10 +3526,10 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY12" t="n">
         <v>9.800000000000001</v>
@@ -3538,19 +3538,19 @@
         <v>10</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF12" t="n">
         <v>7.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -3759,16 +3759,16 @@
         <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT13" t="n">
         <v>12</v>
@@ -3780,7 +3780,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
         <v>13.5</v>
@@ -3792,7 +3792,7 @@
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
         <v>17</v>
@@ -3801,10 +3801,10 @@
         <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
         <v>6.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -3905,40 +3905,40 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R14" t="n">
         <v>1.56</v>
@@ -3947,55 +3947,55 @@
         <v>2.46</v>
       </c>
       <c r="T14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
         <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF14" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
         <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
         <v>48</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>20</v>
@@ -4010,31 +4010,31 @@
         <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -4043,28 +4043,28 @@
         <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH14" t="n">
         <v>4.4</v>
@@ -4076,16 +4076,16 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO14" t="n">
         <v>3.85</v>
@@ -4094,31 +4094,31 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -4150,88 +4150,88 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sarpsborg</t>
+          <t>Ham-Kam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="G15" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I15" t="n">
         <v>2.5</v>
       </c>
-      <c r="I15" t="n">
-        <v>2.64</v>
-      </c>
       <c r="J15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z15" t="n">
         <v>22</v>
       </c>
-      <c r="Z15" t="n">
-        <v>27</v>
-      </c>
       <c r="AA15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
         <v>29</v>
@@ -4240,52 +4240,52 @@
         <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR15" t="n">
         <v>13</v>
       </c>
-      <c r="AR15" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AS15" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
         <v>17</v>
@@ -4297,28 +4297,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="BB15" t="n">
         <v>3.95</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
         <v>4</v>
       </c>
       <c r="BF15" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
         <v>2.56</v>
@@ -4431,16 +4431,16 @@
         <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
         <v>2.56</v>
@@ -4452,7 +4452,7 @@
         <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
         <v>1.44</v>
@@ -4461,13 +4461,13 @@
         <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X16" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
         <v>21</v>
@@ -4530,7 +4530,7 @@
         <v>17</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
         <v>13</v>
@@ -4554,10 +4554,10 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC16" t="n">
         <v>18</v>
@@ -4566,7 +4566,7 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -4685,16 +4685,16 @@
         <v>6.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P17" t="n">
         <v>3.05</v>
@@ -4703,194 +4703,194 @@
         <v>1.38</v>
       </c>
       <c r="R17" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="S17" t="n">
         <v>1.95</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL17" t="n">
         <v>25</v>
       </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>32</v>
-      </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT17" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BU17" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="BZ17" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.62</v>
+        <v>7.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="G18" t="n">
-        <v>3.85</v>
+        <v>1.89</v>
       </c>
       <c r="H18" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="P18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.72</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V18" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -5166,217 +5166,217 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="G19" t="n">
-        <v>1.89</v>
+        <v>2.76</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.2</v>
       </c>
-      <c r="K19" t="n">
-        <v>5</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="R19" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.47</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W19" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="X19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE19" t="n">
         <v>36</v>
       </c>
-      <c r="Y19" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>23</v>
       </c>
-      <c r="AE19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="n">
         <v>20</v>
       </c>
-      <c r="AI19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AO19" t="n">
         <v>25</v>
       </c>
-      <c r="AK19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>40</v>
-      </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
       </c>
       <c r="AU19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
@@ -5388,24 +5388,24 @@
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,31 +5420,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="O20" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5477,55 +5477,55 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
         <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -5591,75 +5591,75 @@
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,31 +5674,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="I21" t="n">
-        <v>990</v>
+        <v>2.42</v>
       </c>
       <c r="J21" t="n">
-        <v>1.72</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5707,22 +5707,22 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -5731,112 +5731,112 @@
         <v>1.11</v>
       </c>
       <c r="V21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.01</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -5946,19 +5946,19 @@
         <v>2.58</v>
       </c>
       <c r="I22" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
         <v>3.9</v>
@@ -5979,13 +5979,13 @@
         <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U22" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
         <v>1.56</v>
@@ -6006,7 +6006,7 @@
         <v>14</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD22" t="n">
         <v>15</v>
@@ -6015,13 +6015,13 @@
         <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
         <v>48</v>
@@ -6033,13 +6033,13 @@
         <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
         <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
         <v>29</v>
@@ -6054,7 +6054,7 @@
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -6078,19 +6078,19 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF22" t="n">
         <v>16</v>
@@ -6099,68 +6099,68 @@
         <v>17</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ22" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.63</v>
+        <v>5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.86</v>
+        <v>9.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP22" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="BR22" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.79</v>
+        <v>7.8</v>
       </c>
       <c r="BT22" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BV22" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="BX22" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.79</v>
+        <v>8</v>
       </c>
       <c r="BZ22" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.76</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H23" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I23" t="n">
         <v>2.64</v>
@@ -6206,52 +6206,52 @@
         <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
         <v>2.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y23" t="n">
         <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -6260,7 +6260,7 @@
         <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -6272,10 +6272,10 @@
         <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -6293,128 +6293,128 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.16</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.16</v>
+        <v>18.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>2.88</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H24" t="n">
         <v>2.56</v>
@@ -6463,7 +6463,7 @@
         <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
@@ -6487,16 +6487,16 @@
         <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
         <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
@@ -6592,7 +6592,7 @@
         <v>9.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BD24" t="n">
         <v>9.6</v>
@@ -6607,68 +6607,68 @@
         <v>19</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ24" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV24" t="n">
         <v>21</v>
       </c>
-      <c r="BN24" t="n">
+      <c r="BW24" t="n">
         <v>8.6</v>
       </c>
-      <c r="BO24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>12</v>
-      </c>
       <c r="BX24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BZ24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G25" t="n">
         <v>1.74</v>
@@ -6708,7 +6708,7 @@
         <v>4.9</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
         <v>4.3</v>
@@ -6717,16 +6717,16 @@
         <v>5.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.46</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
         <v>2.46</v>
@@ -6735,184 +6735,184 @@
         <v>1.59</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
         <v>2.34</v>
       </c>
       <c r="X25" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG25" t="n">
         <v>34</v>
       </c>
-      <c r="Y25" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
         <v>3.95</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -6971,16 +6971,16 @@
         <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P26" t="n">
         <v>2.36</v>
@@ -6989,184 +6989,184 @@
         <v>1.63</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,239 +7198,239 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H27" t="n">
         <v>2.52</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3</v>
-      </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="Q27" t="n">
         <v>2.08</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
@@ -7452,246 +7452,246 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1.86</v>
+        <v>2.92</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="I28" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="K28" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,181 +7706,181 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="G29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J29" t="n">
         <v>3.5</v>
       </c>
-      <c r="H29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X29" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>3.6</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X29" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ29" t="n">
+      <c r="AR29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH29" t="n">
         <v>3.85</v>
       </c>
-      <c r="AR29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB29" t="n">
+      <c r="BI29" t="n">
         <v>3.3</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>2.64</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
@@ -7892,60 +7892,60 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.18</v>
+        <v>4.8</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO29" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.31</v>
+        <v>5.5</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.27</v>
+        <v>7.6</v>
       </c>
       <c r="BT29" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>2.06</v>
+        <v>4.5</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.26</v>
+        <v>6.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,251 +7955,251 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
         <v>1.01</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,251 +8209,251 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="G31" t="n">
-        <v>600</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="I31" t="n">
-        <v>870</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K31" t="n">
-        <v>500</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,251 +8463,251 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,36 +8717,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Comerciantes Unidos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.84</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,36 +8971,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>2.16</v>
+        <v>600</v>
       </c>
       <c r="H34" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>870</v>
       </c>
       <c r="J34" t="n">
-        <v>2.92</v>
+        <v>1.03</v>
       </c>
       <c r="K34" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,261 +9208,1023 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-23 14:35:48</t>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>2026-05-23 17:05:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-05-23 17:05:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="inlineStr">
+        <is>
+          <t>2026-05-23 17:05:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Floresta EC</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="F38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J38" t="n">
         <v>3.1</v>
       </c>
-      <c r="K35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB35" t="inlineStr">
-        <is>
-          <t>2026-05-23 14:35:48</t>
+      <c r="K38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>2026-05-23 17:05:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -866,7 +866,7 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -884,19 +884,19 @@
         <v>2.72</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -905,7 +905,7 @@
         <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
         <v>5.8</v>
@@ -1162,7 +1162,7 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -1509,19 +1509,19 @@
         <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
         <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG4" t="n">
         <v>9.800000000000001</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I7" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.65</v>
@@ -2169,13 +2169,13 @@
         <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
         <v>1.47</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>5.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
         <v>2.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
         <v>1.57</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
         <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
         <v>1.63</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H16" t="n">
         <v>2.56</v>
       </c>
       <c r="I16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
@@ -4446,13 +4446,13 @@
         <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
         <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T16" t="n">
         <v>1.44</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
         <v>9.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>10.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -5205,10 +5205,10 @@
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.47</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.33</v>
@@ -5462,10 +5462,10 @@
         <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
         <v>3.3</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -5686,16 +5686,16 @@
         <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H21" t="n">
         <v>2.12</v>
       </c>
       <c r="I21" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
         <v>4.2</v>
@@ -5707,16 +5707,16 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="O21" t="n">
         <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R21" t="n">
         <v>1.43</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         <v>2.58</v>
       </c>
       <c r="I22" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
@@ -5985,7 +5985,7 @@
         <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
         <v>1.56</v>
@@ -5994,7 +5994,7 @@
         <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
         <v>21</v>
@@ -6024,7 +6024,7 @@
         <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ22" t="n">
         <v>42</v>
@@ -6054,7 +6054,7 @@
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -6078,19 +6078,19 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC22" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD22" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF22" t="n">
         <v>16</v>
@@ -6102,7 +6102,7 @@
         <v>3.7</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
         <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6221,19 +6221,19 @@
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q23" t="n">
         <v>1.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U23" t="n">
         <v>2.16</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G24" t="n">
         <v>3.15</v>
@@ -6505,7 +6505,7 @@
         <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AA24" t="n">
         <v>40</v>
@@ -6610,65 +6610,65 @@
         <v>3.3</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ24" t="n">
         <v>9.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT24" t="n">
         <v>5.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV24" t="n">
         <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
         <v>10</v>
       </c>
-      <c r="BZ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>55</v>
       </c>
       <c r="AJ25" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AK25" t="n">
         <v>16.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.27</v>
@@ -6989,7 +6989,7 @@
         <v>1.63</v>
       </c>
       <c r="R26" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S26" t="n">
         <v>2.6</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7210,19 @@
         <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="H27" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J27" t="n">
         <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L27" t="n">
         <v>1.43</v>
@@ -7255,10 +7255,10 @@
         <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X27" t="n">
         <v>970</v>
@@ -7318,7 +7318,7 @@
         <v>3.05</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="AR27" t="n">
         <v>3.15</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G28" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="H28" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7485,16 +7485,16 @@
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
         <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R28" t="n">
         <v>1.23</v>
@@ -7506,19 +7506,19 @@
         <v>1.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V28" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X28" t="n">
         <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
         <v>23</v>
@@ -7527,25 +7527,25 @@
         <v>75</v>
       </c>
       <c r="AB28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
         <v>55</v>
       </c>
       <c r="AF28" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
         <v>65</v>
@@ -7560,7 +7560,7 @@
         <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN28" t="n">
         <v>36</v>
@@ -7572,16 +7572,16 @@
         <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>15</v>
       </c>
       <c r="AS28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT28" t="n">
         <v>7</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
         <v>5.3</v>
@@ -7590,38 +7590,38 @@
         <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX28" t="n">
         <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
         <v>14</v>
       </c>
       <c r="BA28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC28" t="n">
         <v>7</v>
       </c>
-      <c r="BB28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF28" t="n">
         <v>7</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH28" t="n">
         <v>1000</v>
       </c>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
         <v>1.54</v>
       </c>
       <c r="I30" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="J30" t="n">
         <v>3.9</v>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="O30" t="n">
         <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
         <v>1.96</v>
       </c>
       <c r="R30" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="S30" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="n">
         <v>2.8</v>
@@ -8232,7 +8232,7 @@
         <v>2.9</v>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
         <v>3.15</v>
@@ -8262,7 +8262,7 @@
         <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
         <v>1.81</v>
@@ -8271,7 +8271,7 @@
         <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W31" t="n">
         <v>1.55</v>
@@ -8406,7 +8406,7 @@
         <v>5.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP31" t="n">
         <v>22</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G32" t="n">
         <v>2.58</v>
@@ -8495,7 +8495,7 @@
         <v>3.65</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -8731,220 +8731,220 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -8988,217 +8988,217 @@
         <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H34" t="n">
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K34" t="n">
         <v>950</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P34" t="n">
         <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -9239,34 +9239,34 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P35" t="n">
         <v>1.25</v>
@@ -9275,194 +9275,194 @@
         <v>1.01</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G37" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H37" t="n">
         <v>2.74</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>1.84</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H38" t="n">
         <v>4.9</v>
@@ -10031,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q38" t="n">
         <v>2.48</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-23 17:05:08</t>
+          <t>2026-05-23 19:32:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB38"/>
+  <dimension ref="A1:CB39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -890,13 +890,13 @@
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.9</v>
@@ -1162,7 +1162,7 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J4" t="n">
         <v>3.95</v>
@@ -1401,7 +1401,7 @@
         <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
         <v>3.1</v>
@@ -1461,7 +1461,7 @@
         <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -1536,13 +1536,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>7.8</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
         <v>5</v>
@@ -1569,7 +1569,7 @@
         <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW4" t="n">
         <v>6</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2289,68 +2289,68 @@
         <v>5</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.56</v>
+        <v>4.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.75</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.67</v>
+        <v>6.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV7" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.66</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.69</v>
+        <v>7.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>5.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kfum Oslo</t>
+          <t>Ham-Kam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.94</v>
+        <v>2.36</v>
       </c>
       <c r="I10" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,142 +2913,142 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
         <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW10" t="n">
         <v>17</v>
       </c>
-      <c r="AI10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AX10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY10" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -3433,10 +3433,10 @@
         <v>1.39</v>
       </c>
       <c r="R12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T12" t="n">
         <v>1.36</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
         <v>2.06</v>
@@ -3660,7 +3660,7 @@
         <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ham-Kam</t>
+          <t>Kfum Oslo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H15" t="n">
         <v>2.94</v>
       </c>
-      <c r="G15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.36</v>
-      </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T15" t="n">
         <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="X15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
         <v>24</v>
       </c>
-      <c r="Y15" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>22</v>
-      </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AB15" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
         <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR15" t="n">
         <v>19</v>
       </c>
-      <c r="AI15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="AS15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW15" t="n">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH15" t="n">
         <v>3.9</v>
       </c>
-      <c r="BE15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>2.56</v>
       </c>
       <c r="I16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
@@ -4452,7 +4452,7 @@
         <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
         <v>1.44</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
@@ -5223,7 +5223,7 @@
         <v>2.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
         <v>1.58</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,31 +5420,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="H20" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="I20" t="n">
-        <v>990</v>
+        <v>2.42</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="O20" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5477,10 +5477,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>3.9</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS21" t="n">
         <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
         <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG21" t="n">
         <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.76</v>
+        <v>990</v>
       </c>
       <c r="H22" t="n">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>990</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>1.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,244 +6177,244 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hacken</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.84</v>
+        <v>2.48</v>
       </c>
       <c r="G23" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="H23" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="I23" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
         <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="X23" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF23" t="n">
         <v>22</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG23" t="n">
         <v>17</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="BH23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP23" t="n">
         <v>21</v>
       </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -6436,246 +6436,246 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Hacken</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G24" t="n">
         <v>3.15</v>
       </c>
       <c r="H24" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W24" t="n">
         <v>1.46</v>
       </c>
       <c r="X24" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY24" t="n">
         <v>11</v>
       </c>
-      <c r="Z24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>1.31</v>
       </c>
       <c r="BA24" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>30</v>
+        <v>1.36</v>
       </c>
       <c r="BD24" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.5</v>
+        <v>1.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>19</v>
+        <v>1.4</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,251 +6685,251 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.68</v>
+        <v>2.86</v>
       </c>
       <c r="G25" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="T25" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="U25" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="W25" t="n">
-        <v>2.34</v>
+        <v>1.46</v>
       </c>
       <c r="X25" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AA25" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AD25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF25" t="n">
         <v>21</v>
       </c>
-      <c r="AE25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
         <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ25" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="AK25" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="AL25" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AN25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX25" t="n">
         <v>7.6</v>
       </c>
-      <c r="AO25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AY25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA25" t="n">
         <v>9.4</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="BB25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
         <v>11</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="BT25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW25" t="n">
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
         <v>10</v>
       </c>
-      <c r="AX25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>0</v>
-      </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,234 +6939,234 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="R26" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="X26" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y26" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA26" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AB26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD26" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI26" t="n">
         <v>55</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AK26" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AM26" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS26" t="n">
         <v>11</v>
       </c>
-      <c r="AO26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AT26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU26" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV26" t="n">
-        <v>13</v>
-      </c>
       <c r="AW26" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.6</v>
+        <v>38</v>
       </c>
       <c r="BB26" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.5</v>
+        <v>34</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,244 +7193,244 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="G27" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>2.32</v>
+        <v>3.95</v>
       </c>
       <c r="I27" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="P27" t="n">
-        <v>1.74</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="S27" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="U27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W27" t="n">
         <v>2</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.37</v>
-      </c>
       <c r="X27" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AE27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV27" t="n">
         <v>32</v>
       </c>
-      <c r="AF27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW27" t="n">
-        <v>2.22</v>
+        <v>7.6</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.26</v>
+        <v>7.8</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G29" t="n">
         <v>1.77</v>
@@ -7727,10 +7727,10 @@
         <v>7.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
         <v>1.3</v>
@@ -7742,13 +7742,13 @@
         <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
         <v>2.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R29" t="n">
         <v>1.41</v>
@@ -7763,7 +7763,7 @@
         <v>1.87</v>
       </c>
       <c r="V29" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W29" t="n">
         <v>2.28</v>
@@ -7826,7 +7826,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR29" t="n">
         <v>3.95</v>
@@ -7853,19 +7853,19 @@
         <v>7.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BC29" t="n">
         <v>12.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE29" t="n">
         <v>4.1</v>
@@ -7874,25 +7874,25 @@
         <v>7</v>
       </c>
       <c r="BG29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="BN29" t="n">
         <v>4.5</v>
@@ -7904,25 +7904,25 @@
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.5</v>
+        <v>2.08</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
@@ -7934,18 +7934,18 @@
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,251 +7955,251 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="G30" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="H30" t="n">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="I30" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="K30" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R30" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X30" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG30" t="n">
         <v>2.4</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH30" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.34</v>
+        <v>5.4</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.34</v>
+        <v>4.1</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.34</v>
+        <v>2.22</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8214,239 +8214,239 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>2.9</v>
+        <v>1.54</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="J31" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="P31" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>2.22</v>
       </c>
       <c r="T31" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BI31" t="n">
         <v>2.62</v>
       </c>
       <c r="BJ31" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.6</v>
+        <v>1.34</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>11.5</v>
+        <v>1.34</v>
       </c>
       <c r="BN31" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>4.3</v>
+        <v>1.34</v>
       </c>
       <c r="BP31" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>8</v>
+        <v>1.34</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>9.6</v>
+        <v>1.34</v>
       </c>
       <c r="BT31" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.8</v>
+        <v>1.34</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>8.6</v>
+        <v>1.34</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>9.800000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>9.199999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -8463,174 +8463,174 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="H32" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P32" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U32" t="n">
         <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W32" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="X32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP32" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>9</v>
-      </c>
       <c r="AQ32" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT32" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT32" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AU32" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW32" t="n">
         <v>7.8</v>
       </c>
       <c r="AX32" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
         <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="BB32" t="n">
         <v>7.8</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD32" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.68</v>
+        <v>9</v>
       </c>
       <c r="BF32" t="n">
         <v>7.4</v>
@@ -8639,75 +8639,75 @@
         <v>7.8</v>
       </c>
       <c r="BH32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ32" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK32" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>2.82</v>
+        <v>11.5</v>
       </c>
       <c r="BN32" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP32" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ32" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="BT32" t="n">
         <v>6.2</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>2.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,251 +8717,251 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G33" t="n">
         <v>2.58</v>
       </c>
       <c r="H33" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="I33" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L33" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="P33" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U33" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
         <v>1.63</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD33" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AF33" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG33" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI33" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ33" t="n">
         <v>40</v>
       </c>
       <c r="AK33" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL33" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN33" t="n">
         <v>36</v>
       </c>
       <c r="AO33" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AP33" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AQ33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS33" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AT33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BT33" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU33" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB33" t="n">
+      <c r="BU33" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8971,234 +8971,234 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Comerciantes Unidos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G34" t="n">
-        <v>990</v>
+        <v>2.58</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I34" t="n">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="K34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH34" t="n">
         <v>950</v>
       </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH34" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ34" t="n">
         <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,36 +9225,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>2.4</v>
+        <v>990</v>
       </c>
       <c r="H35" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>5.6</v>
+        <v>990</v>
       </c>
       <c r="J35" t="n">
-        <v>2.84</v>
+        <v>1.08</v>
       </c>
       <c r="K35" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -9266,31 +9266,31 @@
         <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R35" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S35" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -9401,75 +9401,75 @@
         <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35" t="n">
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN35" t="n">
         <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9479,244 +9479,244 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="G36" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H36" t="n">
         <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J36" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K36" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P36" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -9765,16 +9765,16 @@
         <v>3.5</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P37" t="n">
         <v>1.84</v>
@@ -9783,194 +9783,194 @@
         <v>2.02</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-23 19:32:41</t>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>
@@ -9992,239 +9992,493 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>2026-05-23 21:58:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Floresta EC</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F39" t="n">
         <v>1.84</v>
       </c>
-      <c r="G38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H38" t="n">
+      <c r="G39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H39" t="n">
         <v>4.9</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I39" t="n">
         <v>6.8</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>3.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>4</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="L39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q39" t="n">
         <v>2.48</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB38" t="inlineStr">
-        <is>
-          <t>2026-05-23 19:32:41</t>
+      <c r="R39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X39" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-05-23 21:58:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB39"/>
+  <dimension ref="A1:CB41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -884,7 +884,7 @@
         <v>2.72</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
         <v>1.58</v>
@@ -896,7 +896,7 @@
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -905,7 +905,7 @@
         <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
         <v>2.42</v>
@@ -1276,7 +1276,7 @@
         <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1906,13 +1906,13 @@
         <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
         <v>1.64</v>
@@ -1924,7 +1924,7 @@
         <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X6" t="n">
         <v>19.5</v>
@@ -2038,19 +2038,19 @@
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN6" t="n">
         <v>5.5</v>
@@ -2062,13 +2062,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
         <v>29</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
         <v>7</v>
@@ -2086,17 +2086,17 @@
         <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
         <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2310,7 +2310,7 @@
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
         <v>26</v>
@@ -2328,7 +2328,7 @@
         <v>6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
         <v>25</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G8" t="n">
         <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>2.32</v>
@@ -2396,7 +2396,7 @@
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.43</v>
@@ -2408,19 +2408,19 @@
         <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
         <v>1.71</v>
@@ -2435,13 +2435,13 @@
         <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="n">
         <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA8" t="n">
         <v>34</v>
@@ -2453,7 +2453,7 @@
         <v>9.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>30</v>
@@ -2522,43 +2522,43 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
       </c>
       <c r="BG8" t="n">
         <v>13.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
         <v>7.6</v>
@@ -2570,13 +2570,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
         <v>5</v>
@@ -2585,7 +2585,7 @@
         <v>3.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
         <v>6.2</v>
@@ -2594,17 +2594,17 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
         <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
         <v>6</v>
@@ -2749,10 +2749,10 @@
         <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
         <v>9.4</v>
@@ -2764,7 +2764,7 @@
         <v>19.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2794,10 +2794,10 @@
         <v>5.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI9" t="n">
         <v>3.35</v>
@@ -2806,13 +2806,13 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
@@ -2827,28 +2827,28 @@
         <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
         <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
         <v>60</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ham-Kam</t>
+          <t>Kfum Oslo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.94</v>
       </c>
-      <c r="G10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.36</v>
-      </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,196 +2913,196 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="n">
         <v>24</v>
       </c>
-      <c r="Y10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
       <c r="AA10" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR10" t="n">
         <v>19</v>
       </c>
-      <c r="AI10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AS10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW10" t="n">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH10" t="n">
         <v>3.9</v>
       </c>
-      <c r="BE10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
         <v>1.5</v>
@@ -3230,7 +3230,7 @@
         <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ11" t="n">
         <v>48</v>
@@ -3287,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.36</v>
       </c>
       <c r="G12" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H12" t="n">
         <v>2.46</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -3415,13 +3415,13 @@
         <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>1.13</v>
@@ -3436,16 +3436,16 @@
         <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
         <v>2.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
         <v>1.57</v>
@@ -3580,19 +3580,19 @@
         <v>9</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
         <v>23</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BT12" t="n">
         <v>9.199999999999999</v>
@@ -3604,23 +3604,23 @@
         <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA12" t="n">
         <v>1.88</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G13" t="n">
         <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -3669,7 +3669,7 @@
         <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
@@ -3738,7 +3738,7 @@
         <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
         <v>29</v>
@@ -3765,7 +3765,7 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS13" t="n">
         <v>5.9</v>
@@ -3780,7 +3780,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX13" t="n">
         <v>13.5</v>
@@ -3813,68 +3813,68 @@
         <v>18.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
         <v>3.7</v>
@@ -3917,10 +3917,10 @@
         <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
@@ -3935,7 +3935,7 @@
         <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q14" t="n">
         <v>1.51</v>
@@ -4019,7 +4019,7 @@
         <v>4.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="AS14" t="n">
         <v>5.3</v>
@@ -4076,13 +4076,13 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
@@ -4094,41 +4094,41 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kfum Oslo</t>
+          <t>Ham-Kam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="G15" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
         <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW15" t="n">
         <v>17</v>
       </c>
-      <c r="AI15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="AX15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY15" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="BF15" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
         <v>2.56</v>
       </c>
       <c r="I16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q16" t="n">
         <v>1.47</v>
@@ -4458,13 +4458,13 @@
         <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4515,7 +4515,7 @@
         <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
         <v>16.5</v>
@@ -4536,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB16" t="n">
         <v>4.5</v>
@@ -4566,7 +4566,7 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
@@ -4584,13 +4584,13 @@
         <v>8.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
         <v>6.4</v>
@@ -4602,16 +4602,16 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU16" t="n">
         <v>5</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>4.8</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.19</v>
@@ -4706,7 +4706,7 @@
         <v>1.85</v>
       </c>
       <c r="S17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T17" t="n">
         <v>1.53</v>
@@ -4718,7 +4718,7 @@
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
         <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="R18" t="n">
         <v>1.66</v>
@@ -4963,10 +4963,10 @@
         <v>2.14</v>
       </c>
       <c r="T18" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="U18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
         <v>1.25</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
@@ -5199,25 +5199,25 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T19" t="n">
         <v>1.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.59</v>
       </c>
       <c r="U19" t="n">
         <v>2.38</v>
@@ -5226,7 +5226,7 @@
         <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5265,10 +5265,10 @@
         <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
         <v>40</v>
@@ -5292,7 +5292,7 @@
         <v>15.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
         <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX19" t="n">
         <v>13.5</v>
@@ -5316,7 +5316,7 @@
         <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB19" t="n">
         <v>3.9</v>
@@ -5325,10 +5325,10 @@
         <v>3.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
         <v>12</v>
@@ -5346,7 +5346,7 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5388,24 +5388,24 @@
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,246 +5420,246 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.85</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS20" t="n">
         <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
         <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28</v>
+        <v>990</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>990</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="K21" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>1.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
         <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
         <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
         <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
         <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,67 +5928,67 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>990</v>
+        <v>3.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="I22" t="n">
-        <v>990</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O22" t="n">
         <v>1.25</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R22" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>1.05</v>
+        <v>2.72</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6099,68 +6099,68 @@
         <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
         <v>3.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.6</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -6466,13 +6466,13 @@
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
         <v>1.99</v>
@@ -6481,130 +6481,130 @@
         <v>1.88</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
         <v>1.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG24" t="n">
         <v>18.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.4</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
@@ -7115,58 +7115,58 @@
         <v>34</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
         <v>1.54</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
         <v>1.6</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,239 +7452,239 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="G28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.05</v>
       </c>
-      <c r="H28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.86</v>
-      </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="W28" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="X28" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
         <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AA28" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AB28" t="n">
         <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AG28" t="n">
         <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL28" t="n">
         <v>65</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
         <v>55</v>
       </c>
-      <c r="AK28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>36</v>
-      </c>
       <c r="AO28" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="AR28" t="n">
-        <v>15</v>
+        <v>3.15</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.6</v>
+        <v>2.46</v>
       </c>
       <c r="AT28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="AV28" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.4</v>
+        <v>2.42</v>
       </c>
       <c r="AX28" t="n">
-        <v>12</v>
+        <v>2.38</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.6</v>
+        <v>3.15</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14</v>
+        <v>2.32</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.4</v>
+        <v>2.54</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>2.52</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.199999999999999</v>
+        <v>2.56</v>
       </c>
       <c r="BF28" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -7706,205 +7706,205 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.63</v>
+        <v>2.58</v>
       </c>
       <c r="G29" t="n">
-        <v>1.77</v>
+        <v>3.05</v>
       </c>
       <c r="H29" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="I29" t="n">
-        <v>7.2</v>
+        <v>3.65</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>5.1</v>
+        <v>3.25</v>
       </c>
       <c r="L29" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>2.98</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="W29" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="X29" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL29" t="n">
         <v>60</v>
       </c>
-      <c r="AA29" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>42</v>
-      </c>
       <c r="AM29" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN29" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AO29" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC29" t="n">
         <v>7</v>
       </c>
-      <c r="AV29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY29" t="n">
+      <c r="BD29" t="n">
         <v>7.4</v>
       </c>
-      <c r="AZ29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE29" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
         <v>7</v>
       </c>
       <c r="BG29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO29" t="n">
         <v>4.1</v>
       </c>
-      <c r="BH29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
@@ -7913,39 +7913,39 @@
         <v>7.8</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,181 +7960,181 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="G30" t="n">
-        <v>3.65</v>
+        <v>1.77</v>
       </c>
       <c r="H30" t="n">
-        <v>2.34</v>
+        <v>5.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2.64</v>
+        <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="P30" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="T30" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="V30" t="n">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>2.28</v>
       </c>
       <c r="X30" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="AB30" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE30" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
         <v>950</v>
       </c>
       <c r="AI30" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AJ30" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.05</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD30" t="n">
         <v>3.85</v>
       </c>
-      <c r="AR30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BE30" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
@@ -8146,53 +8146,53 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
         <v>5.1</v>
       </c>
-      <c r="BP30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.26</v>
+        <v>7</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -8259,10 +8259,10 @@
         <v>1.96</v>
       </c>
       <c r="R31" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
         <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -8516,7 +8516,7 @@
         <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
         <v>1.81</v>
@@ -8531,7 +8531,7 @@
         <v>1.56</v>
       </c>
       <c r="X32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y32" t="n">
         <v>11.5</v>
@@ -8585,7 +8585,7 @@
         <v>40</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ32" t="n">
         <v>9.4</v>
@@ -8594,7 +8594,7 @@
         <v>17.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT32" t="n">
         <v>8.4</v>
@@ -8606,7 +8606,7 @@
         <v>11.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX32" t="n">
         <v>14.5</v>
@@ -8621,22 +8621,22 @@
         <v>38</v>
       </c>
       <c r="BB32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC32" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>7.4</v>
       </c>
       <c r="BD32" t="n">
         <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="n">
         <v>3.2</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>3.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
         <v>3.65</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -8994,19 +8994,19 @@
         <v>3.45</v>
       </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="L34" t="n">
         <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
         <v>2.84</v>
@@ -9018,7 +9018,7 @@
         <v>1.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R34" t="n">
         <v>1.23</v>
@@ -9027,16 +9027,16 @@
         <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="U34" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W34" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X34" t="n">
         <v>11.5</v>
@@ -9099,7 +9099,7 @@
         <v>8.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="AS34" t="n">
         <v>4.9</v>
@@ -9117,13 +9117,13 @@
         <v>4.8</v>
       </c>
       <c r="AX34" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AY34" t="n">
         <v>9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
         <v>4.9</v>
@@ -9132,13 +9132,13 @@
         <v>4.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD34" t="n">
         <v>4.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF34" t="n">
         <v>4.5</v>
@@ -9162,13 +9162,13 @@
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="BN34" t="n">
         <v>5.1</v>
       </c>
       <c r="BO34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
@@ -9180,7 +9180,7 @@
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>2.28</v>
+        <v>3.45</v>
       </c>
       <c r="BT34" t="n">
         <v>6.8</v>
@@ -9192,13 +9192,13 @@
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H35" t="n">
         <v>1.04</v>
@@ -9251,7 +9251,7 @@
         <v>990</v>
       </c>
       <c r="J35" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K35" t="n">
         <v>950</v>
@@ -9263,10 +9263,10 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P35" t="n">
         <v>1.24</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
         <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>3.1</v>
@@ -9511,34 +9511,34 @@
         <v>3.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="O36" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="Q36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T36" t="n">
         <v>2.08</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="V36" t="n">
         <v>1.26</v>
@@ -9547,176 +9547,176 @@
         <v>1.83</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV36" t="n">
         <v>16</v>
       </c>
-      <c r="Z36" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AW36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX36" t="n">
         <v>10</v>
       </c>
-      <c r="AD36" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AY36" t="n">
-        <v>2.1</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.28</v>
+        <v>20</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.46</v>
+        <v>7.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>19.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.38</v>
+        <v>7.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.46</v>
+        <v>8</v>
       </c>
       <c r="BF36" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.46</v>
+        <v>7.8</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
         <v>3.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9864,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT37" t="n">
         <v>9.199999999999999</v>
@@ -9876,7 +9876,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.05</v>
+        <v>6.6</v>
       </c>
       <c r="AX37" t="n">
         <v>15.5</v>
@@ -9888,89 +9888,89 @@
         <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.05</v>
+        <v>6.6</v>
       </c>
       <c r="BD37" t="n">
         <v>32</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.05</v>
+        <v>6.6</v>
       </c>
       <c r="BH37" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ37" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN37" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR37" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT37" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV37" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX37" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ37" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
         <v>3.7</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
         <v>4.9</v>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
         <v>3.1</v>
@@ -10285,10 +10285,10 @@
         <v>1.5</v>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R39" t="n">
         <v>1.19</v>
@@ -10303,10 +10303,10 @@
         <v>1.71</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X39" t="n">
         <v>11</v>
@@ -10369,10 +10369,10 @@
         <v>10</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT39" t="n">
         <v>4.9</v>
@@ -10384,7 +10384,7 @@
         <v>16.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX39" t="n">
         <v>7.6</v>
@@ -10396,7 +10396,7 @@
         <v>18.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB39" t="n">
         <v>16.5</v>
@@ -10405,16 +10405,16 @@
         <v>19</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF39" t="n">
         <v>16</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH39" t="n">
         <v>2.86</v>
@@ -10478,7 +10478,515 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-23 21:58:43</t>
+          <t>2026-05-24 00:23:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Deportes Copiapo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Union Espanola</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-05-24 00:23:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H41" t="n">
+        <v>11</v>
+      </c>
+      <c r="I41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>2026-05-24 00:23:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.46</v>
@@ -887,7 +887,7 @@
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
         <v>2.38</v>
@@ -896,19 +896,19 @@
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -938,7 +938,7 @@
         <v>38</v>
       </c>
       <c r="AG2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
         <v>27</v>
@@ -950,19 +950,19 @@
         <v>140</v>
       </c>
       <c r="AK2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="n">
         <v>110</v>
       </c>
       <c r="AM2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>7.4</v>
@@ -986,10 +986,10 @@
         <v>8.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
         <v>14.5</v>
@@ -998,25 +998,25 @@
         <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
         <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
         <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="n">
         <v>2.92</v>
@@ -1025,10 +1025,10 @@
         <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,28 +1040,28 @@
         <v>8</v>
       </c>
       <c r="BO2" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW2" t="n">
         <v>6.8</v>
@@ -1070,7 +1070,7 @@
         <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>42</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J3" t="n">
         <v>4.1</v>
@@ -1129,55 +1129,55 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
         <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
         <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1210,28 +1210,28 @@
         <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP3" t="n">
         <v>11</v>
       </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.4</v>
@@ -1240,7 +1240,7 @@
         <v>4.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
@@ -1255,46 +1255,46 @@
         <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
         <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -1371,40 +1371,40 @@
         <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J4" t="n">
         <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.74</v>
@@ -1413,13 +1413,13 @@
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W4" t="n">
         <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>12</v>
@@ -1428,7 +1428,7 @@
         <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB4" t="n">
         <v>16.5</v>
@@ -1440,7 +1440,7 @@
         <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
         <v>32</v>
@@ -1488,7 +1488,7 @@
         <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
         <v>7.8</v>
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
@@ -1506,22 +1506,22 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG4" t="n">
         <v>9.800000000000001</v>
@@ -1575,7 +1575,7 @@
         <v>6</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY4" t="n">
         <v>7.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>3.25</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
         <v>2.38</v>
@@ -1637,7 +1637,7 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1673,7 +1673,7 @@
         <v>1.44</v>
       </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
         <v>40</v>
@@ -1736,7 +1736,7 @@
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>14.5</v>
@@ -1763,16 +1763,16 @@
         <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>16.5</v>
@@ -1790,13 +1790,13 @@
         <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN5" t="n">
         <v>7</v>
@@ -1808,13 +1808,13 @@
         <v>22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR5" t="n">
         <v>29</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT5" t="n">
         <v>5.9</v>
@@ -1823,7 +1823,7 @@
         <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW5" t="n">
         <v>6</v>
@@ -1832,7 +1832,7 @@
         <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
@@ -1897,16 +1897,16 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
@@ -1921,7 +1921,7 @@
         <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
         <v>1.76</v>
@@ -1963,7 +1963,7 @@
         <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>36</v>
@@ -1990,7 +1990,7 @@
         <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -2014,7 +2014,7 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
         <v>5</v>
@@ -2023,16 +2023,16 @@
         <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
         <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH6" t="n">
         <v>3.8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
@@ -2136,13 +2136,13 @@
         <v>2.56</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.45</v>
@@ -2175,7 +2175,7 @@
         <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
         <v>1.47</v>
@@ -2190,7 +2190,7 @@
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
@@ -2214,7 +2214,7 @@
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
         <v>60</v>
@@ -2226,67 +2226,67 @@
         <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
         <v>42</v>
       </c>
       <c r="AO7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV7" t="n">
         <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
         <v>15.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="BH7" t="n">
         <v>3.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I8" t="n">
         <v>2.32</v>
@@ -2399,7 +2399,7 @@
         <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -2447,7 +2447,7 @@
         <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
         <v>9.4</v>
@@ -2459,7 +2459,7 @@
         <v>30</v>
       </c>
       <c r="AF8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
         <v>20</v>
@@ -2495,13 +2495,13 @@
         <v>6.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.6</v>
+        <v>3.45</v>
       </c>
       <c r="AS8" t="n">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="AU8" t="n">
         <v>5.9</v>
@@ -2510,7 +2510,7 @@
         <v>8</v>
       </c>
       <c r="AW8" t="n">
-        <v>17.5</v>
+        <v>3.9</v>
       </c>
       <c r="AX8" t="n">
         <v>20</v>
@@ -2522,25 +2522,25 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG8" t="n">
-        <v>13.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH8" t="n">
         <v>3.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -2797,10 +2797,10 @@
         <v>7</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
@@ -2815,40 +2815,40 @@
         <v>9</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
         <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>60</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -2904,10 +2904,10 @@
         <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2928,7 +2928,7 @@
         <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
         <v>2.5</v>
@@ -3161,7 +3161,7 @@
         <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
@@ -3203,7 +3203,7 @@
         <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
         <v>44</v>
@@ -3245,7 +3245,7 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO11" t="n">
         <v>15.5</v>
@@ -3260,7 +3260,7 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
@@ -3287,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -3305,58 +3305,58 @@
         <v>11</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -3415,13 +3415,13 @@
         <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.13</v>
@@ -3430,25 +3430,25 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S12" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U12" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3460,7 +3460,7 @@
         <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
@@ -3469,16 +3469,16 @@
         <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
         <v>970</v>
@@ -3487,37 +3487,37 @@
         <v>32</v>
       </c>
       <c r="AJ12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP12" t="n">
         <v>3.85</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.75</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
         <v>3.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.65</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>8.6</v>
@@ -3526,101 +3526,101 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>10</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.75</v>
+        <v>19</v>
       </c>
       <c r="BB12" t="n">
         <v>3.85</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.65</v>
+        <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.75</v>
+        <v>17.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.06</v>
+        <v>8.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.93</v>
+        <v>6.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.97</v>
+        <v>6.8</v>
       </c>
       <c r="BT12" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.94</v>
+        <v>6.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.88</v>
+        <v>5.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -3905,49 +3905,49 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
         <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
         <v>2.22</v>
@@ -3956,7 +3956,7 @@
         <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
         <v>950</v>
@@ -3965,7 +3965,7 @@
         <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
         <v>90</v>
@@ -4013,16 +4013,16 @@
         <v>36</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR14" t="n">
         <v>4.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -4031,10 +4031,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -4043,22 +4043,22 @@
         <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
         <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF14" t="n">
         <v>6.4</v>
@@ -4070,37 +4070,37 @@
         <v>4.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
@@ -4112,23 +4112,23 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G15" t="n">
         <v>3.1</v>
@@ -4168,16 +4168,16 @@
         <v>2.38</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J15" t="n">
         <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -4192,13 +4192,13 @@
         <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
         <v>1.61</v>
@@ -4207,13 +4207,13 @@
         <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
         <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
         <v>16</v>
@@ -4237,10 +4237,10 @@
         <v>29</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
         <v>19</v>
@@ -4276,7 +4276,7 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
@@ -4300,19 +4300,19 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BB15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD15" t="n">
         <v>4</v>
       </c>
-      <c r="BC15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
         <v>16.5</v>
@@ -4321,58 +4321,58 @@
         <v>13</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H16" t="n">
         <v>2.56</v>
@@ -4437,40 +4437,40 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S16" t="n">
         <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
         <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
         <v>26</v>
@@ -4479,7 +4479,7 @@
         <v>46</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC16" t="n">
         <v>12</v>
@@ -4515,7 +4515,7 @@
         <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO16" t="n">
         <v>16.5</v>
@@ -4524,19 +4524,19 @@
         <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
         <v>17</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
@@ -4572,13 +4572,13 @@
         <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH16" t="n">
         <v>4.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ16" t="n">
         <v>8.6</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16" t="n">
         <v>6.4</v>
@@ -4602,41 +4602,41 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT16" t="n">
         <v>6.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA16" t="n">
         <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H17" t="n">
         <v>5.3</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U17" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4730,7 +4730,7 @@
         <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
         <v>970</v>
@@ -4766,37 +4766,37 @@
         <v>25</v>
       </c>
       <c r="AM17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AP17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR17" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
         <v>7.6</v>
       </c>
-      <c r="AS17" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AT17" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX17" t="n">
         <v>11.5</v>
@@ -4805,92 +4805,92 @@
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC17" t="n">
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN17" t="n">
         <v>5</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT17" t="n">
         <v>10.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA17" t="n">
         <v>5.1</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         <v>1.89</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
         <v>5</v>
@@ -5011,7 +5011,7 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
         <v>20</v>
@@ -5032,7 +5032,7 @@
         <v>3.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR18" t="n">
         <v>3.9</v>
@@ -5119,10 +5119,10 @@
         <v>6.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5140,11 +5140,11 @@
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H19" t="n">
         <v>2.72</v>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
@@ -5199,7 +5199,7 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
@@ -5211,7 +5211,7 @@
         <v>1.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
         <v>2.6</v>
@@ -5226,13 +5226,13 @@
         <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z19" t="n">
         <v>26</v>
@@ -5310,7 +5310,7 @@
         <v>13.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
         <v>11</v>
@@ -5319,10 +5319,10 @@
         <v>3.95</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD19" t="n">
         <v>3.9</v>
@@ -5337,7 +5337,7 @@
         <v>15</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI19" t="n">
         <v>3.1</v>
@@ -5346,13 +5346,13 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="BN19" t="n">
         <v>5.9</v>
@@ -5364,13 +5364,13 @@
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT19" t="n">
         <v>6.4</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H20" t="n">
         <v>3.55</v>
@@ -5444,7 +5444,7 @@
         <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.37</v>
@@ -5480,7 +5480,7 @@
         <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X20" t="n">
         <v>15.5</v>
@@ -5510,7 +5510,7 @@
         <v>14.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>19</v>
@@ -5531,7 +5531,7 @@
         <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>60</v>
@@ -5543,10 +5543,10 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT20" t="n">
         <v>7.2</v>
@@ -5558,7 +5558,7 @@
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
         <v>11.5</v>
@@ -5570,25 +5570,25 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="BC20" t="n">
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
         <v>14</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH20" t="n">
         <v>3.45</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>990</v>
       </c>
       <c r="J21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>3.9</v>
       </c>
       <c r="H22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I22" t="n">
         <v>2.4</v>
@@ -5955,37 +5955,37 @@
         <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
         <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T22" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W22" t="n">
         <v>1.35</v>
@@ -6099,10 +6099,10 @@
         <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.4</v>
@@ -6117,7 +6117,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO22" t="n">
         <v>5.1</v>
@@ -6126,13 +6126,13 @@
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT22" t="n">
         <v>5.5</v>
@@ -6141,7 +6141,7 @@
         <v>4</v>
       </c>
       <c r="BV22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW22" t="n">
         <v>6.2</v>
@@ -6153,14 +6153,14 @@
         <v>7.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
         <v>2.76</v>
@@ -6200,10 +6200,10 @@
         <v>2.58</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
         <v>4.1</v>
@@ -6218,16 +6218,16 @@
         <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
         <v>3.1</v>
@@ -6236,13 +6236,13 @@
         <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
         <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X23" t="n">
         <v>20</v>
@@ -6257,16 +6257,16 @@
         <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" t="n">
         <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF23" t="n">
         <v>22</v>
@@ -6281,7 +6281,7 @@
         <v>40</v>
       </c>
       <c r="AJ23" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK23" t="n">
         <v>30</v>
@@ -6293,10 +6293,10 @@
         <v>100</v>
       </c>
       <c r="AN23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP23" t="n">
         <v>14</v>
@@ -6308,7 +6308,7 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
@@ -6323,7 +6323,7 @@
         <v>21</v>
       </c>
       <c r="AX23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -6332,19 +6332,19 @@
         <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF23" t="n">
         <v>16</v>
@@ -6356,7 +6356,7 @@
         <v>3.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.6</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -6472,13 +6472,13 @@
         <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
         <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R24" t="n">
         <v>1.38</v>
@@ -6508,7 +6508,7 @@
         <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB24" t="n">
         <v>15.5</v>
@@ -6532,7 +6532,7 @@
         <v>17</v>
       </c>
       <c r="AI24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ24" t="n">
         <v>60</v>
@@ -6544,13 +6544,13 @@
         <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN24" t="n">
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
         <v>13.5</v>
@@ -6562,7 +6562,7 @@
         <v>15</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -6574,7 +6574,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
@@ -6586,25 +6586,25 @@
         <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG24" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>2.86</v>
       </c>
       <c r="G25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I25" t="n">
         <v>2.7</v>
@@ -6723,7 +6723,7 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>1.35</v>
@@ -6738,7 +6738,7 @@
         <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
         <v>1.78</v>
@@ -6750,7 +6750,7 @@
         <v>1.58</v>
       </c>
       <c r="W25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X25" t="n">
         <v>13.5</v>
@@ -6759,10 +6759,10 @@
         <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB25" t="n">
         <v>11.5</v>
@@ -6795,7 +6795,7 @@
         <v>36</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM25" t="n">
         <v>120</v>
@@ -6816,7 +6816,7 @@
         <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
         <v>10</v>
@@ -6828,10 +6828,10 @@
         <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AY25" t="n">
         <v>11.5</v>
@@ -6840,22 +6840,22 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE25" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC25" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BG25" t="n">
         <v>19</v>
@@ -6864,19 +6864,19 @@
         <v>3.3</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ25" t="n">
         <v>9.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN25" t="n">
         <v>6</v>
@@ -6888,25 +6888,25 @@
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU25" t="n">
         <v>4.3</v>
       </c>
       <c r="BV25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -6953,25 +6953,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I26" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
         <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
@@ -6989,22 +6989,22 @@
         <v>1.59</v>
       </c>
       <c r="R26" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
         <v>2.48</v>
       </c>
       <c r="T26" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W26" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="X26" t="n">
         <v>950</v>
@@ -7016,7 +7016,7 @@
         <v>44</v>
       </c>
       <c r="AA26" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB26" t="n">
         <v>12</v>
@@ -7031,7 +7031,7 @@
         <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG26" t="n">
         <v>10.5</v>
@@ -7046,7 +7046,7 @@
         <v>970</v>
       </c>
       <c r="AK26" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AL26" t="n">
         <v>28</v>
@@ -7055,34 +7055,34 @@
         <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO26" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
         <v>10.5</v>
       </c>
       <c r="AU26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW26" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>10</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -7091,7 +7091,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
         <v>38</v>
@@ -7103,70 +7103,70 @@
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG26" t="n">
         <v>34</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN26" t="n">
         <v>4.7</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP26" t="n">
         <v>11</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT26" t="n">
         <v>8.6</v>
       </c>
-      <c r="BT26" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU26" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H27" t="n">
         <v>3.95</v>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L27" t="n">
         <v>1.27</v>
@@ -7258,7 +7258,7 @@
         <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X27" t="n">
         <v>26</v>
@@ -7282,7 +7282,7 @@
         <v>19.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF27" t="n">
         <v>16</v>
@@ -7312,7 +7312,7 @@
         <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP27" t="n">
         <v>16.5</v>
@@ -7321,10 +7321,10 @@
         <v>15</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
         <v>9.4</v>
@@ -7348,7 +7348,7 @@
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB27" t="n">
         <v>16.5</v>
@@ -7360,7 +7360,7 @@
         <v>21</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF27" t="n">
         <v>7.4</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H28" t="n">
         <v>2.34</v>
       </c>
       <c r="I28" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J28" t="n">
         <v>3.15</v>
@@ -7479,7 +7479,7 @@
         <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
@@ -7488,7 +7488,7 @@
         <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
         <v>1.74</v>
@@ -7503,16 +7503,16 @@
         <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
         <v>970</v>
@@ -7539,7 +7539,7 @@
         <v>32</v>
       </c>
       <c r="AF28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG28" t="n">
         <v>970</v>
@@ -7551,10 +7551,10 @@
         <v>50</v>
       </c>
       <c r="AJ28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL28" t="n">
         <v>65</v>
@@ -7563,64 +7563,64 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO28" t="n">
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW28" t="n">
         <v>3.15</v>
       </c>
-      <c r="AS28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AX28" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="BB28" t="n">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="BH28" t="n">
         <v>3.25</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
@@ -7680,11 +7680,11 @@
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
         <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.41</v>
@@ -7739,7 +7739,7 @@
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
         <v>1.42</v>
@@ -7751,7 +7751,7 @@
         <v>2.28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
         <v>4.3</v>
@@ -7823,94 +7823,94 @@
         <v>55</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ29" t="n">
         <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT29" t="n">
         <v>7</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
         <v>10.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY29" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>14</v>
+        <v>5.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BG29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH29" t="n">
         <v>3.1</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ29" t="n">
         <v>11</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN29" t="n">
         <v>5.7</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT29" t="n">
         <v>6.4</v>
@@ -7922,23 +7922,23 @@
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
         <v>8</v>
       </c>
-      <c r="BZ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -7972,19 +7972,19 @@
         <v>1.63</v>
       </c>
       <c r="G30" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
         <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L30" t="n">
         <v>1.3</v>
@@ -8020,7 +8020,7 @@
         <v>1.17</v>
       </c>
       <c r="W30" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
         <v>950</v>
@@ -8029,10 +8029,10 @@
         <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB30" t="n">
         <v>11</v>
@@ -8044,7 +8044,7 @@
         <v>950</v>
       </c>
       <c r="AE30" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -8056,7 +8056,7 @@
         <v>950</v>
       </c>
       <c r="AI30" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="n">
         <v>21</v>
@@ -8065,7 +8065,7 @@
         <v>21</v>
       </c>
       <c r="AL30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM30" t="n">
         <v>130</v>
@@ -8074,19 +8074,19 @@
         <v>11.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP30" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT30" t="n">
         <v>6.8</v>
@@ -8095,10 +8095,10 @@
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AW30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
         <v>7.8</v>
@@ -8107,28 +8107,28 @@
         <v>7.4</v>
       </c>
       <c r="AZ30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB30" t="n">
         <v>3.65</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>3.55</v>
       </c>
       <c r="BC30" t="n">
         <v>12.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF30" t="n">
         <v>7</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH30" t="n">
         <v>3.8</v>
@@ -8146,7 +8146,7 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="BN30" t="n">
         <v>4.5</v>
@@ -8176,13 +8176,13 @@
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -8223,103 +8223,103 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I31" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="J31" t="n">
         <v>3.9</v>
       </c>
       <c r="K31" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>2.04</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.31</v>
       </c>
-      <c r="P31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V31" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="W31" t="n">
         <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
         <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -8328,125 +8328,125 @@
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BI31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
         <v>2.62</v>
       </c>
-      <c r="BJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BX31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BZ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA31" t="n">
-        <v>1.34</v>
-      </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
         <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -8994,10 +8994,10 @@
         <v>3.45</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -9030,13 +9030,13 @@
         <v>1.98</v>
       </c>
       <c r="U34" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="X34" t="n">
         <v>11.5</v>
@@ -9117,7 +9117,7 @@
         <v>4.8</v>
       </c>
       <c r="AX34" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AY34" t="n">
         <v>9</v>
@@ -9132,16 +9132,16 @@
         <v>4.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD34" t="n">
         <v>4.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="BG34" t="n">
         <v>4.9</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
         <v>1.02</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -9499,10 +9499,10 @@
         <v>2.2</v>
       </c>
       <c r="H36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I36" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>3.1</v>
@@ -9529,7 +9529,7 @@
         <v>2.54</v>
       </c>
       <c r="R36" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
         <v>5.1</v>
@@ -9541,10 +9541,10 @@
         <v>1.75</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W36" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X36" t="n">
         <v>10.5</v>
@@ -9556,7 +9556,7 @@
         <v>34</v>
       </c>
       <c r="AA36" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB36" t="n">
         <v>7.2</v>
@@ -9580,7 +9580,7 @@
         <v>25</v>
       </c>
       <c r="AI36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ36" t="n">
         <v>29</v>
@@ -9592,13 +9592,13 @@
         <v>60</v>
       </c>
       <c r="AM36" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN36" t="n">
         <v>28</v>
       </c>
       <c r="AO36" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP36" t="n">
         <v>8</v>
@@ -9622,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX36" t="n">
         <v>10</v>
@@ -9634,7 +9634,7 @@
         <v>20</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB36" t="n">
         <v>6.4</v>
@@ -9643,7 +9643,7 @@
         <v>6.6</v>
       </c>
       <c r="BD36" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE36" t="n">
         <v>8</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -9747,19 +9747,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="G37" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H37" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I37" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K37" t="n">
         <v>3.5</v>
@@ -9780,7 +9780,7 @@
         <v>1.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
         <v>1.31</v>
@@ -9795,7 +9795,7 @@
         <v>2.08</v>
       </c>
       <c r="V37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W37" t="n">
         <v>1.52</v>
@@ -9837,7 +9837,7 @@
         <v>48</v>
       </c>
       <c r="AJ37" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK37" t="n">
         <v>34</v>
@@ -9849,7 +9849,7 @@
         <v>120</v>
       </c>
       <c r="AN37" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO37" t="n">
         <v>32</v>
@@ -9861,10 +9861,10 @@
         <v>9.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT37" t="n">
         <v>9.199999999999999</v>
@@ -9876,7 +9876,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX37" t="n">
         <v>15.5</v>
@@ -9888,25 +9888,25 @@
         <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC37" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD37" t="n">
         <v>32</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH37" t="n">
         <v>3.4</v>
@@ -9918,59 +9918,59 @@
         <v>10</v>
       </c>
       <c r="BK37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN37" t="n">
         <v>6</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP37" t="n">
         <v>23</v>
       </c>
       <c r="BQ37" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR37" t="n">
         <v>38</v>
       </c>
       <c r="BS37" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT37" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU37" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BV37" t="n">
         <v>23</v>
       </c>
       <c r="BW37" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX37" t="n">
         <v>38</v>
       </c>
       <c r="BY37" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ37" t="n">
         <v>32</v>
       </c>
       <c r="CA37" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -10001,31 +10001,31 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H38" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I38" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J38" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K38" t="n">
         <v>3.7</v>
       </c>
       <c r="L38" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="O38" t="n">
         <v>1.44</v>
@@ -10034,197 +10034,197 @@
         <v>1.62</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T38" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V38" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W38" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -10258,19 +10258,19 @@
         <v>1.84</v>
       </c>
       <c r="G39" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H39" t="n">
         <v>4.9</v>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L39" t="n">
         <v>1.46</v>
@@ -10294,7 +10294,7 @@
         <v>1.19</v>
       </c>
       <c r="S39" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="T39" t="n">
         <v>2.18</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G40" t="n">
         <v>2.36</v>
@@ -10518,7 +10518,7 @@
         <v>3.2</v>
       </c>
       <c r="I40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
         <v>2.94</v>
@@ -10527,37 +10527,37 @@
         <v>3.8</v>
       </c>
       <c r="L40" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M40" t="n">
         <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O40" t="n">
         <v>1.35</v>
       </c>
       <c r="P40" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="R40" t="n">
         <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U40" t="n">
         <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
         <v>1.73</v>
@@ -10566,28 +10566,28 @@
         <v>15.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA40" t="n">
         <v>90</v>
       </c>
       <c r="AB40" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC40" t="n">
         <v>9.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE40" t="n">
         <v>60</v>
       </c>
       <c r="AF40" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG40" t="n">
         <v>13.5</v>
@@ -10599,16 +10599,16 @@
         <v>70</v>
       </c>
       <c r="AJ40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK40" t="n">
         <v>32</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>27</v>
       </c>
       <c r="AL40" t="n">
         <v>50</v>
       </c>
       <c r="AM40" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN40" t="n">
         <v>25</v>
@@ -10620,13 +10620,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT40" t="n">
         <v>6.8</v>
@@ -10635,10 +10635,10 @@
         <v>5.9</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="AX40" t="n">
         <v>10</v>
@@ -10650,37 +10650,37 @@
         <v>13.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BD40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BH40" t="n">
         <v>3.35</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ40" t="n">
         <v>10.5</v>
       </c>
       <c r="BK40" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
@@ -10692,7 +10692,7 @@
         <v>5.2</v>
       </c>
       <c r="BO40" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP40" t="n">
         <v>1000</v>
@@ -10710,7 +10710,7 @@
         <v>7.2</v>
       </c>
       <c r="BU40" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G41" t="n">
         <v>1.46</v>
@@ -10808,22 +10808,22 @@
         <v>2.46</v>
       </c>
       <c r="U41" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V41" t="n">
         <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y41" t="n">
         <v>29</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
@@ -10832,37 +10832,37 @@
         <v>6.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AF41" t="n">
         <v>7.2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="n">
         <v>9.4</v>
@@ -10874,37 +10874,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.68</v>
+        <v>21</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.78</v>
+        <v>6.4</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.78</v>
+        <v>6.8</v>
       </c>
       <c r="AT41" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AU41" t="n">
         <v>8.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.78</v>
+        <v>6</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.78</v>
+        <v>6.6</v>
       </c>
       <c r="AX41" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="AY41" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.78</v>
+        <v>5.9</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.78</v>
+        <v>6.6</v>
       </c>
       <c r="BB41" t="n">
         <v>8.6</v>
@@ -10913,16 +10913,16 @@
         <v>14</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.78</v>
+        <v>6.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.78</v>
+        <v>6.6</v>
       </c>
       <c r="BF41" t="n">
         <v>7</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.78</v>
+        <v>6.8</v>
       </c>
       <c r="BH41" t="n">
         <v>3.35</v>
@@ -10946,7 +10946,7 @@
         <v>3.6</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="BP41" t="n">
         <v>9.199999999999999</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -866,7 +866,7 @@
         <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -887,10 +887,10 @@
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
@@ -905,7 +905,7 @@
         <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.25</v>
@@ -917,13 +917,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
         <v>32</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -935,7 +935,7 @@
         <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG2" t="n">
         <v>22</v>
@@ -968,16 +968,16 @@
         <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
         <v>5.9</v>
@@ -992,28 +992,28 @@
         <v>4.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF2" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5</v>
       </c>
       <c r="BG2" t="n">
         <v>18.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
         <v>1.96</v>
@@ -1234,7 +1234,7 @@
         <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="AV3" t="n">
         <v>4.4</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1488,7 +1488,7 @@
         <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
         <v>7.8</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
@@ -1652,13 +1652,13 @@
         <v>2.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
         <v>1.6</v>
@@ -1667,10 +1667,10 @@
         <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1727,64 +1727,64 @@
         <v>44</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY5" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC5" t="n">
         <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.64</v>
+        <v>3.55</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>970</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G6" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I6" t="n">
         <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
         <v>6.4</v>
@@ -1903,10 +1903,10 @@
         <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R6" t="n">
         <v>1.66</v>
@@ -1915,7 +1915,7 @@
         <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1924,43 +1924,43 @@
         <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="X6" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y6" t="n">
         <v>44</v>
       </c>
-      <c r="Y6" t="n">
-        <v>48</v>
-      </c>
       <c r="Z6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD6" t="n">
         <v>38</v>
       </c>
       <c r="AE6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
         <v>16</v>
@@ -1969,79 +1969,79 @@
         <v>17</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH6" t="n">
         <v>5.1</v>
       </c>
-      <c r="AO6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI6" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,25 +2053,25 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
@@ -2089,14 +2089,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I7" t="n">
         <v>2.38</v>
@@ -2142,7 +2142,7 @@
         <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.26</v>
@@ -2166,13 +2166,13 @@
         <v>1.59</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
         <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V7" t="n">
         <v>1.72</v>
@@ -2187,7 +2187,7 @@
         <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
         <v>36</v>
@@ -2259,7 +2259,7 @@
         <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY7" t="n">
         <v>12</v>
@@ -2271,16 +2271,16 @@
         <v>21</v>
       </c>
       <c r="BB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
         <v>16.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -2381,55 +2381,55 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.18</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="O8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S8" t="n">
         <v>1.96</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.88</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
         <v>2.2</v>
@@ -2441,13 +2441,13 @@
         <v>32</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="n">
         <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
         <v>970</v>
@@ -2456,7 +2456,7 @@
         <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
@@ -2471,10 +2471,10 @@
         <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL8" t="n">
         <v>28</v>
@@ -2483,128 +2483,128 @@
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AO8" t="n">
         <v>27</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -2638,227 +2638,227 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
         <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.56</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.51</v>
-      </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
         <v>42</v>
       </c>
       <c r="AB9" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
         <v>17</v>
       </c>
-      <c r="AO9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
         <v>1.73</v>
@@ -3000,7 +3000,7 @@
         <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
         <v>19</v>
@@ -3054,7 +3054,7 @@
         <v>3.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
         <v>5.5</v>
@@ -3081,7 +3081,7 @@
         <v>6.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS10" t="n">
         <v>7.6</v>
@@ -3096,7 +3096,7 @@
         <v>27</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>36</v>
@@ -3108,11 +3108,11 @@
         <v>23</v>
       </c>
       <c r="CA10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -3143,85 +3143,85 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V11" t="n">
         <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA11" t="n">
         <v>200</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -3230,143 +3230,143 @@
         <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK11" t="n">
         <v>18.5</v>
       </c>
-      <c r="AK11" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.82</v>
+        <v>1.82</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="CA11" t="n">
         <v>5.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -3418,7 +3418,7 @@
         <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
         <v>4.1</v>
@@ -3427,7 +3427,7 @@
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
         <v>1.6</v>
@@ -3436,19 +3436,19 @@
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U12" t="n">
         <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
         <v>26</v>
@@ -3457,10 +3457,10 @@
         <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
@@ -3469,94 +3469,94 @@
         <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
         <v>970</v>
       </c>
       <c r="AI12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
         <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="n">
         <v>4.4</v>
@@ -3568,7 +3568,7 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,10 +3577,10 @@
         <v>1.98</v>
       </c>
       <c r="BN12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
@@ -3592,25 +3592,25 @@
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>6.8</v>
       </c>
-      <c r="BU12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.45</v>
@@ -3675,10 +3675,10 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
         <v>1.67</v>
@@ -3687,22 +3687,22 @@
         <v>2.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -3711,13 +3711,13 @@
         <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
         <v>8</v>
@@ -3726,13 +3726,13 @@
         <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH13" t="n">
         <v>20</v>
@@ -3741,25 +3741,25 @@
         <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
         <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.2</v>
@@ -3768,10 +3768,10 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>5.6</v>
@@ -3780,37 +3780,37 @@
         <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AX13" t="n">
         <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB13" t="n">
         <v>34</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="n">
         <v>3.2</v>
@@ -3831,40 +3831,40 @@
         <v>8.4</v>
       </c>
       <c r="BN13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BO13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BX13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13" t="n">
         <v>38</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H14" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I14" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
         <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -4004,31 +4004,31 @@
         <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO14" t="n">
         <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
         <v>8.6</v>
@@ -4046,19 +4046,19 @@
         <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD14" t="n">
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
         <v>34</v>
@@ -4067,10 +4067,10 @@
         <v>16</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4085,10 +4085,10 @@
         <v>9.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4103,10 +4103,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
@@ -4115,20 +4115,20 @@
         <v>6.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H15" t="n">
         <v>3.75</v>
@@ -4171,7 +4171,7 @@
         <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
         <v>4.7</v>
@@ -4195,7 +4195,7 @@
         <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
         <v>2.5</v>
@@ -4207,10 +4207,10 @@
         <v>2.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4273,22 +4273,22 @@
         <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
@@ -4300,7 +4300,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
         <v>16.5</v>
@@ -4309,16 +4309,16 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF15" t="n">
         <v>7</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="n">
         <v>4.3</v>
@@ -4327,16 +4327,16 @@
         <v>3.3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BN15" t="n">
         <v>5.1</v>
@@ -4348,16 +4348,16 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
         <v>5.8</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>1.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H16" t="n">
         <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
         <v>5.3</v>
@@ -4446,16 +4446,16 @@
         <v>2.5</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.6</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.59</v>
-      </c>
       <c r="S16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U16" t="n">
         <v>2.14</v>
@@ -4464,7 +4464,7 @@
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X16" t="n">
         <v>29</v>
@@ -4554,7 +4554,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB16" t="n">
         <v>11.5</v>
@@ -4563,7 +4563,7 @@
         <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE16" t="n">
         <v>7.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
@@ -4679,25 +4679,25 @@
         <v>3.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
         <v>1.8</v>
@@ -4712,13 +4712,13 @@
         <v>1.66</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X17" t="n">
         <v>21</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.64</v>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H18" t="n">
         <v>2.52</v>
@@ -4948,25 +4948,25 @@
         <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q18" t="n">
         <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V18" t="n">
         <v>1.61</v>
@@ -5038,7 +5038,7 @@
         <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT18" t="n">
         <v>13</v>
@@ -5074,7 +5074,7 @@
         <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
         <v>12</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
         <v>3.05</v>
@@ -5199,7 +5199,7 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
         <v>1.13</v>
@@ -5211,10 +5211,10 @@
         <v>1.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S19" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T19" t="n">
         <v>1.41</v>
@@ -5223,10 +5223,10 @@
         <v>2.96</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5238,31 +5238,31 @@
         <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB19" t="n">
         <v>950</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
         <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF19" t="n">
         <v>28</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ19" t="n">
         <v>42</v>
@@ -5271,10 +5271,10 @@
         <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN19" t="n">
         <v>12</v>
@@ -5289,10 +5289,10 @@
         <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AT19" t="n">
         <v>15</v>
@@ -5310,31 +5310,31 @@
         <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB19" t="n">
         <v>3.85</v>
       </c>
       <c r="BC19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BF19" t="n">
         <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19" t="n">
         <v>5.5</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN19" t="n">
         <v>6.6</v>
@@ -5364,13 +5364,13 @@
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT19" t="n">
         <v>7</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA19" t="n">
         <v>5.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -5429,73 +5429,73 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
         <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="R20" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X20" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Y20" t="n">
         <v>26</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
         <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AC20" t="n">
         <v>12.5</v>
@@ -5507,7 +5507,7 @@
         <v>44</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
         <v>13.5</v>
@@ -5537,16 +5537,16 @@
         <v>30</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ20" t="n">
         <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AT20" t="n">
         <v>12</v>
@@ -5558,7 +5558,7 @@
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX20" t="n">
         <v>13.5</v>
@@ -5570,7 +5570,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
         <v>17</v>
@@ -5579,10 +5579,10 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
         <v>6.6</v>
@@ -5591,10 +5591,10 @@
         <v>18.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ20" t="n">
         <v>8.6</v>
@@ -5609,19 +5609,19 @@
         <v>12</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ20" t="n">
         <v>6.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS20" t="n">
         <v>8.6</v>
@@ -5633,26 +5633,26 @@
         <v>5.7</v>
       </c>
       <c r="BV20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW20" t="n">
         <v>9.4</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H21" t="n">
         <v>2.14</v>
@@ -5707,46 +5707,46 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
         <v>1.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
         <v>1.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
         <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB21" t="n">
         <v>19.5</v>
@@ -5764,13 +5764,13 @@
         <v>32</v>
       </c>
       <c r="AG21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH21" t="n">
         <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="n">
         <v>70</v>
@@ -5791,7 +5791,7 @@
         <v>16.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
         <v>9</v>
@@ -5824,10 +5824,10 @@
         <v>11.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC21" t="n">
         <v>3.85</v>
@@ -5845,16 +5845,16 @@
         <v>10</v>
       </c>
       <c r="BH21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI21" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5863,7 +5863,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO21" t="n">
         <v>5.1</v>
@@ -5884,7 +5884,7 @@
         <v>5.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV21" t="n">
         <v>16</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
         <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T22" t="n">
         <v>1.63</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G23" t="n">
         <v>1.61</v>
@@ -6206,7 +6206,7 @@
         <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -6233,10 +6233,10 @@
         <v>2.08</v>
       </c>
       <c r="T23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U23" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V23" t="n">
         <v>1.17</v>
@@ -6332,7 +6332,7 @@
         <v>5.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BB23" t="n">
         <v>13</v>
@@ -6344,13 +6344,13 @@
         <v>6</v>
       </c>
       <c r="BE23" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BF23" t="n">
         <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BH23" t="n">
         <v>5.3</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G24" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H24" t="n">
         <v>4.2</v>
@@ -6460,7 +6460,7 @@
         <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.22</v>
@@ -6490,13 +6490,13 @@
         <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X24" t="n">
         <v>950</v>
@@ -6505,7 +6505,7 @@
         <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA24" t="n">
         <v>110</v>
@@ -6514,55 +6514,55 @@
         <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
         <v>950</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF24" t="n">
         <v>970</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
         <v>19</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AM24" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN24" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>17.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
@@ -6574,7 +6574,7 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
         <v>10.5</v>
@@ -6586,7 +6586,7 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
         <v>14.5</v>
@@ -6595,19 +6595,19 @@
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF24" t="n">
         <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI24" t="n">
         <v>3.6</v>
@@ -6634,7 +6634,7 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
@@ -6658,17 +6658,17 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G25" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I25" t="n">
         <v>3.4</v>
@@ -6714,10 +6714,10 @@
         <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -6732,7 +6732,7 @@
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R25" t="n">
         <v>1.48</v>
@@ -6747,10 +6747,10 @@
         <v>2.38</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X25" t="n">
         <v>950</v>
@@ -6813,7 +6813,7 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="AS25" t="n">
         <v>4.4</v>
@@ -6828,16 +6828,16 @@
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX25" t="n">
         <v>13.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="BA25" t="n">
         <v>4.3</v>
@@ -6852,34 +6852,34 @@
         <v>4.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF25" t="n">
         <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="BH25" t="n">
         <v>4</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
         <v>5</v>
       </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>10</v>
-      </c>
       <c r="BN25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO25" t="n">
         <v>4.2</v>
@@ -6888,16 +6888,16 @@
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU25" t="n">
         <v>4.9</v>
@@ -6906,23 +6906,23 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="I26" t="n">
-        <v>110</v>
+        <v>2.18</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -6977,10 +6977,10 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P26" t="n">
         <v>1.24</v>
@@ -6992,7 +6992,7 @@
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G27" t="n">
         <v>110</v>
@@ -7216,7 +7216,7 @@
         <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="J27" t="n">
         <v>1.03</v>
@@ -7234,7 +7234,7 @@
         <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P27" t="n">
         <v>1.24</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J28" t="n">
         <v>3.55</v>
       </c>
-      <c r="I28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>1.41</v>
@@ -7497,7 +7497,7 @@
         <v>1.98</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
         <v>3.5</v>
@@ -7509,10 +7509,10 @@
         <v>2.06</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="X28" t="n">
         <v>15.5</v>
@@ -7527,7 +7527,7 @@
         <v>80</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC28" t="n">
         <v>8.4</v>
@@ -7554,10 +7554,10 @@
         <v>30</v>
       </c>
       <c r="AK28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL28" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM28" t="n">
         <v>120</v>
@@ -7569,28 +7569,28 @@
         <v>60</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT28" t="n">
         <v>7.2</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
@@ -7602,61 +7602,61 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC28" t="n">
         <v>18.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF28" t="n">
         <v>14</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ28" t="n">
         <v>10.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN28" t="n">
         <v>5.2</v>
       </c>
       <c r="BO28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP28" t="n">
         <v>17</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT28" t="n">
         <v>7.2</v>
@@ -7668,23 +7668,23 @@
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H29" t="n">
         <v>2.56</v>
       </c>
       <c r="I29" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.24</v>
@@ -7739,7 +7739,7 @@
         <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O29" t="n">
         <v>1.17</v>
@@ -7748,31 +7748,31 @@
         <v>2.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R29" t="n">
         <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T29" t="n">
         <v>1.5</v>
       </c>
       <c r="U29" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X29" t="n">
         <v>950</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="n">
         <v>26</v>
@@ -7781,7 +7781,7 @@
         <v>46</v>
       </c>
       <c r="AB29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC29" t="n">
         <v>12</v>
@@ -7802,7 +7802,7 @@
         <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ29" t="n">
         <v>42</v>
@@ -7868,16 +7868,16 @@
         <v>4.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF29" t="n">
         <v>10</v>
       </c>
       <c r="BG29" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI29" t="n">
         <v>3.65</v>
@@ -7886,16 +7886,16 @@
         <v>8.6</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO29" t="n">
         <v>4.8</v>
@@ -7904,13 +7904,13 @@
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT29" t="n">
         <v>6.4</v>
@@ -7919,26 +7919,26 @@
         <v>4.9</v>
       </c>
       <c r="BV29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
         <v>7</v>
       </c>
-      <c r="BX29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>990</v>
       </c>
       <c r="H30" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="I30" t="n">
         <v>990</v>
@@ -7996,13 +7996,13 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R30" t="n">
         <v>1.12</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -8223,82 +8223,82 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G31" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="H31" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P31" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T31" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="X31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y31" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z31" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA31" t="n">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="AB31" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC31" t="n">
         <v>14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE31" t="n">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="AF31" t="n">
         <v>8.6</v>
@@ -8310,7 +8310,7 @@
         <v>34</v>
       </c>
       <c r="AI31" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -8322,121 +8322,121 @@
         <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN31" t="n">
         <v>6.6</v>
       </c>
       <c r="AO31" t="n">
-        <v>260</v>
+        <v>370</v>
       </c>
       <c r="AP31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB31" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU31" t="n">
+      <c r="BC31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BN31" t="n">
         <v>3.75</v>
       </c>
-      <c r="AV31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF31" t="n">
+      <c r="BO31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
         <v>2.9</v>
       </c>
-      <c r="BG31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.8</v>
+        <v>2.88</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR33" t="n">
         <v>16</v>
@@ -8854,10 +8854,10 @@
         <v>8</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
         <v>6.4</v>
@@ -8896,7 +8896,7 @@
         <v>3.7</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
         <v>1.09</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="R34" t="n">
         <v>1.09</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>110</v>
+        <v>620</v>
       </c>
       <c r="J35" t="n">
         <v>1.03</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H37" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I37" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>3.5</v>
@@ -9765,7 +9765,7 @@
         <v>3.65</v>
       </c>
       <c r="L37" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M37" t="n">
         <v>1.06</v>
@@ -9774,10 +9774,10 @@
         <v>3.9</v>
       </c>
       <c r="O37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q37" t="n">
         <v>1.89</v>
@@ -9792,10 +9792,10 @@
         <v>1.71</v>
       </c>
       <c r="U37" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W37" t="n">
         <v>1.47</v>
@@ -9807,7 +9807,7 @@
         <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA37" t="n">
         <v>44</v>
@@ -9816,7 +9816,7 @@
         <v>15.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD37" t="n">
         <v>14.5</v>
@@ -9888,19 +9888,19 @@
         <v>14</v>
       </c>
       <c r="BA37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB37" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>5.6</v>
       </c>
       <c r="BC37" t="n">
         <v>5.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF37" t="n">
         <v>20</v>
@@ -9918,13 +9918,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN37" t="n">
         <v>6.2</v>
@@ -9936,16 +9936,16 @@
         <v>23</v>
       </c>
       <c r="BQ37" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR37" t="n">
         <v>34</v>
       </c>
       <c r="BS37" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT37" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU37" t="n">
         <v>4.3</v>
@@ -9954,23 +9954,23 @@
         <v>19</v>
       </c>
       <c r="BW37" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY37" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ37" t="n">
         <v>25</v>
       </c>
       <c r="CA37" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -10001,19 +10001,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G38" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I38" t="n">
         <v>2.8</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
         <v>3.45</v>
@@ -10034,10 +10034,10 @@
         <v>1.88</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
         <v>3.7</v>
@@ -10052,7 +10052,7 @@
         <v>1.55</v>
       </c>
       <c r="W38" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
         <v>13.5</v>
@@ -10079,7 +10079,7 @@
         <v>32</v>
       </c>
       <c r="AF38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG38" t="n">
         <v>13.5</v>
@@ -10106,22 +10106,22 @@
         <v>50</v>
       </c>
       <c r="AO38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP38" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR38" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS38" t="n">
         <v>34</v>
       </c>
       <c r="AT38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU38" t="n">
         <v>6.8</v>
@@ -10133,7 +10133,7 @@
         <v>19.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY38" t="n">
         <v>11.5</v>
@@ -10166,19 +10166,19 @@
         <v>3.3</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ38" t="n">
         <v>9.6</v>
       </c>
       <c r="BK38" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN38" t="n">
         <v>6</v>
@@ -10187,16 +10187,16 @@
         <v>4.5</v>
       </c>
       <c r="BP38" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BR38" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT38" t="n">
         <v>5.7</v>
@@ -10208,13 +10208,13 @@
         <v>21</v>
       </c>
       <c r="BW38" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX38" t="n">
         <v>36</v>
       </c>
       <c r="BY38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>1.63</v>
       </c>
       <c r="G39" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H39" t="n">
         <v>5</v>
@@ -10270,7 +10270,7 @@
         <v>4.4</v>
       </c>
       <c r="K39" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L39" t="n">
         <v>1.26</v>
@@ -10306,7 +10306,7 @@
         <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X39" t="n">
         <v>950</v>
@@ -10333,7 +10333,7 @@
         <v>60</v>
       </c>
       <c r="AF39" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG39" t="n">
         <v>10.5</v>
@@ -10348,7 +10348,7 @@
         <v>970</v>
       </c>
       <c r="AK39" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AL39" t="n">
         <v>28</v>
@@ -10357,22 +10357,22 @@
         <v>75</v>
       </c>
       <c r="AN39" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO39" t="n">
         <v>50</v>
       </c>
       <c r="AP39" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ39" t="n">
         <v>17.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AS39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT39" t="n">
         <v>10.5</v>
@@ -10381,10 +10381,10 @@
         <v>8.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AW39" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AX39" t="n">
         <v>9.4</v>
@@ -10393,7 +10393,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ39" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA39" t="n">
         <v>38</v>
@@ -10405,13 +10405,13 @@
         <v>14</v>
       </c>
       <c r="BD39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE39" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG39" t="n">
         <v>34</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
         <v>1.64</v>
       </c>
       <c r="U40" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V40" t="n">
         <v>1.31</v>
@@ -10638,7 +10638,7 @@
         <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX40" t="n">
         <v>12</v>
@@ -10650,7 +10650,7 @@
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB40" t="n">
         <v>16.5</v>
@@ -10668,7 +10668,7 @@
         <v>8.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH40" t="n">
         <v>4.3</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G41" t="n">
         <v>2.98</v>
       </c>
       <c r="H41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I41" t="n">
         <v>3.6</v>
@@ -10778,7 +10778,7 @@
         <v>2.76</v>
       </c>
       <c r="K41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.48</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -11274,22 +11274,22 @@
         <v>3.15</v>
       </c>
       <c r="G43" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H43" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J43" t="n">
         <v>3.25</v>
       </c>
       <c r="K43" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
@@ -11319,10 +11319,10 @@
         <v>2.04</v>
       </c>
       <c r="V43" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W43" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X43" t="n">
         <v>970</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J44" t="n">
         <v>1.03</v>
@@ -11549,13 +11549,13 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.28</v>
+        <v>3.35</v>
       </c>
       <c r="O44" t="n">
         <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q44" t="n">
         <v>1.33</v>
@@ -11564,7 +11564,7 @@
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11788,7 @@
         <v>1.56</v>
       </c>
       <c r="I45" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J45" t="n">
         <v>3.9</v>
@@ -11797,7 +11797,7 @@
         <v>4.7</v>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M45" t="n">
         <v>1.07</v>
@@ -11884,7 +11884,7 @@
         <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP45" t="n">
         <v>10.5</v>
@@ -11899,7 +11899,7 @@
         <v>10.5</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU45" t="n">
         <v>7</v>
@@ -11911,28 +11911,28 @@
         <v>13</v>
       </c>
       <c r="AX45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA45" t="n">
         <v>4</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>3.95</v>
       </c>
       <c r="BB45" t="n">
         <v>4.2</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF45" t="n">
         <v>4.2</v>
@@ -11944,7 +11944,7 @@
         <v>3.5</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -12287,16 +12287,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G47" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H47" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J47" t="n">
         <v>3.35</v>
@@ -12305,7 +12305,7 @@
         <v>3.6</v>
       </c>
       <c r="L47" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -12544,16 +12544,16 @@
         <v>2.3</v>
       </c>
       <c r="G48" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="H48" t="n">
         <v>3.45</v>
       </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K48" t="n">
         <v>3.4</v>
@@ -12589,7 +12589,7 @@
         <v>1.87</v>
       </c>
       <c r="V48" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W48" t="n">
         <v>1.64</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G49" t="n">
         <v>990</v>
       </c>
       <c r="H49" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I49" t="n">
         <v>990</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
         <v>2.9</v>
       </c>
       <c r="H51" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I51" t="n">
         <v>2.94</v>
@@ -13333,7 +13333,7 @@
         <v>1.36</v>
       </c>
       <c r="P51" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q51" t="n">
         <v>2.04</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
         <v>1.98</v>
       </c>
       <c r="G52" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H52" t="n">
         <v>4.1</v>
@@ -13572,7 +13572,7 @@
         <v>3.15</v>
       </c>
       <c r="K52" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L52" t="n">
         <v>1.44</v>
@@ -13608,7 +13608,7 @@
         <v>1.26</v>
       </c>
       <c r="W52" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X52" t="n">
         <v>11.5</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -13841,25 +13841,25 @@
         <v>1.49</v>
       </c>
       <c r="P53" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R53" t="n">
         <v>1.2</v>
       </c>
       <c r="S53" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="T53" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U53" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V53" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W53" t="n">
         <v>1.96</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -14065,22 +14065,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G54" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H54" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I54" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L54" t="n">
         <v>1.43</v>
@@ -14104,19 +14104,19 @@
         <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T54" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U54" t="n">
         <v>2</v>
       </c>
       <c r="V54" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W54" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X54" t="n">
         <v>15.5</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -14319,67 +14319,67 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="G55" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="H55" t="n">
         <v>11</v>
       </c>
       <c r="I55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K55" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L55" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M55" t="n">
         <v>1.08</v>
       </c>
       <c r="N55" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P55" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
         <v>2.18</v>
       </c>
       <c r="R55" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S55" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T55" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="U55" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="V55" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="X55" t="n">
         <v>14.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Z55" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AA55" t="n">
         <v>1000</v>
@@ -14391,10 +14391,10 @@
         <v>13</v>
       </c>
       <c r="AD55" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AE55" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="AF55" t="n">
         <v>7.2</v>
@@ -14406,13 +14406,13 @@
         <v>46</v>
       </c>
       <c r="AI55" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AJ55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL55" t="n">
         <v>70</v>
@@ -14421,7 +14421,7 @@
         <v>380</v>
       </c>
       <c r="AN55" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO55" t="n">
         <v>1000</v>
@@ -14433,22 +14433,22 @@
         <v>21</v>
       </c>
       <c r="AR55" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS55" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT55" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU55" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV55" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW55" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX55" t="n">
         <v>5.5</v>
@@ -14457,10 +14457,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA55" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB55" t="n">
         <v>8.6</v>
@@ -14469,80 +14469,80 @@
         <v>14</v>
       </c>
       <c r="BD55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF55" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE55" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF55" t="n">
+      <c r="BG55" t="n">
         <v>7.2</v>
       </c>
-      <c r="BG55" t="n">
+      <c r="BH55" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK55" t="n">
         <v>6.8</v>
       </c>
-      <c r="BH55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI55" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ55" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK55" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW55" t="n">
         <v>11</v>
       </c>
-      <c r="BN55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BO55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BP55" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ55" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR55" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS55" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT55" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU55" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW55" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ55" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="CA55" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -860,19 +860,19 @@
         <v>4.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H2" t="n">
         <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.46</v>
@@ -887,7 +887,7 @@
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
         <v>2.38</v>
@@ -905,7 +905,7 @@
         <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W2" t="n">
         <v>1.25</v>
@@ -935,7 +935,7 @@
         <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG2" t="n">
         <v>22</v>
@@ -998,22 +998,22 @@
         <v>17.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BF2" t="n">
         <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
         <v>18.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
@@ -1162,13 +1162,13 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>60</v>
@@ -1204,7 +1204,7 @@
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
         <v>46</v>
@@ -1222,25 +1222,25 @@
         <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
@@ -1249,10 +1249,10 @@
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1261,22 +1261,22 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1416,7 +1416,7 @@
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1482,7 +1482,7 @@
         <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AT4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>1.71</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1655,7 +1655,7 @@
         <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
         <v>2.26</v>
@@ -1670,7 +1670,7 @@
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1766,7 +1766,7 @@
         <v>4.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
         <v>4.7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>1.49</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="I6" t="n">
         <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
         <v>6.4</v>
@@ -1897,28 +1897,28 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="Q6" t="n">
         <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="S6" t="n">
         <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.1</v>
@@ -1993,43 +1993,43 @@
         <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="AW6" t="n">
         <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.8</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
         <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
         <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
         <v>4.2</v>
@@ -2038,65 +2038,65 @@
         <v>5.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BN6" t="n">
         <v>4.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP6" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR6" t="n">
         <v>19.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
         <v>12</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>10.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.98</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
         <v>2.3</v>
@@ -2139,7 +2139,7 @@
         <v>2.38</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -2151,28 +2151,28 @@
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
         <v>2.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
         <v>1.59</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V7" t="n">
         <v>1.72</v>
@@ -2289,7 +2289,7 @@
         <v>11</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI7" t="n">
         <v>3.45</v>
@@ -2298,13 +2298,13 @@
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>7</v>
@@ -2316,13 +2316,13 @@
         <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT7" t="n">
         <v>5.9</v>
@@ -2334,13 +2334,13 @@
         <v>16.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX7" t="n">
         <v>25</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
         <v>3.85</v>
@@ -2405,7 +2405,7 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.13</v>
@@ -2429,10 +2429,10 @@
         <v>2.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X8" t="n">
         <v>46</v>
@@ -2531,13 +2531,13 @@
         <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.7</v>
+        <v>16.5</v>
       </c>
       <c r="BE8" t="n">
         <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
         <v>4.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="n">
         <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
@@ -2656,25 +2656,25 @@
         <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T9" t="n">
         <v>1.48</v>
@@ -2689,7 +2689,7 @@
         <v>1.56</v>
       </c>
       <c r="X9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2725,7 +2725,7 @@
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
         <v>28</v>
@@ -2743,22 +2743,22 @@
         <v>970</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
         <v>4.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV9" t="n">
         <v>4.2</v>
@@ -2767,98 +2767,98 @@
         <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC9" t="n">
         <v>5</v>
       </c>
-      <c r="BB9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
         <v>4.2</v>
       </c>
       <c r="BH9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
         <v>4.9</v>
       </c>
-      <c r="BI9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5</v>
-      </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>13</v>
+        <v>3.25</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>17.5</v>
+        <v>3.45</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
         <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
@@ -3006,7 +3006,7 @@
         <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
@@ -3030,25 +3030,25 @@
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
         <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -3143,58 +3143,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G11" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="X11" t="n">
         <v>30</v>
@@ -3251,10 +3251,10 @@
         <v>95</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.7</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.75</v>
+        <v>19.5</v>
       </c>
       <c r="AR11" t="n">
         <v>4</v>
@@ -3263,43 +3263,43 @@
         <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
         <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="BE11" t="n">
         <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.72</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
         <v>4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -3406,10 +3406,10 @@
         <v>2.88</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
         <v>4.4</v>
@@ -3421,22 +3421,22 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
         <v>1.55</v>
@@ -3445,7 +3445,7 @@
         <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
         <v>1.66</v>
@@ -3505,10 +3505,10 @@
         <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
         <v>4.3</v>
@@ -3517,25 +3517,25 @@
         <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
         <v>4.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
         <v>4.6</v>
@@ -3544,7 +3544,7 @@
         <v>4.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
         <v>4.4</v>
@@ -3553,10 +3553,10 @@
         <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.05</v>
       </c>
-      <c r="G13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -3678,10 +3678,10 @@
         <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
         <v>2.14</v>
@@ -3696,118 +3696,118 @@
         <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB13" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12</v>
       </c>
       <c r="AC13" t="n">
         <v>8</v>
       </c>
       <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG13" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15.5</v>
       </c>
       <c r="AH13" t="n">
         <v>20</v>
       </c>
       <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL13" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>60</v>
       </c>
       <c r="AM13" t="n">
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP13" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
         <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BG13" t="n">
         <v>20</v>
@@ -3831,40 +3831,40 @@
         <v>8.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>38</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>1.42</v>
@@ -4061,7 +4061,7 @@
         <v>8</v>
       </c>
       <c r="BF14" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
         <v>16</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G15" t="n">
         <v>1.96</v>
       </c>
       <c r="H15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
@@ -4174,7 +4174,7 @@
         <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.25</v>
@@ -4189,13 +4189,13 @@
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q15" t="n">
         <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
         <v>2.5</v>
@@ -4204,7 +4204,7 @@
         <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
         <v>1.32</v>
@@ -4324,19 +4324,19 @@
         <v>4.3</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="BN15" t="n">
         <v>5.1</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.24</v>
@@ -4443,16 +4443,16 @@
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T16" t="n">
         <v>1.82</v>
@@ -4509,7 +4509,7 @@
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
         <v>120</v>
@@ -4530,10 +4530,10 @@
         <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU16" t="n">
         <v>10.5</v>
@@ -4551,10 +4551,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
         <v>11.5</v>
@@ -4578,7 +4578,7 @@
         <v>4.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ16" t="n">
         <v>11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -4703,13 +4703,13 @@
         <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
         <v>2.96</v>
       </c>
       <c r="T17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
         <v>2.38</v>
@@ -4811,7 +4811,7 @@
         <v>7</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
         <v>20</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -4927,40 +4927,40 @@
         <v>2.74</v>
       </c>
       <c r="H18" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M18" t="n">
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="S18" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
         <v>1.52</v>
@@ -4969,16 +4969,16 @@
         <v>2.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.57</v>
       </c>
       <c r="X18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
         <v>26</v>
@@ -4987,10 +4987,10 @@
         <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD18" t="n">
         <v>15.5</v>
@@ -4999,7 +4999,7 @@
         <v>29</v>
       </c>
       <c r="AF18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -5035,10 +5035,10 @@
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AS18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
         <v>13</v>
@@ -5053,19 +5053,19 @@
         <v>17</v>
       </c>
       <c r="AX18" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC18" t="n">
         <v>18</v>
@@ -5074,28 +5074,28 @@
         <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
         <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ18" t="n">
         <v>8.4</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM18" t="n">
         <v>12</v>
@@ -5104,10 +5104,10 @@
         <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ18" t="n">
         <v>8</v>
@@ -5116,25 +5116,25 @@
         <v>24</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT18" t="n">
         <v>6.2</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV18" t="n">
         <v>17</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I19" t="n">
         <v>3.05</v>
@@ -5217,16 +5217,16 @@
         <v>2.02</v>
       </c>
       <c r="T19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U19" t="n">
         <v>2.96</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5253,7 +5253,7 @@
         <v>32</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
         <v>15.5</v>
@@ -5280,7 +5280,7 @@
         <v>12</v>
       </c>
       <c r="AO19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
         <v>3.85</v>
@@ -5295,10 +5295,10 @@
         <v>3.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
@@ -5307,7 +5307,7 @@
         <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>9.4</v>
@@ -5316,7 +5316,7 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB19" t="n">
         <v>3.85</v>
@@ -5325,16 +5325,16 @@
         <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="n">
         <v>5.5</v>
@@ -5343,7 +5343,7 @@
         <v>4</v>
       </c>
       <c r="BJ19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK19" t="n">
         <v>6</v>
@@ -5352,13 +5352,13 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN19" t="n">
         <v>6.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
@@ -5394,11 +5394,11 @@
         <v>12.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -5435,19 +5435,19 @@
         <v>2.04</v>
       </c>
       <c r="H20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I20" t="n">
         <v>3.95</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
@@ -5459,22 +5459,22 @@
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="U20" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V20" t="n">
         <v>1.35</v>
@@ -5516,7 +5516,7 @@
         <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
         <v>29</v>
@@ -5528,37 +5528,37 @@
         <v>27</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT20" t="n">
         <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX20" t="n">
         <v>13.5</v>
@@ -5570,7 +5570,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB20" t="n">
         <v>17</v>
@@ -5582,7 +5582,7 @@
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF20" t="n">
         <v>6.6</v>
@@ -5591,10 +5591,10 @@
         <v>18.5</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ20" t="n">
         <v>8.6</v>
@@ -5621,38 +5621,38 @@
         <v>6.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV20" t="n">
         <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
         <v>1.63</v>
       </c>
       <c r="U21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V21" t="n">
         <v>1.75</v>
@@ -5785,7 +5785,7 @@
         <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO21" t="n">
         <v>16.5</v>
@@ -5827,7 +5827,7 @@
         <v>3.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC21" t="n">
         <v>3.85</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>3.15</v>
@@ -5946,16 +5946,16 @@
         <v>2.36</v>
       </c>
       <c r="I22" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -5967,7 +5967,7 @@
         <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
         <v>1.73</v>
@@ -5976,16 +5976,16 @@
         <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T22" t="n">
         <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V22" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W22" t="n">
         <v>1.46</v>
@@ -5997,7 +5997,7 @@
         <v>16</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
         <v>38</v>
@@ -6054,7 +6054,7 @@
         <v>12.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>11</v>
@@ -6078,19 +6078,19 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF22" t="n">
         <v>16.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>1.53</v>
       </c>
       <c r="G23" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H23" t="n">
         <v>5.6</v>
@@ -6236,13 +6236,13 @@
         <v>1.58</v>
       </c>
       <c r="U23" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V23" t="n">
         <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X23" t="n">
         <v>950</v>
@@ -6269,16 +6269,16 @@
         <v>65</v>
       </c>
       <c r="AF23" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>970</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ23" t="n">
         <v>970</v>
@@ -6293,46 +6293,46 @@
         <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AO23" t="n">
         <v>50</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU23" t="n">
         <v>10.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.6</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB23" t="n">
         <v>13</v>
@@ -6341,22 +6341,22 @@
         <v>12</v>
       </c>
       <c r="BD23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE23" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="BF23" t="n">
         <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="BH23" t="n">
         <v>5.3</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.800000000000001</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>1.76</v>
       </c>
       <c r="G24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H24" t="n">
         <v>4.2</v>
@@ -6457,10 +6457,10 @@
         <v>4.9</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.22</v>
@@ -6475,7 +6475,7 @@
         <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q24" t="n">
         <v>1.5</v>
@@ -6517,7 +6517,7 @@
         <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
         <v>48</v>
@@ -6529,7 +6529,7 @@
         <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI24" t="n">
         <v>46</v>
@@ -6538,7 +6538,7 @@
         <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL24" t="n">
         <v>26</v>
@@ -6553,7 +6553,7 @@
         <v>34</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24" t="n">
         <v>17.5</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
@@ -6574,7 +6574,7 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
         <v>10.5</v>
@@ -6586,7 +6586,7 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB24" t="n">
         <v>14.5</v>
@@ -6595,19 +6595,19 @@
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
         <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI24" t="n">
         <v>3.6</v>
@@ -6634,7 +6634,7 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
@@ -6658,17 +6658,17 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -6705,19 +6705,19 @@
         <v>2.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J25" t="n">
         <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -6741,13 +6741,13 @@
         <v>2.74</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U25" t="n">
         <v>2.38</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
         <v>1.67</v>
@@ -6816,13 +6816,13 @@
         <v>4.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV25" t="n">
         <v>10</v>
@@ -6831,25 +6831,25 @@
         <v>4.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BA25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB25" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.2</v>
       </c>
       <c r="BC25" t="n">
         <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
         <v>4.6</v>
@@ -6858,7 +6858,7 @@
         <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH25" t="n">
         <v>4</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -6956,217 +6956,217 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>220</v>
+        <v>4.6</v>
       </c>
       <c r="H26" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.89</v>
       </c>
-      <c r="K26" t="n">
-        <v>950</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="W26" t="n">
         <v>1.28</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS26" t="n">
         <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AZ26" t="n">
         <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -7207,94 +7207,94 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M27" t="n">
         <v>1.08</v>
       </c>
-      <c r="G27" t="n">
-        <v>110</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I27" t="n">
-        <v>170</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K27" t="n">
-        <v>950</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N27" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.25</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ27" t="n">
         <v>1000</v>
@@ -7303,7 +7303,7 @@
         <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
@@ -7312,67 +7312,67 @@
         <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>2.06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H28" t="n">
         <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
@@ -7479,22 +7479,22 @@
         <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R28" t="n">
         <v>1.33</v>
@@ -7506,13 +7506,13 @@
         <v>1.8</v>
       </c>
       <c r="U28" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V28" t="n">
         <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X28" t="n">
         <v>15.5</v>
@@ -7542,7 +7542,7 @@
         <v>14.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>19</v>
@@ -7563,10 +7563,10 @@
         <v>120</v>
       </c>
       <c r="AN28" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP28" t="n">
         <v>10.5</v>
@@ -7575,10 +7575,10 @@
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT28" t="n">
         <v>7.2</v>
@@ -7590,7 +7590,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
@@ -7602,25 +7602,25 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB28" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>5.9</v>
       </c>
       <c r="BC28" t="n">
         <v>18.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF28" t="n">
         <v>14</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH28" t="n">
         <v>3.45</v>
@@ -7662,7 +7662,7 @@
         <v>7.2</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -7757,22 +7757,22 @@
         <v>2.24</v>
       </c>
       <c r="T29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U29" t="n">
         <v>2.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X29" t="n">
         <v>950</v>
       </c>
       <c r="Y29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="n">
         <v>26</v>
@@ -7781,7 +7781,7 @@
         <v>46</v>
       </c>
       <c r="AB29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC29" t="n">
         <v>12</v>
@@ -7844,7 +7844,7 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX29" t="n">
         <v>16</v>
@@ -7874,19 +7874,19 @@
         <v>10</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ29" t="n">
         <v>8.6</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7904,13 +7904,13 @@
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT29" t="n">
         <v>6.4</v>
@@ -7922,23 +7922,23 @@
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -7969,220 +7969,220 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.09</v>
+        <v>2.46</v>
       </c>
       <c r="G30" t="n">
-        <v>990</v>
+        <v>3.1</v>
       </c>
       <c r="H30" t="n">
-        <v>1.15</v>
+        <v>2.94</v>
       </c>
       <c r="I30" t="n">
-        <v>990</v>
+        <v>3.75</v>
       </c>
       <c r="J30" t="n">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O30" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G31" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="H31" t="n">
         <v>11</v>
@@ -8235,10 +8235,10 @@
         <v>13.5</v>
       </c>
       <c r="J31" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.32</v>
@@ -8247,19 +8247,19 @@
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
         <v>1.69</v>
       </c>
       <c r="R31" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S31" t="n">
         <v>2.74</v>
@@ -8274,7 +8274,7 @@
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="X31" t="n">
         <v>23</v>
@@ -8298,7 +8298,7 @@
         <v>46</v>
       </c>
       <c r="AE31" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF31" t="n">
         <v>8.6</v>
@@ -8325,7 +8325,7 @@
         <v>210</v>
       </c>
       <c r="AN31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO31" t="n">
         <v>370</v>
@@ -8334,55 +8334,55 @@
         <v>14</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT31" t="n">
         <v>6.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC31" t="n">
         <v>11</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF31" t="n">
         <v>3.3</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH31" t="n">
         <v>4.1</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G32" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J32" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K32" t="n">
         <v>950</v>
@@ -8501,13 +8501,13 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O32" t="n">
         <v>1.02</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
         <v>1.4</v>
@@ -8519,10 +8519,10 @@
         <v>1.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
         <v>38</v>
@@ -8812,7 +8812,7 @@
         <v>16.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
         <v>18</v>
@@ -8827,7 +8827,7 @@
         <v>28</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM33" t="n">
         <v>100</v>
@@ -8848,7 +8848,7 @@
         <v>16</v>
       </c>
       <c r="AS33" t="n">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="AT33" t="n">
         <v>8</v>
@@ -8896,22 +8896,22 @@
         <v>3.7</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.6</v>
       </c>
       <c r="BK33" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN33" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO33" t="n">
         <v>4.1</v>
@@ -8920,13 +8920,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT33" t="n">
         <v>6.6</v>
@@ -8938,23 +8938,23 @@
         <v>25</v>
       </c>
       <c r="BW33" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX33" t="n">
         <v>36</v>
       </c>
       <c r="BY33" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ33" t="n">
         <v>25</v>
       </c>
       <c r="CA33" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -8985,175 +8985,175 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>1.2</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>19</v>
       </c>
       <c r="I34" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="L34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M34" t="n">
         <v>1.01</v>
       </c>
-      <c r="M34" t="n">
-        <v>1.02</v>
-      </c>
       <c r="N34" t="n">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.1</v>
       </c>
       <c r="P34" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="R34" t="n">
-        <v>1.09</v>
+        <v>2.02</v>
       </c>
       <c r="S34" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH34" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK34" t="n">
         <v>1.01</v>
@@ -9165,25 +9165,25 @@
         <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS34" t="n">
         <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -9239,157 +9239,157 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="G35" t="n">
-        <v>110</v>
+        <v>2.04</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>620</v>
+        <v>5.7</v>
       </c>
       <c r="J35" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K35" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP35" t="n">
         <v>1.01</v>
       </c>
-      <c r="M35" t="n">
+      <c r="AQ35" t="n">
         <v>1.01</v>
       </c>
-      <c r="N35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T35" t="n">
+      <c r="AR35" t="n">
         <v>1.01</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.03</v>
       </c>
       <c r="AS35" t="n">
         <v>1.03</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
         <v>1.03</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
         <v>1.03</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
         <v>1.03</v>
@@ -9401,58 +9401,58 @@
         <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BX35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -9493,154 +9493,154 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G36" t="n">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I36" t="n">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP36" t="n">
         <v>1.01</v>
       </c>
-      <c r="M36" t="n">
+      <c r="AQ36" t="n">
         <v>1.01</v>
       </c>
-      <c r="N36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="AR36" t="n">
         <v>1.01</v>
       </c>
-      <c r="U36" t="n">
+      <c r="AS36" t="n">
         <v>1.01</v>
       </c>
-      <c r="V36" t="n">
+      <c r="AT36" t="n">
         <v>1.01</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AU36" t="n">
         <v>1.01</v>
       </c>
-      <c r="X36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
         <v>1.03</v>
@@ -9655,10 +9655,10 @@
         <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -9747,19 +9747,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G37" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I37" t="n">
         <v>2.6</v>
       </c>
       <c r="J37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K37" t="n">
         <v>3.65</v>
@@ -9771,34 +9771,34 @@
         <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
         <v>1.29</v>
       </c>
       <c r="P37" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R37" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T37" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U37" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V37" t="n">
         <v>1.62</v>
       </c>
       <c r="W37" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X37" t="n">
         <v>16</v>
@@ -9852,7 +9852,7 @@
         <v>28</v>
       </c>
       <c r="AO37" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP37" t="n">
         <v>13.5</v>
@@ -9891,7 +9891,7 @@
         <v>5.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC37" t="n">
         <v>5.2</v>
@@ -9900,13 +9900,13 @@
         <v>5.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF37" t="n">
         <v>20</v>
       </c>
       <c r="BG37" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH37" t="n">
         <v>3.6</v>
@@ -9930,7 +9930,7 @@
         <v>6.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP37" t="n">
         <v>23</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -10001,22 +10001,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H38" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J38" t="n">
         <v>3.3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L38" t="n">
         <v>1.36</v>
@@ -10025,7 +10025,7 @@
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.35</v>
@@ -10040,7 +10040,7 @@
         <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T38" t="n">
         <v>1.79</v>
@@ -10049,22 +10049,22 @@
         <v>2.18</v>
       </c>
       <c r="V38" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X38" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y38" t="n">
         <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB38" t="n">
         <v>11.5</v>
@@ -10079,13 +10079,13 @@
         <v>32</v>
       </c>
       <c r="AF38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG38" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI38" t="n">
         <v>44</v>
@@ -10094,19 +10094,19 @@
         <v>48</v>
       </c>
       <c r="AK38" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL38" t="n">
         <v>46</v>
       </c>
       <c r="AM38" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN38" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AO38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP38" t="n">
         <v>11.5</v>
@@ -10118,13 +10118,13 @@
         <v>15.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV38" t="n">
         <v>11.5</v>
@@ -10133,7 +10133,7 @@
         <v>19.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY38" t="n">
         <v>11.5</v>
@@ -10142,16 +10142,16 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BB38" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BC38" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BD38" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BE38" t="n">
         <v>36</v>
@@ -10160,7 +10160,7 @@
         <v>19.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BH38" t="n">
         <v>3.3</v>
@@ -10172,7 +10172,7 @@
         <v>9.6</v>
       </c>
       <c r="BK38" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G39" t="n">
         <v>1.71</v>
@@ -10264,19 +10264,19 @@
         <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J39" t="n">
         <v>4.4</v>
       </c>
       <c r="K39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N39" t="n">
         <v>5.3</v>
@@ -10288,7 +10288,7 @@
         <v>2.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R39" t="n">
         <v>1.59</v>
@@ -10300,7 +10300,7 @@
         <v>1.67</v>
       </c>
       <c r="U39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V39" t="n">
         <v>1.21</v>
@@ -10369,7 +10369,7 @@
         <v>17.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AS39" t="n">
         <v>12</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -10512,16 +10512,16 @@
         <v>1.9</v>
       </c>
       <c r="G40" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
         <v>4.3</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K40" t="n">
         <v>4.2</v>
@@ -10539,7 +10539,7 @@
         <v>1.22</v>
       </c>
       <c r="P40" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q40" t="n">
         <v>1.65</v>
@@ -10602,7 +10602,7 @@
         <v>26</v>
       </c>
       <c r="AK40" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL40" t="n">
         <v>34</v>
@@ -10623,13 +10623,13 @@
         <v>15</v>
       </c>
       <c r="AR40" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS40" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU40" t="n">
         <v>8.6</v>
@@ -10638,10 +10638,10 @@
         <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY40" t="n">
         <v>9.6</v>
@@ -10650,7 +10650,7 @@
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB40" t="n">
         <v>16.5</v>
@@ -10662,13 +10662,13 @@
         <v>21</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF40" t="n">
         <v>8.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH40" t="n">
         <v>4.3</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G41" t="n">
         <v>2.98</v>
@@ -10778,10 +10778,10 @@
         <v>2.76</v>
       </c>
       <c r="K41" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
         <v>1.1</v>
@@ -10793,16 +10793,16 @@
         <v>1.44</v>
       </c>
       <c r="P41" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R41" t="n">
         <v>1.24</v>
       </c>
       <c r="S41" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T41" t="n">
         <v>1.75</v>
@@ -10838,7 +10838,7 @@
         <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF41" t="n">
         <v>970</v>
@@ -10892,10 +10892,10 @@
         <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX41" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY41" t="n">
         <v>9.6</v>
@@ -10913,10 +10913,10 @@
         <v>22</v>
       </c>
       <c r="BD41" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF41" t="n">
         <v>22</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
         <v>2.98</v>
       </c>
       <c r="T42" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U42" t="n">
         <v>1.87</v>
@@ -11128,13 +11128,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AR42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS42" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>4.6</v>
       </c>
       <c r="AT42" t="n">
         <v>6.8</v>
@@ -11143,10 +11143,10 @@
         <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX42" t="n">
         <v>7.8</v>
@@ -11155,28 +11155,28 @@
         <v>7.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BC42" t="n">
         <v>12.5</v>
       </c>
       <c r="BD42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG42" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>4.5</v>
       </c>
       <c r="BH42" t="n">
         <v>3.8</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="F43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J43" t="n">
         <v>3.15</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3.25</v>
       </c>
       <c r="K43" t="n">
         <v>3.55</v>
@@ -11301,10 +11301,10 @@
         <v>1.36</v>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="R43" t="n">
         <v>1.3</v>
@@ -11319,10 +11319,10 @@
         <v>2.04</v>
       </c>
       <c r="V43" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W43" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X43" t="n">
         <v>970</v>
@@ -11385,58 +11385,58 @@
         <v>4.1</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AT43" t="n">
         <v>4.2</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AV43" t="n">
         <v>4.2</v>
       </c>
       <c r="AW43" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AX43" t="n">
         <v>3.05</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="BA43" t="n">
         <v>3.25</v>
       </c>
       <c r="BB43" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BD43" t="n">
         <v>3.3</v>
       </c>
       <c r="BE43" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BF43" t="n">
         <v>3.25</v>
       </c>
       <c r="BG43" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ43" t="n">
         <v>1000</v>
@@ -11448,7 +11448,7 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="BN43" t="n">
         <v>1000</v>
@@ -11460,16 +11460,16 @@
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.27</v>
+        <v>1.99</v>
       </c>
       <c r="BT43" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BU43" t="n">
         <v>4.1</v>
@@ -11478,23 +11478,23 @@
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.26</v>
+        <v>1.96</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G44" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I44" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J44" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K44" t="n">
         <v>950</v>
@@ -11555,7 +11555,7 @@
         <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q44" t="n">
         <v>1.33</v>
@@ -11564,13 +11564,13 @@
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I45" t="n">
         <v>1.66</v>
@@ -11902,7 +11902,7 @@
         <v>3.7</v>
       </c>
       <c r="AU45" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV45" t="n">
         <v>7.4</v>
@@ -11944,7 +11944,7 @@
         <v>3.5</v>
       </c>
       <c r="BI45" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
@@ -11956,7 +11956,7 @@
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="BN45" t="n">
         <v>1000</v>
@@ -11968,13 +11968,13 @@
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>9.199999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>9.199999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="BT45" t="n">
         <v>4.1</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -12033,13 +12033,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G46" t="n">
         <v>2.74</v>
       </c>
       <c r="H46" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I46" t="n">
         <v>3.2</v>
@@ -12048,13 +12048,13 @@
         <v>3.15</v>
       </c>
       <c r="K46" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L46" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M46" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N46" t="n">
         <v>3.2</v>
@@ -12066,7 +12066,7 @@
         <v>1.76</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R46" t="n">
         <v>1.28</v>
@@ -12075,19 +12075,19 @@
         <v>3.95</v>
       </c>
       <c r="T46" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U46" t="n">
         <v>2.02</v>
       </c>
       <c r="V46" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W46" t="n">
         <v>1.57</v>
       </c>
       <c r="X46" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y46" t="n">
         <v>11.5</v>
@@ -12150,7 +12150,7 @@
         <v>17.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT46" t="n">
         <v>8.4</v>
@@ -12174,31 +12174,31 @@
         <v>14</v>
       </c>
       <c r="BA46" t="n">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="BB46" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC46" t="n">
         <v>7.6</v>
       </c>
       <c r="BD46" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF46" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG46" t="n">
         <v>8</v>
       </c>
       <c r="BH46" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BJ46" t="n">
         <v>10</v>
@@ -12219,7 +12219,7 @@
         <v>4.3</v>
       </c>
       <c r="BP46" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ46" t="n">
         <v>8.199999999999999</v>
@@ -12252,11 +12252,11 @@
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -12287,25 +12287,25 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G47" t="n">
         <v>2.62</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I47" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L47" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
@@ -12401,7 +12401,7 @@
         <v>5.1</v>
       </c>
       <c r="AR47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS47" t="n">
         <v>3.65</v>
@@ -12413,10 +12413,10 @@
         <v>6.8</v>
       </c>
       <c r="AV47" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX47" t="n">
         <v>6</v>
@@ -12428,25 +12428,25 @@
         <v>6.4</v>
       </c>
       <c r="BA47" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="BB47" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD47" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC47" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>32</v>
-      </c>
       <c r="BE47" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF47" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG47" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH47" t="n">
         <v>3.1</v>
@@ -12464,7 +12464,7 @@
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>6</v>
+        <v>1.88</v>
       </c>
       <c r="BN47" t="n">
         <v>5.4</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -12544,16 +12544,16 @@
         <v>2.3</v>
       </c>
       <c r="G48" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="H48" t="n">
         <v>3.45</v>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K48" t="n">
         <v>3.4</v>
@@ -12574,7 +12574,7 @@
         <v>1.62</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R48" t="n">
         <v>1.23</v>
@@ -12592,7 +12592,7 @@
         <v>1.33</v>
       </c>
       <c r="W48" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X48" t="n">
         <v>11.5</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -12795,112 +12795,112 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.19</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>990</v>
+        <v>3.9</v>
       </c>
       <c r="H49" t="n">
-        <v>1.19</v>
+        <v>2.36</v>
       </c>
       <c r="I49" t="n">
-        <v>990</v>
+        <v>2.92</v>
       </c>
       <c r="J49" t="n">
-        <v>1.1</v>
+        <v>2.82</v>
       </c>
       <c r="K49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X49" t="n">
         <v>950</v>
       </c>
-      <c r="L49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI49" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL49" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM49" t="n">
         <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP49" t="n">
         <v>1.01</v>
@@ -12957,58 +12957,58 @@
         <v>1.01</v>
       </c>
       <c r="BH49" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ49" t="n">
         <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BN49" t="n">
         <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BT49" t="n">
         <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
         <v>3.35</v>
       </c>
       <c r="L50" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M50" t="n">
         <v>1.12</v>
@@ -13076,13 +13076,13 @@
         <v>2.66</v>
       </c>
       <c r="O50" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P50" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R50" t="n">
         <v>1.2</v>
@@ -13091,10 +13091,10 @@
         <v>5.3</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U50" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V50" t="n">
         <v>1.27</v>
@@ -13157,7 +13157,7 @@
         <v>130</v>
       </c>
       <c r="AP50" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ50" t="n">
         <v>10</v>
@@ -13193,10 +13193,10 @@
         <v>7.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BC50" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BD50" t="n">
         <v>7.4</v>
@@ -13211,10 +13211,10 @@
         <v>7.8</v>
       </c>
       <c r="BH50" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI50" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ50" t="n">
         <v>12</v>
@@ -13238,13 +13238,13 @@
         <v>18</v>
       </c>
       <c r="BQ50" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR50" t="n">
         <v>42</v>
       </c>
       <c r="BS50" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT50" t="n">
         <v>7.8</v>
@@ -13256,23 +13256,23 @@
         <v>48</v>
       </c>
       <c r="BW50" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX50" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ50" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA50" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
         <v>2.72</v>
       </c>
       <c r="G51" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H51" t="n">
         <v>2.76</v>
@@ -13318,22 +13318,22 @@
         <v>3.4</v>
       </c>
       <c r="K51" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L51" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M51" t="n">
         <v>1.08</v>
       </c>
       <c r="N51" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O51" t="n">
         <v>1.36</v>
       </c>
       <c r="P51" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q51" t="n">
         <v>2.04</v>
@@ -13342,7 +13342,7 @@
         <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T51" t="n">
         <v>1.79</v>
@@ -13372,13 +13372,13 @@
         <v>11.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD51" t="n">
         <v>13.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF51" t="n">
         <v>19.5</v>
@@ -13402,7 +13402,7 @@
         <v>48</v>
       </c>
       <c r="AM51" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>32</v>
@@ -13420,7 +13420,7 @@
         <v>16</v>
       </c>
       <c r="AS51" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT51" t="n">
         <v>9.199999999999999</v>
@@ -13441,34 +13441,34 @@
         <v>10.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BA51" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC51" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>6.8</v>
       </c>
       <c r="BD51" t="n">
         <v>32</v>
       </c>
       <c r="BE51" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF51" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG51" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH51" t="n">
         <v>3.4</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ51" t="n">
         <v>10</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -13557,55 +13557,55 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G52" t="n">
         <v>2.12</v>
       </c>
       <c r="H52" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I52" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K52" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L52" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M52" t="n">
         <v>1.1</v>
       </c>
       <c r="N52" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O52" t="n">
         <v>1.44</v>
       </c>
       <c r="P52" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="R52" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S52" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U52" t="n">
         <v>1.81</v>
       </c>
       <c r="V52" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W52" t="n">
         <v>1.89</v>
@@ -13614,28 +13614,28 @@
         <v>11.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z52" t="n">
         <v>38</v>
       </c>
       <c r="AA52" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC52" t="n">
         <v>8.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE52" t="n">
         <v>85</v>
       </c>
       <c r="AF52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG52" t="n">
         <v>12.5</v>
@@ -13644,61 +13644,61 @@
         <v>26</v>
       </c>
       <c r="AI52" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ52" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK52" t="n">
         <v>29</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>30</v>
       </c>
       <c r="AL52" t="n">
         <v>60</v>
       </c>
       <c r="AM52" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO52" t="n">
         <v>120</v>
       </c>
       <c r="AP52" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ52" t="n">
         <v>10</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS52" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU52" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV52" t="n">
         <v>14.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX52" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY52" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ52" t="n">
         <v>17</v>
       </c>
       <c r="BA52" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB52" t="n">
         <v>19</v>
@@ -13707,80 +13707,80 @@
         <v>19.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE52" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF52" t="n">
         <v>16.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH52" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="BJ52" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK52" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN52" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO52" t="n">
         <v>3.6</v>
       </c>
       <c r="BP52" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ52" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT52" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU52" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
         <v>1.2</v>
       </c>
       <c r="S53" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T53" t="n">
         <v>2.12</v>
@@ -13859,7 +13859,7 @@
         <v>1.7</v>
       </c>
       <c r="V53" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W53" t="n">
         <v>1.96</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -14080,10 +14080,10 @@
         <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L54" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
@@ -14224,13 +14224,13 @@
         <v>15</v>
       </c>
       <c r="BG54" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH54" t="n">
         <v>3.35</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="BJ54" t="n">
         <v>10.5</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -14322,10 +14322,10 @@
         <v>1.33</v>
       </c>
       <c r="G55" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I55" t="n">
         <v>16</v>
@@ -14334,10 +14334,10 @@
         <v>4.7</v>
       </c>
       <c r="K55" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L55" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M55" t="n">
         <v>1.08</v>
@@ -14358,7 +14358,7 @@
         <v>1.29</v>
       </c>
       <c r="S55" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T55" t="n">
         <v>2.56</v>
@@ -14370,7 +14370,7 @@
         <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X55" t="n">
         <v>14.5</v>
@@ -14433,7 +14433,7 @@
         <v>21</v>
       </c>
       <c r="AR55" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS55" t="n">
         <v>7.2</v>
@@ -14445,10 +14445,10 @@
         <v>9.4</v>
       </c>
       <c r="AV55" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW55" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX55" t="n">
         <v>5.5</v>
@@ -14469,10 +14469,10 @@
         <v>14</v>
       </c>
       <c r="BD55" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF55" t="n">
         <v>6.2</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>
@@ -14573,112 +14573,112 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X56" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO56" t="n">
         <v>110</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I56" t="n">
-        <v>110</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K56" t="n">
-        <v>950</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>1000</v>
       </c>
       <c r="AP56" t="n">
         <v>1.03</v>
@@ -14729,74 +14729,74 @@
         <v>1.03</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG56" t="n">
         <v>1.01</v>
       </c>
       <c r="BH56" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ56" t="n">
         <v>1000</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN56" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP56" t="n">
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT56" t="n">
         <v>1000</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -869,25 +869,25 @@
         <v>2.22</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
         <v>2.38</v>
@@ -896,61 +896,61 @@
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK2" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL2" t="n">
         <v>110</v>
@@ -962,13 +962,13 @@
         <v>130</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
         <v>9.199999999999999</v>
@@ -980,40 +980,40 @@
         <v>9.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW2" t="n">
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
         <v>18.5</v>
@@ -1028,7 +1028,7 @@
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,7 +1037,7 @@
         <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO2" t="n">
         <v>4.6</v>
@@ -1046,13 +1046,13 @@
         <v>46</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>4.8</v>
@@ -1070,17 +1070,17 @@
         <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>42</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
         <v>6</v>
@@ -1123,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
@@ -1138,13 +1138,13 @@
         <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
@@ -1156,13 +1156,13 @@
         <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1195,13 +1195,13 @@
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
         <v>22</v>
@@ -1213,34 +1213,34 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
         <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV3" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AW3" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
@@ -1249,10 +1249,10 @@
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1261,22 +1261,22 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="BF3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="BH3" t="n">
         <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="n">
         <v>1.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
@@ -1395,7 +1395,7 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
         <v>1.8</v>
@@ -1410,13 +1410,13 @@
         <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1428,7 +1428,7 @@
         <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB4" t="n">
         <v>16.5</v>
@@ -1443,7 +1443,7 @@
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
         <v>19.5</v>
@@ -1455,7 +1455,7 @@
         <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AK4" t="n">
         <v>60</v>
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
@@ -1506,31 +1506,31 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
@@ -1542,19 +1542,19 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1563,32 +1563,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW4" t="n">
         <v>5.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA4" t="n">
         <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>1.71</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1658,16 +1658,16 @@
         <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
         <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
         <v>2.4</v>
@@ -1724,55 +1724,55 @@
         <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
         <v>4.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>2.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R6" t="n">
         <v>1.72</v>
@@ -1915,10 +1915,10 @@
         <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
         <v>1.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.98</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
         <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.85</v>
@@ -2175,10 +2175,10 @@
         <v>2.62</v>
       </c>
       <c r="V7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
         <v>27</v>
@@ -2244,7 +2244,7 @@
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT7" t="n">
         <v>14.5</v>
@@ -2292,7 +2292,7 @@
         <v>4.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
         <v>3.85</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
@@ -2659,13 +2659,13 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
         <v>1.51</v>
@@ -2674,19 +2674,19 @@
         <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2695,10 +2695,10 @@
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
@@ -2710,10 +2710,10 @@
         <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
@@ -2722,13 +2722,13 @@
         <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AK9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
         <v>34</v>
@@ -2746,31 +2746,31 @@
         <v>5.1</v>
       </c>
       <c r="AQ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR9" t="n">
         <v>4.7</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW9" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AX9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>11</v>
@@ -2779,10 +2779,10 @@
         <v>5.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
         <v>5.1</v>
@@ -2791,10 +2791,10 @@
         <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
         <v>4.8</v>
@@ -2812,43 +2812,43 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.31</v>
+        <v>2.3</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G10" t="n">
         <v>2.32</v>
@@ -2922,7 +2922,7 @@
         <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
         <v>1.43</v>
@@ -3054,7 +3054,7 @@
         <v>3.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -3158,13 +3158,13 @@
         <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3182,13 +3182,13 @@
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V11" t="n">
         <v>1.15</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
         <v>1.55</v>
@@ -3436,10 +3436,10 @@
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U12" t="n">
         <v>2.44</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -3651,34 +3651,34 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="G13" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
         <v>1.68</v>
@@ -3687,130 +3687,130 @@
         <v>2.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
         <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB13" t="n">
         <v>11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
         <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
         <v>60</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT13" t="n">
         <v>7.6</v>
       </c>
-      <c r="AR13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AU13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
         <v>5.6</v>
       </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA13" t="n">
         <v>6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
         <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="BH13" t="n">
         <v>3.2</v>
@@ -3828,40 +3828,40 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
         <v>42</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
         <v>6.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY13" t="n">
         <v>7.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4.8</v>
@@ -4183,19 +4183,19 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q15" t="n">
         <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
         <v>2.5</v>
@@ -4207,10 +4207,10 @@
         <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4219,7 +4219,7 @@
         <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
         <v>75</v>
@@ -4240,7 +4240,7 @@
         <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
         <v>970</v>
@@ -4252,7 +4252,7 @@
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>34</v>
@@ -4264,7 +4264,7 @@
         <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP15" t="n">
         <v>17.5</v>
@@ -4276,19 +4276,19 @@
         <v>4.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
@@ -4300,7 +4300,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BB15" t="n">
         <v>16.5</v>
@@ -4309,10 +4309,10 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BF15" t="n">
         <v>7</v>
@@ -4321,7 +4321,7 @@
         <v>4.3</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI15" t="n">
         <v>3.35</v>
@@ -4330,13 +4330,13 @@
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="BN15" t="n">
         <v>5.1</v>
@@ -4348,16 +4348,16 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU15" t="n">
         <v>5.8</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H16" t="n">
         <v>7</v>
@@ -4437,7 +4437,7 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
@@ -4446,7 +4446,7 @@
         <v>2.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R16" t="n">
         <v>1.6</v>
@@ -4464,7 +4464,7 @@
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X16" t="n">
         <v>29</v>
@@ -4482,7 +4482,7 @@
         <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD16" t="n">
         <v>34</v>
@@ -4527,10 +4527,10 @@
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -4542,7 +4542,7 @@
         <v>19.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX16" t="n">
         <v>9</v>
@@ -4554,7 +4554,7 @@
         <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
         <v>11.5</v>
@@ -4563,16 +4563,16 @@
         <v>13</v>
       </c>
       <c r="BD16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE16" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="n">
         <v>4.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>2.48</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
         <v>3.2</v>
@@ -4685,7 +4685,7 @@
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -4703,7 +4703,7 @@
         <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
         <v>2.96</v>
@@ -4712,7 +4712,7 @@
         <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V17" t="n">
         <v>1.45</v>
@@ -4721,13 +4721,13 @@
         <v>1.67</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
         <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
         <v>55</v>
@@ -4745,7 +4745,7 @@
         <v>34</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
@@ -4757,10 +4757,10 @@
         <v>42</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
         <v>36</v>
@@ -4769,22 +4769,22 @@
         <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AT17" t="n">
         <v>10.5</v>
@@ -4796,7 +4796,7 @@
         <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
@@ -4805,10 +4805,10 @@
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BB17" t="n">
         <v>27</v>
@@ -4817,16 +4817,16 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BF17" t="n">
         <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH17" t="n">
         <v>3.9</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.64</v>
       </c>
       <c r="G18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
         <v>2.54</v>
@@ -4936,7 +4936,7 @@
         <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.23</v>
@@ -4954,7 +4954,7 @@
         <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R18" t="n">
         <v>1.68</v>
@@ -4963,7 +4963,7 @@
         <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U18" t="n">
         <v>2.8</v>
@@ -5104,7 +5104,7 @@
         <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP18" t="n">
         <v>18</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -5208,13 +5208,13 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R19" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="S19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
         <v>1.43</v>
@@ -5223,10 +5223,10 @@
         <v>2.96</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5235,19 +5235,19 @@
         <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AC19" t="n">
         <v>14</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
         <v>32</v>
@@ -5265,10 +5265,10 @@
         <v>34</v>
       </c>
       <c r="AJ19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>32</v>
@@ -5277,13 +5277,13 @@
         <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AQ19" t="n">
         <v>16</v>
@@ -5292,7 +5292,7 @@
         <v>18.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
         <v>14.5</v>
@@ -5316,19 +5316,19 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BC19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD19" t="n">
         <v>18.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
         <v>7.4</v>
@@ -5358,7 +5358,7 @@
         <v>6.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
@@ -5370,7 +5370,7 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT19" t="n">
         <v>7</v>
@@ -5388,7 +5388,7 @@
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ19" t="n">
         <v>12.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>3.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>4.2</v>
@@ -5462,7 +5462,7 @@
         <v>2.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R20" t="n">
         <v>1.76</v>
@@ -5540,7 +5540,7 @@
         <v>5.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AR20" t="n">
         <v>5.4</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H21" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="I21" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
@@ -5713,7 +5713,7 @@
         <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
         <v>1.7</v>
@@ -5731,34 +5731,34 @@
         <v>2.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W21" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X21" t="n">
         <v>24</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB21" t="n">
         <v>19.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
         <v>13.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF21" t="n">
         <v>32</v>
@@ -5788,7 +5788,7 @@
         <v>34</v>
       </c>
       <c r="AO21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
         <v>14</v>
@@ -5806,7 +5806,7 @@
         <v>11.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
         <v>8.199999999999999</v>
@@ -5824,19 +5824,19 @@
         <v>11.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF21" t="n">
         <v>20</v>
@@ -5848,31 +5848,31 @@
         <v>4.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
@@ -5881,13 +5881,13 @@
         <v>7.8</v>
       </c>
       <c r="BT21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW21" t="n">
         <v>6.2</v>
@@ -5899,14 +5899,14 @@
         <v>7.4</v>
       </c>
       <c r="BZ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA21" t="n">
         <v>6.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H22" t="n">
         <v>2.36</v>
@@ -5949,7 +5949,7 @@
         <v>2.44</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -5970,7 +5970,7 @@
         <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R22" t="n">
         <v>1.5</v>
@@ -5982,13 +5982,13 @@
         <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V22" t="n">
         <v>1.69</v>
       </c>
       <c r="W22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
         <v>23</v>
@@ -6006,7 +6006,7 @@
         <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>14.5</v>
@@ -6048,22 +6048,22 @@
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR22" t="n">
         <v>12.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT22" t="n">
         <v>11</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW22" t="n">
         <v>17</v>
@@ -6078,22 +6078,22 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG22" t="n">
         <v>11</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I23" t="n">
         <v>6.8</v>
@@ -6221,13 +6221,13 @@
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q23" t="n">
         <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="S23" t="n">
         <v>2.08</v>
@@ -6242,7 +6242,7 @@
         <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X23" t="n">
         <v>950</v>
@@ -6302,13 +6302,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT23" t="n">
         <v>5.9</v>
@@ -6320,7 +6320,7 @@
         <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX23" t="n">
         <v>10.5</v>
@@ -6332,7 +6332,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB23" t="n">
         <v>13</v>
@@ -6344,19 +6344,19 @@
         <v>7</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
         <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH23" t="n">
         <v>5.3</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.800000000000001</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G24" t="n">
         <v>1.85</v>
@@ -6460,7 +6460,7 @@
         <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.22</v>
@@ -6481,7 +6481,7 @@
         <v>1.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S24" t="n">
         <v>2.24</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="G25" t="n">
         <v>2.5</v>
@@ -6708,16 +6708,16 @@
         <v>2.98</v>
       </c>
       <c r="I25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
@@ -6768,13 +6768,13 @@
         <v>15.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
         <v>16</v>
       </c>
       <c r="AE25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF25" t="n">
         <v>21</v>
@@ -6783,22 +6783,22 @@
         <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK25" t="n">
         <v>28</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN25" t="n">
         <v>18</v>
@@ -6813,52 +6813,52 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV25" t="n">
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC25" t="n">
         <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF25" t="n">
         <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH25" t="n">
         <v>4</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         <v>2.14</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
         <v>1.08</v>
@@ -6986,7 +6986,7 @@
         <v>1.81</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R26" t="n">
         <v>1.31</v>
@@ -7001,7 +7001,7 @@
         <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W26" t="n">
         <v>1.28</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7369,7 @@
         <v>4.2</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI27" t="n">
         <v>2.62</v>
@@ -7378,49 +7378,49 @@
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
         <v>2.18</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I28" t="n">
         <v>4.1</v>
@@ -7479,7 +7479,7 @@
         <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -7503,7 +7503,7 @@
         <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
         <v>2.08</v>
@@ -7626,37 +7626,37 @@
         <v>3.45</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="BJ28" t="n">
         <v>10.5</v>
       </c>
       <c r="BK28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN28" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>5.2</v>
       </c>
       <c r="BO28" t="n">
         <v>3.95</v>
       </c>
       <c r="BP28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT28" t="n">
         <v>7.2</v>
@@ -7668,23 +7668,23 @@
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G29" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H29" t="n">
         <v>2.56</v>
       </c>
       <c r="I29" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J29" t="n">
         <v>3.9</v>
@@ -7751,19 +7751,19 @@
         <v>1.53</v>
       </c>
       <c r="R29" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="S29" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U29" t="n">
         <v>2.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W29" t="n">
         <v>1.56</v>
@@ -7772,13 +7772,13 @@
         <v>950</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="n">
         <v>26</v>
       </c>
       <c r="AA29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB29" t="n">
         <v>20</v>
@@ -7802,7 +7802,7 @@
         <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ29" t="n">
         <v>42</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>2.46</v>
       </c>
       <c r="G30" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H30" t="n">
         <v>2.94</v>
@@ -7981,7 +7981,7 @@
         <v>3.75</v>
       </c>
       <c r="J30" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K30" t="n">
         <v>3.5</v>
@@ -7993,22 +7993,22 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P30" t="n">
         <v>1.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R30" t="n">
         <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
         <v>1.92</v>
@@ -8017,10 +8017,10 @@
         <v>1.83</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X30" t="n">
         <v>11.5</v>
@@ -8047,7 +8047,7 @@
         <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG30" t="n">
         <v>14.5</v>
@@ -8077,64 +8077,64 @@
         <v>65</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA30" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW30" t="n">
+      <c r="BB30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD30" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA30" t="n">
+      <c r="BE30" t="n">
         <v>5</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BF30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>4.9</v>
       </c>
       <c r="BH30" t="n">
         <v>3</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="BJ30" t="n">
         <v>11.5</v>
@@ -8146,7 +8146,7 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="BN30" t="n">
         <v>5.7</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         <v>13.5</v>
       </c>
       <c r="J31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K31" t="n">
         <v>6.4</v>
@@ -8247,7 +8247,7 @@
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
@@ -8343,7 +8343,7 @@
         <v>6.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU31" t="n">
         <v>4.6</v>
@@ -8355,7 +8355,7 @@
         <v>6.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="G32" t="n">
         <v>990</v>
       </c>
       <c r="H32" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="I32" t="n">
         <v>990</v>
       </c>
       <c r="J32" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K32" t="n">
         <v>950</v>
@@ -8501,13 +8501,13 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O32" t="n">
         <v>1.02</v>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q32" t="n">
         <v>1.4</v>
@@ -8516,7 +8516,7 @@
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -8788,10 +8788,10 @@
         <v>21</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA33" t="n">
         <v>55</v>
@@ -8806,7 +8806,7 @@
         <v>14.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF33" t="n">
         <v>16.5</v>
@@ -8824,7 +8824,7 @@
         <v>32</v>
       </c>
       <c r="AK33" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL33" t="n">
         <v>36</v>
@@ -8848,7 +8848,7 @@
         <v>16</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT33" t="n">
         <v>8</v>
@@ -8860,7 +8860,7 @@
         <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX33" t="n">
         <v>11.5</v>
@@ -8872,19 +8872,19 @@
         <v>12.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC33" t="n">
         <v>17</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF33" t="n">
         <v>12.5</v>
@@ -8896,7 +8896,7 @@
         <v>3.7</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
         <v>11</v>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>1.1</v>
@@ -9030,19 +9030,19 @@
         <v>2.04</v>
       </c>
       <c r="U34" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V34" t="n">
         <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="X34" t="n">
         <v>60</v>
       </c>
       <c r="Y34" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Z34" t="n">
         <v>270</v>
@@ -9060,7 +9060,7 @@
         <v>75</v>
       </c>
       <c r="AE34" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AF34" t="n">
         <v>11</v>
@@ -9072,7 +9072,7 @@
         <v>44</v>
       </c>
       <c r="AI34" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ34" t="n">
         <v>9.800000000000001</v>
@@ -9084,25 +9084,25 @@
         <v>42</v>
       </c>
       <c r="AM34" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN34" t="n">
         <v>2.76</v>
       </c>
       <c r="AO34" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AP34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ34" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT34" t="n">
         <v>11</v>
@@ -9114,7 +9114,7 @@
         <v>8.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX34" t="n">
         <v>7.6</v>
@@ -9123,10 +9123,10 @@
         <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BA34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB34" t="n">
         <v>7</v>
@@ -9135,16 +9135,16 @@
         <v>10.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF34" t="n">
         <v>2.42</v>
       </c>
       <c r="BG34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH34" t="n">
         <v>6.4</v>
@@ -9156,13 +9156,13 @@
         <v>14.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN34" t="n">
         <v>4.2</v>
@@ -9180,25 +9180,25 @@
         <v>21</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT34" t="n">
         <v>21</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
         <v>1.34</v>
       </c>
       <c r="P35" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q35" t="n">
         <v>1.9</v>
@@ -9281,10 +9281,10 @@
         <v>3.05</v>
       </c>
       <c r="T35" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U35" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V35" t="n">
         <v>1.21</v>
@@ -9347,58 +9347,58 @@
         <v>95</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH35" t="n">
         <v>3.4</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -9493,19 +9493,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G36" t="n">
         <v>3.45</v>
       </c>
       <c r="H36" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K36" t="n">
         <v>3.6</v>
@@ -9541,16 +9541,16 @@
         <v>1.91</v>
       </c>
       <c r="V36" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W36" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X36" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y36" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z36" t="n">
         <v>21</v>
@@ -9559,10 +9559,10 @@
         <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD36" t="n">
         <v>970</v>
@@ -9571,22 +9571,22 @@
         <v>42</v>
       </c>
       <c r="AF36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG36" t="n">
         <v>970</v>
       </c>
       <c r="AH36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
         <v>60</v>
       </c>
       <c r="AK36" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL36" t="n">
         <v>65</v>
@@ -9595,64 +9595,64 @@
         <v>150</v>
       </c>
       <c r="AN36" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO36" t="n">
         <v>42</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH36" t="n">
         <v>3.15</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G37" t="n">
         <v>3.1</v>
@@ -9759,40 +9759,40 @@
         <v>2.6</v>
       </c>
       <c r="J37" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L37" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="M37" t="n">
         <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P37" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R37" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U37" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V37" t="n">
         <v>1.62</v>
@@ -9801,13 +9801,13 @@
         <v>1.48</v>
       </c>
       <c r="X37" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="n">
         <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AA37" t="n">
         <v>44</v>
@@ -9828,13 +9828,13 @@
         <v>26</v>
       </c>
       <c r="AG37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH37" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI37" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ37" t="n">
         <v>60</v>
@@ -9843,19 +9843,19 @@
         <v>34</v>
       </c>
       <c r="AL37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM37" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN37" t="n">
         <v>28</v>
       </c>
       <c r="AO37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP37" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>10</v>
@@ -9864,7 +9864,7 @@
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT37" t="n">
         <v>11</v>
@@ -9873,13 +9873,13 @@
         <v>7.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW37" t="n">
         <v>19.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY37" t="n">
         <v>11.5</v>
@@ -9888,31 +9888,31 @@
         <v>14</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD37" t="n">
         <v>5.2</v>
       </c>
-      <c r="BD37" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE37" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF37" t="n">
         <v>20</v>
       </c>
       <c r="BG37" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH37" t="n">
         <v>3.6</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="BJ37" t="n">
         <v>9.199999999999999</v>
@@ -9930,7 +9930,7 @@
         <v>6.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BP37" t="n">
         <v>23</v>
@@ -9948,7 +9948,7 @@
         <v>5.6</v>
       </c>
       <c r="BU37" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV37" t="n">
         <v>19</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -10001,16 +10001,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G38" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I38" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J38" t="n">
         <v>3.3</v>
@@ -10031,7 +10031,7 @@
         <v>1.35</v>
       </c>
       <c r="P38" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q38" t="n">
         <v>2.06</v>
@@ -10046,13 +10046,13 @@
         <v>1.79</v>
       </c>
       <c r="U38" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V38" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W38" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
         <v>13</v>
@@ -10061,7 +10061,7 @@
         <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA38" t="n">
         <v>48</v>
@@ -10079,7 +10079,7 @@
         <v>32</v>
       </c>
       <c r="AF38" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG38" t="n">
         <v>13</v>
@@ -10088,7 +10088,7 @@
         <v>17.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ38" t="n">
         <v>48</v>
@@ -10097,13 +10097,13 @@
         <v>38</v>
       </c>
       <c r="AL38" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM38" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN38" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO38" t="n">
         <v>28</v>
@@ -10130,7 +10130,7 @@
         <v>11.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AX38" t="n">
         <v>17</v>
@@ -10142,13 +10142,13 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BB38" t="n">
         <v>40</v>
       </c>
       <c r="BC38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD38" t="n">
         <v>40</v>
@@ -10157,7 +10157,7 @@
         <v>36</v>
       </c>
       <c r="BF38" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BG38" t="n">
         <v>23</v>
@@ -10166,22 +10166,22 @@
         <v>3.3</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ38" t="n">
         <v>9.6</v>
       </c>
       <c r="BK38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN38" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO38" t="n">
         <v>4.5</v>
@@ -10190,7 +10190,7 @@
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
@@ -10205,10 +10205,10 @@
         <v>4.3</v>
       </c>
       <c r="BV38" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX38" t="n">
         <v>36</v>
@@ -10220,11 +10220,11 @@
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G39" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H39" t="n">
         <v>5</v>
@@ -10270,10 +10270,10 @@
         <v>4.4</v>
       </c>
       <c r="K39" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M39" t="n">
         <v>1.04</v>
@@ -10303,10 +10303,10 @@
         <v>2.32</v>
       </c>
       <c r="V39" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W39" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X39" t="n">
         <v>950</v>
@@ -10363,16 +10363,16 @@
         <v>50</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ39" t="n">
         <v>17.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT39" t="n">
         <v>10.5</v>
@@ -10405,7 +10405,7 @@
         <v>14</v>
       </c>
       <c r="BD39" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE39" t="n">
         <v>11.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -10509,151 +10509,151 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="G40" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="I40" t="n">
-        <v>4.3</v>
-      </c>
       <c r="J40" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
         <v>4.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O40" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P40" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R40" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="S40" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="T40" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U40" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>25</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>26</v>
       </c>
       <c r="AK40" t="n">
         <v>19.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AM40" t="n">
         <v>80</v>
       </c>
       <c r="AN40" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP40" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.9</v>
+        <v>34</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
         <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="AX40" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY40" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="BB40" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC40" t="n">
         <v>14</v>
@@ -10662,19 +10662,19 @@
         <v>21</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="BF40" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BH40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.4</v>
@@ -10692,31 +10692,31 @@
         <v>5.2</v>
       </c>
       <c r="BO40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BQ40" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS40" t="n">
         <v>7</v>
       </c>
       <c r="BT40" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU40" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW40" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G41" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
         <v>3.1</v>
@@ -10778,10 +10778,10 @@
         <v>2.76</v>
       </c>
       <c r="K41" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="L41" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
         <v>1.1</v>
@@ -10793,10 +10793,10 @@
         <v>1.44</v>
       </c>
       <c r="P41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R41" t="n">
         <v>1.24</v>
@@ -10805,10 +10805,10 @@
         <v>4.2</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="U41" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="V41" t="n">
         <v>1.39</v>
@@ -10823,10 +10823,10 @@
         <v>970</v>
       </c>
       <c r="Z41" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AA41" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB41" t="n">
         <v>970</v>
@@ -10841,7 +10841,7 @@
         <v>48</v>
       </c>
       <c r="AF41" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AG41" t="n">
         <v>970</v>
@@ -10877,25 +10877,25 @@
         <v>8</v>
       </c>
       <c r="AR41" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS41" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT41" t="n">
         <v>8</v>
       </c>
       <c r="AU41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AV41" t="n">
         <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX41" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY41" t="n">
         <v>9.6</v>
@@ -10904,7 +10904,7 @@
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB41" t="n">
         <v>27</v>
@@ -10913,16 +10913,16 @@
         <v>22</v>
       </c>
       <c r="BD41" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF41" t="n">
         <v>22</v>
       </c>
       <c r="BG41" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH41" t="n">
         <v>3.1</v>
@@ -10934,7 +10934,7 @@
         <v>11</v>
       </c>
       <c r="BK41" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -11023,22 +11023,22 @@
         <v>1.78</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I42" t="n">
         <v>6.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K42" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.3</v>
       </c>
       <c r="M42" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N42" t="n">
         <v>3.95</v>
@@ -11050,13 +11050,13 @@
         <v>2.04</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T42" t="n">
         <v>1.67</v>
@@ -11095,7 +11095,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG42" t="n">
         <v>12.5</v>
@@ -11128,13 +11128,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AT42" t="n">
         <v>6.8</v>
@@ -11143,10 +11143,10 @@
         <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX42" t="n">
         <v>7.8</v>
@@ -11155,13 +11155,13 @@
         <v>7.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB42" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC42" t="n">
         <v>12.5</v>
@@ -11170,19 +11170,19 @@
         <v>4</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BF42" t="n">
         <v>7.2</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH42" t="n">
         <v>3.8</v>
       </c>
       <c r="BI42" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
@@ -11194,7 +11194,7 @@
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="BN42" t="n">
         <v>4.5</v>
@@ -11224,13 +11224,13 @@
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.89</v>
+        <v>2.36</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -11271,34 +11271,34 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G43" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H43" t="n">
         <v>2.32</v>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J43" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K43" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L43" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P43" t="n">
         <v>1.89</v>
@@ -11307,22 +11307,22 @@
         <v>2.02</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S43" t="n">
         <v>3.6</v>
       </c>
       <c r="T43" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U43" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V43" t="n">
         <v>1.64</v>
       </c>
       <c r="W43" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X43" t="n">
         <v>970</v>
@@ -11340,7 +11340,7 @@
         <v>970</v>
       </c>
       <c r="AC43" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
         <v>970</v>
@@ -11364,19 +11364,19 @@
         <v>70</v>
       </c>
       <c r="AK43" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN43" t="n">
         <v>48</v>
       </c>
-      <c r="AL43" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>50</v>
-      </c>
       <c r="AO43" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP43" t="n">
         <v>4.3</v>
@@ -11385,73 +11385,73 @@
         <v>4.1</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT43" t="n">
         <v>4.2</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AV43" t="n">
         <v>4.2</v>
       </c>
       <c r="AW43" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AX43" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="AZ43" t="n">
         <v>4.8</v>
       </c>
       <c r="BA43" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BB43" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="BF43" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BG43" t="n">
         <v>5.1</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ43" t="n">
         <v>1000</v>
       </c>
       <c r="BK43" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>2.08</v>
+        <v>2.64</v>
       </c>
       <c r="BN43" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BO43" t="n">
         <v>5.1</v>
@@ -11460,41 +11460,41 @@
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="BT43" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU43" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="G44" t="n">
         <v>990</v>
       </c>
       <c r="H44" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="I44" t="n">
         <v>990</v>
@@ -11555,7 +11555,7 @@
         <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Q44" t="n">
         <v>1.33</v>
@@ -11564,7 +11564,7 @@
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T44" t="n">
         <v>1.11</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -11791,10 +11791,10 @@
         <v>1.66</v>
       </c>
       <c r="J45" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K45" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L45" t="n">
         <v>1.34</v>
@@ -11839,7 +11839,7 @@
         <v>9</v>
       </c>
       <c r="Z45" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AA45" t="n">
         <v>970</v>
@@ -11899,7 +11899,7 @@
         <v>10.5</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AU45" t="n">
         <v>7.2</v>
@@ -11911,31 +11911,31 @@
         <v>13</v>
       </c>
       <c r="AX45" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AY45" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AZ45" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BA45" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG45" t="n">
         <v>7.4</v>
@@ -11944,7 +11944,7 @@
         <v>3.5</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G46" t="n">
         <v>2.74</v>
@@ -12045,7 +12045,7 @@
         <v>3.2</v>
       </c>
       <c r="J46" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K46" t="n">
         <v>3.4</v>
@@ -12060,10 +12060,10 @@
         <v>3.2</v>
       </c>
       <c r="O46" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P46" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q46" t="n">
         <v>2.14</v>
@@ -12090,7 +12090,7 @@
         <v>13.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z46" t="n">
         <v>21</v>
@@ -12099,10 +12099,10 @@
         <v>55</v>
       </c>
       <c r="AB46" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD46" t="n">
         <v>14</v>
@@ -12123,7 +12123,7 @@
         <v>55</v>
       </c>
       <c r="AJ46" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK46" t="n">
         <v>32</v>
@@ -12150,7 +12150,7 @@
         <v>17.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT46" t="n">
         <v>8.4</v>
@@ -12162,7 +12162,7 @@
         <v>11.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX46" t="n">
         <v>14.5</v>
@@ -12174,61 +12174,61 @@
         <v>14</v>
       </c>
       <c r="BA46" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BB46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF46" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC46" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG46" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BH46" t="n">
         <v>3.15</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ46" t="n">
         <v>10</v>
       </c>
       <c r="BK46" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN46" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO46" t="n">
         <v>4.3</v>
       </c>
       <c r="BP46" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT46" t="n">
         <v>6.2</v>
@@ -12240,23 +12240,23 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
       </c>
       <c r="BY46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ46" t="n">
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -12290,13 +12290,13 @@
         <v>2.48</v>
       </c>
       <c r="G47" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H47" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J47" t="n">
         <v>3.35</v>
@@ -12308,13 +12308,13 @@
         <v>1.47</v>
       </c>
       <c r="M47" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N47" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P47" t="n">
         <v>1.77</v>
@@ -12326,19 +12326,19 @@
         <v>1.28</v>
       </c>
       <c r="S47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
         <v>1.87</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V47" t="n">
         <v>1.44</v>
       </c>
       <c r="W47" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X47" t="n">
         <v>14.5</v>
@@ -12353,7 +12353,7 @@
         <v>55</v>
       </c>
       <c r="AB47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC47" t="n">
         <v>970</v>
@@ -12362,7 +12362,7 @@
         <v>16.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF47" t="n">
         <v>970</v>
@@ -12377,13 +12377,13 @@
         <v>65</v>
       </c>
       <c r="AJ47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK47" t="n">
         <v>32</v>
       </c>
       <c r="AL47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM47" t="n">
         <v>140</v>
@@ -12395,19 +12395,19 @@
         <v>42</v>
       </c>
       <c r="AP47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR47" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS47" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AT47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU47" t="n">
         <v>6.8</v>
@@ -12416,37 +12416,37 @@
         <v>11.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX47" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY47" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ47" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA47" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BB47" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE47" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF47" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG47" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BH47" t="n">
         <v>3.1</v>
@@ -12464,7 +12464,7 @@
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BN47" t="n">
         <v>5.4</v>
@@ -12506,11 +12506,11 @@
         <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -12544,16 +12544,16 @@
         <v>2.3</v>
       </c>
       <c r="G48" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H48" t="n">
         <v>3.45</v>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K48" t="n">
         <v>3.4</v>
@@ -12574,13 +12574,13 @@
         <v>1.62</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R48" t="n">
         <v>1.23</v>
       </c>
       <c r="S48" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T48" t="n">
         <v>1.98</v>
@@ -12589,10 +12589,10 @@
         <v>1.87</v>
       </c>
       <c r="V48" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="X48" t="n">
         <v>11.5</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -12837,10 +12837,10 @@
         <v>3.55</v>
       </c>
       <c r="T49" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U49" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V49" t="n">
         <v>1.52</v>
@@ -12849,25 +12849,25 @@
         <v>1.34</v>
       </c>
       <c r="X49" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y49" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA49" t="n">
         <v>44</v>
       </c>
       <c r="AB49" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC49" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD49" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE49" t="n">
         <v>38</v>
@@ -12876,7 +12876,7 @@
         <v>26</v>
       </c>
       <c r="AG49" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH49" t="n">
         <v>950</v>
@@ -12903,58 +12903,58 @@
         <v>36</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH49" t="n">
         <v>4.7</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.08</v>
       </c>
       <c r="G50" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H50" t="n">
         <v>4.2</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -13303,16 +13303,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G51" t="n">
         <v>2.88</v>
       </c>
       <c r="H51" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I51" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>3.4</v>
@@ -13345,13 +13345,13 @@
         <v>3.65</v>
       </c>
       <c r="T51" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="U51" t="n">
         <v>2.12</v>
       </c>
       <c r="V51" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W51" t="n">
         <v>1.53</v>
@@ -13384,10 +13384,10 @@
         <v>19.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH51" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI51" t="n">
         <v>48</v>
@@ -13420,7 +13420,7 @@
         <v>16</v>
       </c>
       <c r="AS51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT51" t="n">
         <v>9.199999999999999</v>
@@ -13441,28 +13441,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC51" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD51" t="n">
         <v>32</v>
       </c>
       <c r="BE51" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF51" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG51" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH51" t="n">
         <v>3.4</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -13560,61 +13560,61 @@
         <v>1.97</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H52" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I52" t="n">
         <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L52" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N52" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="P52" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="R52" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S52" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="T52" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U52" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V52" t="n">
         <v>1.25</v>
       </c>
       <c r="W52" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="X52" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y52" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z52" t="n">
         <v>38</v>
@@ -13623,19 +13623,19 @@
         <v>130</v>
       </c>
       <c r="AB52" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE52" t="n">
         <v>85</v>
       </c>
       <c r="AF52" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG52" t="n">
         <v>12.5</v>
@@ -13644,52 +13644,52 @@
         <v>26</v>
       </c>
       <c r="AI52" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ52" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK52" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL52" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM52" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AN52" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO52" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AP52" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ52" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR52" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS52" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS52" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AT52" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU52" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV52" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW52" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX52" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY52" t="n">
         <v>9</v>
@@ -13698,34 +13698,34 @@
         <v>17</v>
       </c>
       <c r="BA52" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB52" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF52" t="n">
         <v>19</v>
       </c>
-      <c r="BC52" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG52" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH52" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BJ52" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK52" t="n">
         <v>5.9</v>
@@ -13743,19 +13743,19 @@
         <v>3.6</v>
       </c>
       <c r="BP52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BQ52" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT52" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU52" t="n">
         <v>4.8</v>
@@ -13770,17 +13770,17 @@
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -13811,16 +13811,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="G53" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H53" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I53" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J53" t="n">
         <v>3.1</v>
@@ -13829,67 +13829,67 @@
         <v>3.6</v>
       </c>
       <c r="L53" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M53" t="n">
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O53" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S53" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T53" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U53" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V53" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W53" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="X53" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y53" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA53" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB53" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC53" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE53" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF53" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG53" t="n">
         <v>13.5</v>
@@ -13898,13 +13898,13 @@
         <v>32</v>
       </c>
       <c r="AI53" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ53" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK53" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL53" t="n">
         <v>70</v>
@@ -13913,52 +13913,52 @@
         <v>250</v>
       </c>
       <c r="AN53" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO53" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP53" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ53" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR53" t="n">
         <v>4</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT53" t="n">
         <v>5</v>
       </c>
       <c r="AU53" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AV53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW53" t="n">
         <v>4.2</v>
       </c>
       <c r="AX53" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY53" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ53" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA53" t="n">
         <v>4.2</v>
       </c>
       <c r="BB53" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC53" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD53" t="n">
         <v>4.1</v>
@@ -13967,16 +13967,16 @@
         <v>4.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BG53" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH53" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI53" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ53" t="n">
         <v>12.5</v>
@@ -13991,16 +13991,16 @@
         <v>10</v>
       </c>
       <c r="BN53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP53" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ53" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
@@ -14009,32 +14009,32 @@
         <v>8.6</v>
       </c>
       <c r="BT53" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA53" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BU53" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW53" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY53" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G54" t="n">
         <v>2.4</v>
@@ -14074,43 +14074,43 @@
         <v>3.45</v>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K54" t="n">
         <v>3.65</v>
       </c>
       <c r="L54" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
       </c>
       <c r="N54" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O54" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R54" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S54" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T54" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V54" t="n">
         <v>1.33</v>
@@ -14128,25 +14128,25 @@
         <v>32</v>
       </c>
       <c r="AA54" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB54" t="n">
         <v>11</v>
       </c>
       <c r="AC54" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD54" t="n">
         <v>970</v>
       </c>
       <c r="AE54" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF54" t="n">
         <v>17</v>
       </c>
       <c r="AG54" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH54" t="n">
         <v>950</v>
@@ -14158,46 +14158,46 @@
         <v>36</v>
       </c>
       <c r="AK54" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL54" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM54" t="n">
         <v>130</v>
       </c>
       <c r="AN54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO54" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP54" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ54" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR54" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT54" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU54" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV54" t="n">
         <v>11</v>
       </c>
       <c r="AW54" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX54" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY54" t="n">
         <v>8.199999999999999</v>
@@ -14206,31 +14206,31 @@
         <v>13.5</v>
       </c>
       <c r="BA54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC54" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB54" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD54" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE54" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF54" t="n">
         <v>15</v>
       </c>
       <c r="BG54" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH54" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="BJ54" t="n">
         <v>10.5</v>
@@ -14278,7 +14278,7 @@
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ54" t="n">
         <v>0</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -14319,10 +14319,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="G55" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H55" t="n">
         <v>13</v>
@@ -14334,10 +14334,10 @@
         <v>4.7</v>
       </c>
       <c r="K55" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L55" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M55" t="n">
         <v>1.08</v>
@@ -14367,10 +14367,10 @@
         <v>1.52</v>
       </c>
       <c r="V55" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W55" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X55" t="n">
         <v>14.5</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H56" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I56" t="n">
         <v>5.5</v>
@@ -14591,55 +14591,55 @@
         <v>3.75</v>
       </c>
       <c r="L56" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M56" t="n">
         <v>1.09</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O56" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="R56" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S56" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T56" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="U56" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V56" t="n">
         <v>1.22</v>
       </c>
       <c r="W56" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="X56" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y56" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z56" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AA56" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB56" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC56" t="n">
         <v>9</v>
@@ -14648,155 +14648,155 @@
         <v>22</v>
       </c>
       <c r="AE56" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF56" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG56" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH56" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI56" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ56" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK56" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL56" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN56" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AO56" t="n">
         <v>110</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BF56" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BH56" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BJ56" t="n">
         <v>1000</v>
       </c>
       <c r="BK56" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>8.800000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="BN56" t="n">
         <v>4.7</v>
       </c>
       <c r="BO56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ56" t="n">
         <v>3.65</v>
       </c>
-      <c r="BP56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ56" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>8.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="BT56" t="n">
         <v>1000</v>
       </c>
       <c r="BU56" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>8.800000000000001</v>
+        <v>2.38</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>8.800000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>9.199999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-25.xlsx
@@ -860,10 +860,10 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
         <v>2.2</v>
@@ -875,46 +875,46 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V2" t="n">
         <v>1.84</v>
       </c>
       <c r="W2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
         <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z2" t="n">
         <v>13</v>
@@ -938,7 +938,7 @@
         <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -947,13 +947,13 @@
         <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="n">
         <v>160</v>
       </c>
       <c r="AL2" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -965,16 +965,16 @@
         <v>25</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
@@ -986,22 +986,22 @@
         <v>9.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
         <v>8.6</v>
@@ -1010,19 +1010,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="n">
         <v>2.98</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="BN2" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1111,40 +1111,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.37</v>
@@ -1162,16 +1162,16 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z3" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AA3" t="n">
         <v>210</v>
@@ -1180,7 +1180,7 @@
         <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
         <v>950</v>
@@ -1192,7 +1192,7 @@
         <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
         <v>950</v>
@@ -1216,31 +1216,31 @@
         <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AV3" t="n">
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
@@ -1249,10 +1249,10 @@
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
         <v>7.6</v>
@@ -1261,16 +1261,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BD3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF3" t="n">
         <v>8.6</v>
       </c>
-      <c r="BE3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="n">
         <v>3.45</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.73</v>
+        <v>110</v>
       </c>
       <c r="BN3" t="n">
         <v>4.1</v>
@@ -1297,10 +1297,10 @@
         <v>3.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>460</v>
+        <v>27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>3.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BU3" t="n">
         <v>6.2</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1413,28 +1413,28 @@
         <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="W4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
         <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1443,7 +1443,7 @@
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
         <v>16</v>
@@ -1455,7 +1455,7 @@
         <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
         <v>120</v>
@@ -1473,31 +1473,31 @@
         <v>15</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR4" t="n">
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
         <v>12.5</v>
@@ -1506,22 +1506,22 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC4" t="n">
         <v>16</v>
       </c>
-      <c r="BB4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BE4" t="n">
         <v>22</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="BG4" t="n">
         <v>12</v>
@@ -1548,7 +1548,7 @@
         <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>5</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV4" t="n">
         <v>14.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1667,7 +1667,7 @@
         <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
         <v>2.4</v>
@@ -1679,10 +1679,10 @@
         <v>950</v>
       </c>
       <c r="Z5" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AB5" t="n">
         <v>46</v>
@@ -1694,7 +1694,7 @@
         <v>40</v>
       </c>
       <c r="AE5" t="n">
-        <v>330</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
         <v>40</v>
@@ -1706,7 +1706,7 @@
         <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
         <v>180</v>
@@ -1715,7 +1715,7 @@
         <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1727,16 +1727,16 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.78</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.88</v>
+        <v>9.6</v>
       </c>
       <c r="AX5" t="n">
         <v>6.2</v>
@@ -1757,10 +1757,10 @@
         <v>5.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
         <v>8.4</v>
@@ -1772,7 +1772,7 @@
         <v>14.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>5.2</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
@@ -1915,7 +1915,7 @@
         <v>2.12</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1924,7 +1924,7 @@
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X6" t="n">
         <v>40</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -2145,13 +2145,13 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.21</v>
@@ -2160,22 +2160,22 @@
         <v>2.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W7" t="n">
         <v>1.44</v>
@@ -2187,7 +2187,7 @@
         <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
         <v>30</v>
@@ -2199,7 +2199,7 @@
         <v>9.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -2235,7 +2235,7 @@
         <v>12.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
         <v>12.5</v>
@@ -2244,10 +2244,10 @@
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU7" t="n">
         <v>8.4</v>
@@ -2268,22 +2268,22 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BF7" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
         <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
         <v>5.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
         <v>2.54</v>
@@ -2653,13 +2653,13 @@
         <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O9" t="n">
         <v>1.17</v>
@@ -2695,7 +2695,7 @@
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
@@ -2707,13 +2707,13 @@
         <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
         <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
@@ -2725,7 +2725,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>75</v>
@@ -2737,25 +2737,25 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
@@ -2764,10 +2764,10 @@
         <v>7</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
@@ -2776,25 +2776,25 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="n">
         <v>4.8</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BN9" t="n">
         <v>6.8</v>
@@ -2830,7 +2830,7 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BT9" t="n">
         <v>6.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
         <v>3.75</v>
@@ -2922,7 +2922,7 @@
         <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
         <v>1.43</v>
@@ -2934,10 +2934,10 @@
         <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
         <v>1.86</v>
@@ -2958,7 +2958,7 @@
         <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>19</v>
@@ -3006,7 +3006,7 @@
         <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -3018,19 +3018,19 @@
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
@@ -3048,43 +3048,43 @@
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
         <v>5.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR10" t="n">
         <v>28</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT10" t="n">
         <v>7.2</v>
@@ -3096,10 +3096,10 @@
         <v>29</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BY10" t="n">
         <v>8.4</v>
@@ -3108,11 +3108,11 @@
         <v>23</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H11" t="n">
         <v>5.9</v>
@@ -3176,7 +3176,7 @@
         <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
@@ -3251,7 +3251,7 @@
         <v>410</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>19.5</v>
@@ -3263,10 +3263,10 @@
         <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AV11" t="n">
         <v>18</v>
@@ -3275,19 +3275,19 @@
         <v>5.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
         <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
         <v>11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3457,7 +3457,7 @@
         <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
@@ -3469,13 +3469,13 @@
         <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="n">
         <v>21</v>
@@ -3499,100 +3499,100 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.4</v>
       </c>
       <c r="AR12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BA12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB12" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BC12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG12" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>6.2</v>
       </c>
       <c r="BH12" t="n">
         <v>4.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO12" t="n">
         <v>4.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT12" t="n">
         <v>7.4</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -3657,16 +3657,16 @@
         <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>1.45</v>
@@ -3678,7 +3678,7 @@
         <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
         <v>1.68</v>
@@ -3702,7 +3702,7 @@
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -3720,7 +3720,7 @@
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>13.5</v>
@@ -3756,7 +3756,7 @@
         <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
         <v>8.4</v>
@@ -3780,7 +3780,7 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
         <v>16</v>
@@ -3789,28 +3789,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
         <v>34</v>
       </c>
       <c r="BB13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC13" t="n">
-        <v>6</v>
-      </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
         <v>30</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>3.2</v>
@@ -3822,7 +3822,7 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -3905,28 +3905,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
         <v>2.42</v>
       </c>
       <c r="I14" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
         <v>3.15</v>
@@ -3950,13 +3950,13 @@
         <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
@@ -3968,7 +3968,7 @@
         <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
         <v>19</v>
@@ -3980,10 +3980,10 @@
         <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
         <v>26</v>
@@ -3992,25 +3992,25 @@
         <v>60</v>
       </c>
       <c r="AI14" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AO14" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
         <v>9.199999999999999</v>
@@ -4022,10 +4022,10 @@
         <v>11</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
         <v>5.9</v>
@@ -4034,37 +4034,37 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX14" t="n">
         <v>17.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD14" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD14" t="n">
+      <c r="BE14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7</v>
-      </c>
       <c r="BG14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="n">
         <v>3.3</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
         <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
         <v>1.58</v>
@@ -4210,7 +4210,7 @@
         <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X15" t="n">
         <v>26</v>
@@ -4225,10 +4225,10 @@
         <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
         <v>19</v>
@@ -4237,10 +4237,10 @@
         <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
@@ -4252,7 +4252,7 @@
         <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -4264,7 +4264,7 @@
         <v>8.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
         <v>18</v>
@@ -4276,7 +4276,7 @@
         <v>32</v>
       </c>
       <c r="AS15" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
@@ -4291,7 +4291,7 @@
         <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
@@ -4309,13 +4309,13 @@
         <v>14.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
         <v>23</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
         <v>2.28</v>
@@ -4431,7 +4431,7 @@
         <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4440,22 +4440,22 @@
         <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
         <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
         <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U16" t="n">
         <v>2.48</v>
@@ -4464,7 +4464,7 @@
         <v>1.74</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
         <v>23</v>
@@ -4530,7 +4530,7 @@
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT16" t="n">
         <v>11</v>
@@ -4554,10 +4554,10 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
         <v>14.5</v>
@@ -4566,7 +4566,7 @@
         <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
         <v>20</v>
@@ -4614,7 +4614,7 @@
         <v>5.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV16" t="n">
         <v>16</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H17" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
@@ -4685,7 +4685,7 @@
         <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -4697,13 +4697,13 @@
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
         <v>3.05</v>
@@ -4715,10 +4715,10 @@
         <v>2.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X17" t="n">
         <v>18</v>
@@ -4727,10 +4727,10 @@
         <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA17" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AB17" t="n">
         <v>12.5</v>
@@ -4769,7 +4769,7 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
@@ -4778,7 +4778,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
         <v>19</v>
@@ -4796,13 +4796,13 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AX17" t="n">
         <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
@@ -4817,7 +4817,7 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE17" t="n">
         <v>34</v>
@@ -4838,49 +4838,49 @@
         <v>9.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ17" t="n">
         <v>6.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT17" t="n">
         <v>6.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW17" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX17" t="n">
         <v>34</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
         <v>5.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P18" t="n">
         <v>2.66</v>
@@ -5065,7 +5065,7 @@
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC18" t="n">
         <v>18</v>
@@ -5074,7 +5074,7 @@
         <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
         <v>13</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G19" t="n">
         <v>2.44</v>
@@ -5190,7 +5190,7 @@
         <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.19</v>
@@ -5217,16 +5217,16 @@
         <v>1.95</v>
       </c>
       <c r="T19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U19" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5271,31 +5271,31 @@
         <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AM19" t="n">
         <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
@@ -5307,34 +5307,34 @@
         <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="AY19" t="n">
         <v>7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
         <v>18.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="n">
         <v>5.5</v>
@@ -5346,7 +5346,7 @@
         <v>8.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5376,13 +5376,13 @@
         <v>7</v>
       </c>
       <c r="BU19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
@@ -5394,11 +5394,11 @@
         <v>12.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
         <v>3.95</v>
@@ -5468,19 +5468,19 @@
         <v>1.75</v>
       </c>
       <c r="S20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T20" t="n">
         <v>1.49</v>
       </c>
       <c r="U20" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X20" t="n">
         <v>32</v>
@@ -5489,13 +5489,13 @@
         <v>25</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA20" t="n">
         <v>160</v>
       </c>
       <c r="AB20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -5522,7 +5522,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -5546,7 +5546,7 @@
         <v>26</v>
       </c>
       <c r="AS20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
         <v>15</v>
@@ -5570,7 +5570,7 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB20" t="n">
         <v>26</v>
@@ -5585,7 +5585,7 @@
         <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG20" t="n">
         <v>16</v>
@@ -5600,40 +5600,40 @@
         <v>8.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP20" t="n">
         <v>14</v>
       </c>
       <c r="BQ20" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BR20" t="n">
         <v>21</v>
       </c>
       <c r="BS20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU20" t="n">
         <v>5.3</v>
       </c>
       <c r="BV20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW20" t="n">
         <v>9.199999999999999</v>
@@ -5642,17 +5642,17 @@
         <v>26</v>
       </c>
       <c r="BY20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>13.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -5848,7 +5848,7 @@
         <v>4.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -5943,16 +5943,16 @@
         <v>1.5</v>
       </c>
       <c r="H22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>4.9</v>
       </c>
       <c r="K22" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.24</v>
@@ -5967,7 +5967,7 @@
         <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q22" t="n">
         <v>1.61</v>
@@ -5994,7 +5994,7 @@
         <v>26</v>
       </c>
       <c r="Y22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z22" t="n">
         <v>160</v>
@@ -6039,22 +6039,22 @@
         <v>320</v>
       </c>
       <c r="AN22" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AO22" t="n">
         <v>120</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AR22" t="n">
         <v>46</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
         <v>9.6</v>
@@ -6063,10 +6063,10 @@
         <v>10.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -6078,7 +6078,7 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
         <v>11.5</v>
@@ -6087,16 +6087,16 @@
         <v>12.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BF22" t="n">
         <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BH22" t="n">
         <v>4.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>7.2</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
         <v>5.4</v>
@@ -6230,7 +6230,7 @@
         <v>1.82</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
         <v>1.58</v>
@@ -6356,7 +6356,7 @@
         <v>5.3</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.800000000000001</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K24" t="n">
         <v>3.5</v>
@@ -6586,7 +6586,7 @@
         <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB24" t="n">
         <v>16</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H25" t="n">
         <v>3.75</v>
@@ -6711,7 +6711,7 @@
         <v>4.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
         <v>3.7</v>
@@ -6738,7 +6738,7 @@
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T25" t="n">
         <v>1.8</v>
@@ -6750,7 +6750,7 @@
         <v>1.32</v>
       </c>
       <c r="W25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X25" t="n">
         <v>14.5</v>
@@ -6861,7 +6861,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI25" t="n">
         <v>2.74</v>
@@ -6870,31 +6870,31 @@
         <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN25" t="n">
         <v>5.1</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP25" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT25" t="n">
         <v>7.4</v>
@@ -6906,23 +6906,23 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
         <v>7.6</v>
       </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>7.4</v>
-      </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
         <v>1.36</v>
       </c>
       <c r="P26" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
         <v>2.06</v>
@@ -6992,7 +6992,7 @@
         <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
         <v>1.84</v>
@@ -7025,7 +7025,7 @@
         <v>14</v>
       </c>
       <c r="AD26" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE26" t="n">
         <v>65</v>
@@ -7067,52 +7067,52 @@
         <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU26" t="n">
         <v>3.95</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AX26" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="AY26" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.02</v>
+        <v>3.35</v>
       </c>
       <c r="BH26" t="n">
         <v>5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
         <v>4.7</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ27" t="n">
         <v>8.6</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="G28" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="H28" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
@@ -7485,13 +7485,13 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.69</v>
@@ -7500,19 +7500,19 @@
         <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U28" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="X28" t="n">
         <v>970</v>
@@ -7530,7 +7530,7 @@
         <v>15.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -7542,19 +7542,19 @@
         <v>21</v>
       </c>
       <c r="AG28" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK28" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
         <v>500</v>
@@ -7563,28 +7563,28 @@
         <v>580</v>
       </c>
       <c r="AN28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO28" t="n">
         <v>970</v>
       </c>
-      <c r="AO28" t="n">
-        <v>55</v>
-      </c>
       <c r="AP28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
         <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV28" t="n">
         <v>7.6</v>
@@ -7599,92 +7599,92 @@
         <v>6.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD28" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD28" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF28" t="n">
         <v>12</v>
       </c>
       <c r="BG28" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BH28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BN28" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
         <v>2.68</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R29" t="n">
         <v>1.69</v>
@@ -7823,31 +7823,31 @@
         <v>270</v>
       </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AS29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX29" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>12</v>
       </c>
       <c r="AY29" t="n">
         <v>8.800000000000001</v>
@@ -7856,7 +7856,7 @@
         <v>12</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BB29" t="n">
         <v>14.5</v>
@@ -7865,10 +7865,10 @@
         <v>13.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BF29" t="n">
         <v>6.6</v>
@@ -7886,7 +7886,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK29" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7898,7 +7898,7 @@
         <v>5.3</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP29" t="n">
         <v>12.5</v>
@@ -7934,11 +7934,11 @@
         <v>14</v>
       </c>
       <c r="CA29" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -7984,7 +7984,7 @@
         <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
         <v>1.43</v>
@@ -8011,19 +8011,19 @@
         <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V30" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y30" t="n">
         <v>27</v>
@@ -8098,7 +8098,7 @@
         <v>7.8</v>
       </c>
       <c r="AW30" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX30" t="n">
         <v>11.5</v>
@@ -8107,22 +8107,22 @@
         <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC30" t="n">
         <v>8.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF30" t="n">
         <v>7.2</v>
@@ -8131,58 +8131,58 @@
         <v>12.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ30" t="n">
         <v>10</v>
       </c>
       <c r="BK30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.68</v>
+        <v>10</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO30" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.63</v>
+        <v>8</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.7</v>
+        <v>10</v>
       </c>
       <c r="BT30" t="n">
         <v>4.8</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.62</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
         <v>6.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
         <v>1.04</v>
@@ -8265,7 +8265,7 @@
         <v>2.74</v>
       </c>
       <c r="T31" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U31" t="n">
         <v>1.75</v>
@@ -8379,10 +8379,10 @@
         <v>7.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="n">
         <v>4.1</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -8480,19 +8480,19 @@
         <v>2.32</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J32" t="n">
         <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L32" t="n">
         <v>1.32</v>
@@ -8501,13 +8501,13 @@
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O32" t="n">
         <v>1.29</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
         <v>1.83</v>
@@ -8522,13 +8522,13 @@
         <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
         <v>1.46</v>
       </c>
       <c r="W32" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X32" t="n">
         <v>21</v>
@@ -8537,7 +8537,7 @@
         <v>14</v>
       </c>
       <c r="Z32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
         <v>55</v>
@@ -8546,25 +8546,25 @@
         <v>11</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE32" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AF32" t="n">
         <v>16</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AJ32" t="n">
         <v>32</v>
@@ -8573,10 +8573,10 @@
         <v>25</v>
       </c>
       <c r="AL32" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AM32" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN32" t="n">
         <v>18</v>
@@ -8585,58 +8585,58 @@
         <v>32</v>
       </c>
       <c r="AP32" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AT32" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU32" t="n">
         <v>7.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AX32" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BB32" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BC32" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BD32" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BE32" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="BF32" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BG32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH32" t="n">
         <v>3.7</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
         <v>2.02</v>
       </c>
       <c r="S33" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="T33" t="n">
         <v>2.04</v>
@@ -8839,10 +8839,10 @@
         <v>380</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AR33" t="n">
         <v>9.6</v>
@@ -8854,10 +8854,10 @@
         <v>11</v>
       </c>
       <c r="AU33" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AW33" t="n">
         <v>9.800000000000001</v>
@@ -8869,7 +8869,7 @@
         <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BA33" t="n">
         <v>9.6</v>
@@ -8881,7 +8881,7 @@
         <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BE33" t="n">
         <v>9.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G34" t="n">
         <v>2.3</v>
@@ -9021,7 +9021,7 @@
         <v>2.08</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
         <v>1.05</v>
@@ -9081,7 +9081,7 @@
         <v>29</v>
       </c>
       <c r="AL34" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM34" t="n">
         <v>170</v>
@@ -9105,10 +9105,10 @@
         <v>5.8</v>
       </c>
       <c r="AT34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3.55</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.5</v>
       </c>
       <c r="AV34" t="n">
         <v>4.7</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
         <v>2.04</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I35" t="n">
         <v>5.2</v>
@@ -9350,7 +9350,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR35" t="n">
         <v>7.2</v>
@@ -9374,7 +9374,7 @@
         <v>5.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AZ35" t="n">
         <v>6.2</v>
@@ -9401,58 +9401,58 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="BJ35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK35" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BL35" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BN35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BP35" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BQ35" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BR35" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS35" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BT35" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BU35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BV35" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BW35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BX35" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY35" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
         <v>5.1</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS36" t="n">
         <v>6.4</v>
@@ -9619,16 +9619,16 @@
         <v>4.9</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW36" t="n">
         <v>6.2</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ36" t="n">
         <v>5.5</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -9747,13 +9747,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I37" t="n">
         <v>2.58</v>
@@ -9762,7 +9762,7 @@
         <v>3.6</v>
       </c>
       <c r="K37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L37" t="n">
         <v>1.31</v>
@@ -9771,25 +9771,25 @@
         <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
         <v>1.27</v>
       </c>
       <c r="P37" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
         <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U37" t="n">
         <v>2.36</v>
@@ -9798,10 +9798,10 @@
         <v>1.63</v>
       </c>
       <c r="W37" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X37" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y37" t="n">
         <v>14</v>
@@ -9813,10 +9813,10 @@
         <v>44</v>
       </c>
       <c r="AB37" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD37" t="n">
         <v>14</v>
@@ -9858,25 +9858,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR37" t="n">
         <v>15</v>
       </c>
       <c r="AS37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU37" t="n">
         <v>7.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AX37" t="n">
         <v>19</v>
@@ -9891,10 +9891,10 @@
         <v>23</v>
       </c>
       <c r="BB37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC37" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD37" t="n">
         <v>24</v>
@@ -9903,13 +9903,13 @@
         <v>34</v>
       </c>
       <c r="BF37" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG37" t="n">
         <v>17</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI37" t="n">
         <v>2.92</v>
@@ -9918,13 +9918,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN37" t="n">
         <v>6.2</v>
@@ -9936,13 +9936,13 @@
         <v>23</v>
       </c>
       <c r="BQ37" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR37" t="n">
         <v>34</v>
       </c>
       <c r="BS37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT37" t="n">
         <v>5.6</v>
@@ -9954,7 +9954,7 @@
         <v>18.5</v>
       </c>
       <c r="BW37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX37" t="n">
         <v>30</v>
@@ -9966,11 +9966,11 @@
         <v>24</v>
       </c>
       <c r="CA37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -10001,31 +10001,31 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G38" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H38" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I38" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M38" t="n">
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.35</v>
@@ -10034,25 +10034,25 @@
         <v>1.86</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R38" t="n">
         <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T38" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U38" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V38" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X38" t="n">
         <v>13</v>
@@ -10070,7 +10070,7 @@
         <v>11.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD38" t="n">
         <v>12.5</v>
@@ -10079,7 +10079,7 @@
         <v>32</v>
       </c>
       <c r="AF38" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG38" t="n">
         <v>13</v>
@@ -10097,7 +10097,7 @@
         <v>38</v>
       </c>
       <c r="AL38" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AM38" t="n">
         <v>100</v>
@@ -10121,7 +10121,7 @@
         <v>36</v>
       </c>
       <c r="AT38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU38" t="n">
         <v>7</v>
@@ -10136,13 +10136,13 @@
         <v>17</v>
       </c>
       <c r="AY38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ38" t="n">
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BB38" t="n">
         <v>40</v>
@@ -10157,10 +10157,10 @@
         <v>36</v>
       </c>
       <c r="BF38" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG38" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BH38" t="n">
         <v>3.3</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>1.65</v>
       </c>
       <c r="G39" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H39" t="n">
         <v>5.1</v>
@@ -10267,10 +10267,10 @@
         <v>5.7</v>
       </c>
       <c r="J39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L39" t="n">
         <v>1.26</v>
@@ -10285,7 +10285,7 @@
         <v>1.2</v>
       </c>
       <c r="P39" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
         <v>1.59</v>
@@ -10306,7 +10306,7 @@
         <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X39" t="n">
         <v>26</v>
@@ -10327,7 +10327,7 @@
         <v>11</v>
       </c>
       <c r="AD39" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE39" t="n">
         <v>130</v>
@@ -10372,7 +10372,7 @@
         <v>32</v>
       </c>
       <c r="AS39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT39" t="n">
         <v>10</v>
@@ -10396,7 +10396,7 @@
         <v>16</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB39" t="n">
         <v>14.5</v>
@@ -10408,7 +10408,7 @@
         <v>14.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF39" t="n">
         <v>6.4</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -10509,16 +10509,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G40" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -10560,7 +10560,7 @@
         <v>1.31</v>
       </c>
       <c r="W40" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X40" t="n">
         <v>22</v>
@@ -10578,7 +10578,7 @@
         <v>12</v>
       </c>
       <c r="AC40" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
         <v>16.5</v>
@@ -10587,7 +10587,7 @@
         <v>120</v>
       </c>
       <c r="AF40" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG40" t="n">
         <v>10.5</v>
@@ -10611,16 +10611,16 @@
         <v>580</v>
       </c>
       <c r="AN40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="AP40" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR40" t="n">
         <v>20</v>
@@ -10635,7 +10635,7 @@
         <v>8.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW40" t="n">
         <v>25</v>
@@ -10647,7 +10647,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA40" t="n">
         <v>26</v>
@@ -10659,7 +10659,7 @@
         <v>16.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE40" t="n">
         <v>32</v>
@@ -10668,13 +10668,13 @@
         <v>9.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH40" t="n">
         <v>4.3</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.4</v>
@@ -10686,7 +10686,7 @@
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN40" t="n">
         <v>5.1</v>
@@ -10698,7 +10698,7 @@
         <v>13.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BR40" t="n">
         <v>24</v>
@@ -10707,16 +10707,16 @@
         <v>7</v>
       </c>
       <c r="BT40" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU40" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV40" t="n">
         <v>32</v>
       </c>
       <c r="BW40" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX40" t="n">
         <v>38</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -10763,25 +10763,25 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G41" t="n">
         <v>3.5</v>
       </c>
       <c r="H41" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="I41" t="n">
         <v>2.56</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K41" t="n">
         <v>3.6</v>
       </c>
       <c r="L41" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M41" t="n">
         <v>1.07</v>
@@ -10817,10 +10817,10 @@
         <v>1.4</v>
       </c>
       <c r="X41" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Y41" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z41" t="n">
         <v>970</v>
@@ -10835,7 +10835,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE41" t="n">
         <v>85</v>
@@ -10871,13 +10871,13 @@
         <v>55</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>5.1</v>
       </c>
       <c r="AR41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS41" t="n">
         <v>7.6</v>
@@ -10904,19 +10904,19 @@
         <v>10.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB41" t="n">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="BF41" t="n">
         <v>8</v>
@@ -10943,7 +10943,7 @@
         <v>1.56</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BO41" t="n">
         <v>5.1</v>
@@ -10964,13 +10964,13 @@
         <v>5.4</v>
       </c>
       <c r="BU41" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
@@ -10982,11 +10982,11 @@
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -11017,22 +11017,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G42" t="n">
         <v>2.64</v>
       </c>
       <c r="H42" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
         <v>4.5</v>
       </c>
       <c r="J42" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K42" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L42" t="n">
         <v>1.48</v>
@@ -11074,7 +11074,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y42" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="Z42" t="n">
         <v>95</v>
@@ -11089,7 +11089,7 @@
         <v>7</v>
       </c>
       <c r="AD42" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE42" t="n">
         <v>160</v>
@@ -11131,7 +11131,7 @@
         <v>10.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS42" t="n">
         <v>5.1</v>
@@ -11158,7 +11158,7 @@
         <v>12.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB42" t="n">
         <v>4.7</v>
@@ -11167,7 +11167,7 @@
         <v>22</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE42" t="n">
         <v>5.2</v>
@@ -11200,7 +11200,7 @@
         <v>5.6</v>
       </c>
       <c r="BO42" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
@@ -11233,14 +11233,14 @@
         <v>8</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA42" t="n">
         <v>7.8</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -11274,19 +11274,19 @@
         <v>1.64</v>
       </c>
       <c r="G43" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I43" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J43" t="n">
         <v>3.7</v>
       </c>
       <c r="K43" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L43" t="n">
         <v>1.3</v>
@@ -11313,7 +11313,7 @@
         <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U43" t="n">
         <v>1.87</v>
@@ -11322,7 +11322,7 @@
         <v>1.19</v>
       </c>
       <c r="W43" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X43" t="n">
         <v>90</v>
@@ -11334,7 +11334,7 @@
         <v>140</v>
       </c>
       <c r="AA43" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB43" t="n">
         <v>11</v>
@@ -11346,7 +11346,7 @@
         <v>950</v>
       </c>
       <c r="AE43" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF43" t="n">
         <v>12.5</v>
@@ -11358,7 +11358,7 @@
         <v>40</v>
       </c>
       <c r="AI43" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ43" t="n">
         <v>48</v>
@@ -11367,7 +11367,7 @@
         <v>970</v>
       </c>
       <c r="AL43" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM43" t="n">
         <v>580</v>
@@ -11376,16 +11376,16 @@
         <v>11.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP43" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS43" t="n">
         <v>4.2</v>
@@ -11400,7 +11400,7 @@
         <v>11.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX43" t="n">
         <v>7.8</v>
@@ -11412,16 +11412,16 @@
         <v>11</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BC43" t="n">
         <v>12.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE43" t="n">
         <v>26</v>
@@ -11430,28 +11430,28 @@
         <v>7.2</v>
       </c>
       <c r="BG43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BN43" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM43" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BN43" t="n">
-        <v>4.5</v>
       </c>
       <c r="BO43" t="n">
         <v>3.35</v>
@@ -11460,41 +11460,41 @@
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT43" t="n">
         <v>1000</v>
       </c>
       <c r="BU43" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>2.26</v>
+        <v>1.55</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
         <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BN45" t="n">
         <v>6.4</v>
@@ -11986,7 +11986,7 @@
         <v>32</v>
       </c>
       <c r="BW45" t="n">
-        <v>1.91</v>
+        <v>6.2</v>
       </c>
       <c r="BX45" t="n">
         <v>60</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -12033,46 +12033,46 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G46" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I46" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J46" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K46" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L46" t="n">
         <v>1.43</v>
       </c>
       <c r="M46" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O46" t="n">
         <v>1.36</v>
       </c>
       <c r="P46" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R46" t="n">
         <v>1.27</v>
       </c>
       <c r="S46" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T46" t="n">
         <v>2.14</v>
@@ -12081,10 +12081,10 @@
         <v>1.68</v>
       </c>
       <c r="V46" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W46" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="X46" t="n">
         <v>970</v>
@@ -12099,7 +12099,7 @@
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AC46" t="n">
         <v>42</v>
@@ -12111,10 +12111,10 @@
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AH46" t="n">
         <v>950</v>
@@ -12141,13 +12141,13 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR46" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS46" t="n">
         <v>4.2</v>
@@ -12156,40 +12156,40 @@
         <v>4.4</v>
       </c>
       <c r="AU46" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AV46" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AW46" t="n">
         <v>4.2</v>
       </c>
       <c r="AX46" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY46" t="n">
         <v>4.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA46" t="n">
         <v>4.2</v>
       </c>
       <c r="BB46" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC46" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="BF46" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG46" t="n">
         <v>4.2</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -12795,25 +12795,25 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G49" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J49" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
         <v>3.4</v>
       </c>
       <c r="L49" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
@@ -12843,10 +12843,10 @@
         <v>2.02</v>
       </c>
       <c r="V49" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W49" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X49" t="n">
         <v>13</v>
@@ -12873,7 +12873,7 @@
         <v>40</v>
       </c>
       <c r="AF49" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG49" t="n">
         <v>12.5</v>
@@ -12912,7 +12912,7 @@
         <v>17.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT49" t="n">
         <v>8.6</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
         <v>2.6</v>
       </c>
       <c r="H50" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I50" t="n">
         <v>3.25</v>
@@ -13067,7 +13067,7 @@
         <v>3.45</v>
       </c>
       <c r="L50" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="M50" t="n">
         <v>1.08</v>
@@ -13082,7 +13082,7 @@
         <v>1.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R50" t="n">
         <v>1.28</v>
@@ -13097,7 +13097,7 @@
         <v>2.08</v>
       </c>
       <c r="V50" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W50" t="n">
         <v>1.62</v>
@@ -13115,7 +13115,7 @@
         <v>900</v>
       </c>
       <c r="AB50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC50" t="n">
         <v>13</v>
@@ -13166,7 +13166,7 @@
         <v>15.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT50" t="n">
         <v>8.4</v>
@@ -13178,7 +13178,7 @@
         <v>11.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX50" t="n">
         <v>7.6</v>
@@ -13190,10 +13190,10 @@
         <v>10.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB50" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC50" t="n">
         <v>22</v>
@@ -13202,10 +13202,10 @@
         <v>32</v>
       </c>
       <c r="BE50" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF50" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG50" t="n">
         <v>30</v>
@@ -13226,7 +13226,7 @@
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BN50" t="n">
         <v>5.4</v>
@@ -13268,11 +13268,11 @@
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -13333,7 +13333,7 @@
         <v>1.46</v>
       </c>
       <c r="P51" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="Q51" t="n">
         <v>2.36</v>
@@ -13417,7 +13417,7 @@
         <v>5.8</v>
       </c>
       <c r="AR51" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS51" t="n">
         <v>7</v>
@@ -13441,7 +13441,7 @@
         <v>10</v>
       </c>
       <c r="AZ51" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BA51" t="n">
         <v>7</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
         <v>21</v>
       </c>
       <c r="AC52" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AD52" t="n">
         <v>970</v>
@@ -13674,7 +13674,7 @@
         <v>4.9</v>
       </c>
       <c r="AS52" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AT52" t="n">
         <v>4.3</v>
@@ -13689,7 +13689,7 @@
         <v>5.7</v>
       </c>
       <c r="AX52" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY52" t="n">
         <v>4.9</v>
@@ -13698,25 +13698,25 @@
         <v>5.2</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="BB52" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="BC52" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF52" t="n">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="BG52" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH52" t="n">
         <v>4.7</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -13853,7 +13853,7 @@
         <v>5.3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U53" t="n">
         <v>1.83</v>
@@ -13865,10 +13865,10 @@
         <v>1.84</v>
       </c>
       <c r="X53" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
         <v>34</v>
@@ -13916,7 +13916,7 @@
         <v>28</v>
       </c>
       <c r="AO53" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AP53" t="n">
         <v>8.4</v>
@@ -13925,10 +13925,10 @@
         <v>10</v>
       </c>
       <c r="AR53" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AS53" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT53" t="n">
         <v>6</v>
@@ -13940,7 +13940,7 @@
         <v>16</v>
       </c>
       <c r="AW53" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AX53" t="n">
         <v>10</v>
@@ -13952,7 +13952,7 @@
         <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB53" t="n">
         <v>23</v>
@@ -13961,16 +13961,16 @@
         <v>24</v>
       </c>
       <c r="BD53" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG53" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG53" t="n">
-        <v>9</v>
       </c>
       <c r="BH53" t="n">
         <v>2.86</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -14083,25 +14083,25 @@
         <v>3.5</v>
       </c>
       <c r="L54" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
       </c>
       <c r="N54" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O54" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P54" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R54" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S54" t="n">
         <v>3.8</v>
@@ -14110,7 +14110,7 @@
         <v>1.82</v>
       </c>
       <c r="U54" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V54" t="n">
         <v>1.52</v>
@@ -14119,7 +14119,7 @@
         <v>1.55</v>
       </c>
       <c r="X54" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Y54" t="n">
         <v>11.5</v>
@@ -14149,7 +14149,7 @@
         <v>13</v>
       </c>
       <c r="AH54" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI54" t="n">
         <v>48</v>
@@ -14161,31 +14161,31 @@
         <v>34</v>
       </c>
       <c r="AL54" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ54" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR54" t="n">
         <v>16</v>
       </c>
       <c r="AS54" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AT54" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU54" t="n">
         <v>6.8</v>
@@ -14206,43 +14206,43 @@
         <v>14.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BB54" t="n">
         <v>32</v>
       </c>
       <c r="BC54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD54" t="n">
         <v>8.6</v>
       </c>
-      <c r="BD54" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BE54" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF54" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG54" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH54" t="n">
         <v>3.35</v>
       </c>
       <c r="BI54" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ54" t="n">
         <v>10</v>
       </c>
       <c r="BK54" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN54" t="n">
         <v>5.9</v>
@@ -14251,44 +14251,44 @@
         <v>4.5</v>
       </c>
       <c r="BP54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ54" t="n">
         <v>7.2</v>
       </c>
       <c r="BR54" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS54" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT54" t="n">
         <v>6.2</v>
       </c>
       <c r="BU54" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV54" t="n">
         <v>24</v>
       </c>
       <c r="BW54" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX54" t="n">
         <v>38</v>
       </c>
       <c r="BY54" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ54" t="n">
         <v>32</v>
       </c>
       <c r="CA54" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -14322,13 +14322,13 @@
         <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H55" t="n">
         <v>4.3</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>3.05</v>
@@ -14346,7 +14346,7 @@
         <v>2.58</v>
       </c>
       <c r="O55" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P55" t="n">
         <v>1.56</v>
@@ -14361,7 +14361,7 @@
         <v>5.5</v>
       </c>
       <c r="T55" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U55" t="n">
         <v>1.72</v>
@@ -14373,7 +14373,7 @@
         <v>1.87</v>
       </c>
       <c r="X55" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y55" t="n">
         <v>14</v>
@@ -14433,13 +14433,13 @@
         <v>9.4</v>
       </c>
       <c r="AR55" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS55" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT55" t="n">
         <v>6</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>5.8</v>
       </c>
       <c r="AU55" t="n">
         <v>6.8</v>
@@ -14460,7 +14460,7 @@
         <v>17</v>
       </c>
       <c r="BA55" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB55" t="n">
         <v>19.5</v>
@@ -14469,13 +14469,13 @@
         <v>20</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE55" t="n">
         <v>6.2</v>
       </c>
       <c r="BF55" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG55" t="n">
         <v>6.2</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -14687,16 +14687,16 @@
         <v>9.6</v>
       </c>
       <c r="AR56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS56" t="n">
         <v>4.3</v>
       </c>
       <c r="AT56" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AU56" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV56" t="n">
         <v>15.5</v>
@@ -14723,7 +14723,7 @@
         <v>19.5</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE56" t="n">
         <v>4.3</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -14827,10 +14827,10 @@
         </is>
       </c>
       <c r="F57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G57" t="n">
         <v>1.38</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1.39</v>
       </c>
       <c r="H57" t="n">
         <v>13</v>
@@ -14842,13 +14842,13 @@
         <v>4.8</v>
       </c>
       <c r="K57" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L57" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M57" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N57" t="n">
         <v>3.3</v>
@@ -14866,7 +14866,7 @@
         <v>1.29</v>
       </c>
       <c r="S57" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T57" t="n">
         <v>2.56</v>
@@ -14875,7 +14875,7 @@
         <v>1.53</v>
       </c>
       <c r="V57" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W57" t="n">
         <v>3.55</v>
@@ -15016,7 +15016,7 @@
         <v>8.4</v>
       </c>
       <c r="BQ57" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BR57" t="n">
         <v>34</v>
@@ -15028,7 +15028,7 @@
         <v>16.5</v>
       </c>
       <c r="BU57" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BV57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
         <v>3.75</v>
       </c>
       <c r="L58" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M58" t="n">
         <v>1.08</v>
@@ -15195,7 +15195,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR58" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="AS58" t="n">
         <v>4.9</v>
@@ -15207,7 +15207,7 @@
         <v>6</v>
       </c>
       <c r="AV58" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="AW58" t="n">
         <v>4.7</v>
@@ -15225,13 +15225,13 @@
         <v>4.8</v>
       </c>
       <c r="BB58" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BC58" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE58" t="n">
         <v>5</v>
@@ -15246,7 +15246,7 @@
         <v>3.4</v>
       </c>
       <c r="BI58" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ58" t="n">
         <v>10.5</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -15341,46 +15341,46 @@
         <v>2.02</v>
       </c>
       <c r="H59" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I59" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J59" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K59" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M59" t="n">
         <v>1.08</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O59" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P59" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R59" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S59" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T59" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U59" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V59" t="n">
         <v>1.22</v>
@@ -15389,13 +15389,13 @@
         <v>1.98</v>
       </c>
       <c r="X59" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y59" t="n">
         <v>970</v>
       </c>
       <c r="Z59" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA59" t="n">
         <v>140</v>
@@ -15404,13 +15404,13 @@
         <v>970</v>
       </c>
       <c r="AC59" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD59" t="n">
         <v>950</v>
       </c>
       <c r="AE59" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF59" t="n">
         <v>970</v>
@@ -15422,16 +15422,16 @@
         <v>950</v>
       </c>
       <c r="AI59" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ59" t="n">
         <v>24</v>
       </c>
       <c r="AK59" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL59" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM59" t="n">
         <v>140</v>
@@ -15440,125 +15440,125 @@
         <v>970</v>
       </c>
       <c r="AO59" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP59" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="AQ59" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AR59" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="AS59" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH59" t="n">
         <v>3.35</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BF59" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG59" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>3.3</v>
       </c>
       <c r="BI59" t="n">
         <v>2.66</v>
       </c>
       <c r="BJ59" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK59" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>1.58</v>
+        <v>9.6</v>
       </c>
       <c r="BN59" t="n">
         <v>4.7</v>
       </c>
       <c r="BO59" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP59" t="n">
         <v>1000</v>
       </c>
       <c r="BQ59" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR59" t="n">
         <v>1000</v>
       </c>
       <c r="BS59" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT59" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU59" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV59" t="n">
         <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX59" t="n">
         <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ59" t="n">
         <v>1000</v>
       </c>
       <c r="CA59" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
